--- a/backend/templates/template_cell_5g.xlsx
+++ b/backend/templates/template_cell_5g.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cell_5G" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cell_5G" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cell_5G'!$A$1:$AJ$1</definedName>
@@ -38830,69 +38830,69 @@
   </sheetData>
   <autoFilter ref="A1:AJ1"/>
   <dataValidations count="19">
-    <dataValidation sqref="A2:A1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$A$2:$A$35</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$B$2:$B$2995</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="H2:H1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VIP,VVIP"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="I2:I1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
+    <dataValidation sqref="J2:J1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Latitude không hợp lệ" error="Latitude phải trong khoảng 8.33–23.39" type="decimal" operator="between">
       <formula1>8.33</formula1>
       <formula2>23.39</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
+    <dataValidation sqref="K2:K1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Longitude không hợp lệ" error="Longitude phải trong khoảng 102.14–109.47" type="decimal" operator="between">
       <formula1>102.14</formula1>
       <formula2>109.47</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Indoor,Outdoor"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Ericsson,Nokia,Huawei,ZTE,Samsung"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
+    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>999</formula2>
     </dataValidation>
-    <dataValidation sqref="O2:O1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
+    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>359</formula2>
     </dataValidation>
-    <dataValidation sqref="P2:P1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="Q2:Q1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="R2:R1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
+    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>'_Lookups'!$C$2:$C$67</formula1>
+    <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+      <formula1>'_Lookups'!$C$2:$C$68</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"2x2,4x4,8x8"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="NR PCI phải trong khoảng 0 – 1007" type="whole" operator="between">
+    <dataValidation sqref="AC2:AC1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="NR PCI phải trong khoảng 0 – 1007" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1007</formula2>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1001" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+    <dataValidation sqref="AJ2:AJ1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X1001" showErrorMessage="1" showInputMessage="1" allowBlank="1" errorTitle="Cell max power không hợp lệ" error="Cell max power thường trong khoảng -30 đến 60 dBm" type="decimal" operator="between">
+    <dataValidation sqref="X2:X1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cell max power không hợp lệ" error="Cell max power thường trong khoảng -30 đến 60 dBm" type="decimal" operator="between">
       <formula1>-30</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -39830,11 +39830,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40728,7 +40728,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TEST_ANTENNA</t>
+          <t>TONGYU|T0004M3V011</t>
         </is>
       </c>
     </row>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TEST_HUAWEI_AAU5613-1</t>
+          <t>TONGYU|TDJ-809018DM-65FT0</t>
         </is>
       </c>
     </row>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TONGYU|T0004M3V011</t>
+          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
         </is>
       </c>
     </row>
@@ -40764,7 +40764,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-809018DM-65FT0</t>
+          <t>TONGYU|TDJ-9018DM-65FT0</t>
         </is>
       </c>
     </row>
@@ -40776,7 +40776,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+          <t>TONGYU|TDJH-182018DE-65F</t>
         </is>
       </c>
     </row>
@@ -40788,7 +40788,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018DM-65FT0</t>
+          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TONGYU|TDJH-182018DE-65F</t>
+          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
         </is>
       </c>
     </row>
@@ -40812,7 +40812,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -40824,7 +40824,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+          <t>test1</t>
         </is>
       </c>
     </row>
@@ -40832,6 +40832,11 @@
       <c r="B68" t="inlineStr">
         <is>
           <t>Phường Bình Hòa</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>test2</t>
         </is>
       </c>
     </row>

--- a/backend/templates/template_cell_5g.xlsx
+++ b/backend/templates/template_cell_5g.xlsx
@@ -38880,7 +38880,7 @@
       <formula2>30</formula2>
     </dataValidation>
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>'_Lookups'!$C$2:$C$68</formula1>
+      <formula1>'_Lookups'!$C$2:$C$83</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"2x2,4x4,8x8"</formula1>
@@ -40168,7 +40168,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GRENTECH|SGR-DTX-YC-18</t>
+          <t>ERICSSON|AIR3219B77U</t>
         </is>
       </c>
     </row>
@@ -40185,7 +40185,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HENGXIN|HX4W3319B2RNF</t>
+          <t>ERICSSON|AIR3265B41</t>
         </is>
       </c>
     </row>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HENGXIN|HXHH3820B2-EU</t>
+          <t>ERICSSON|AIR6419B41</t>
         </is>
       </c>
     </row>
@@ -40219,7 +40219,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HUAWEI|A19451811V01</t>
+          <t>ERICSSON|AIR6419B77D</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HUAWEI|A19451811V06</t>
+          <t>GRENTECH|SGR-DTX-YC-18</t>
         </is>
       </c>
     </row>
@@ -40253,7 +40253,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hengxin|HX4W6518DEF</t>
+          <t>HENGXIN|HX4W3319B2RNF</t>
         </is>
       </c>
     </row>
@@ -40270,7 +40270,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KATHREIN|739623</t>
+          <t>HENGXIN|HXHH3820B2-EU</t>
         </is>
       </c>
     </row>
@@ -40287,7 +40287,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KATHREIN|741 785</t>
+          <t>HUAWEI|A04040PA00v06</t>
         </is>
       </c>
     </row>
@@ -40304,7 +40304,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KATHREIN|741322</t>
+          <t>HUAWEI|A19451811V01</t>
         </is>
       </c>
     </row>
@@ -40321,7 +40321,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KATHREIN|742215</t>
+          <t>HUAWEI|A19451811V06</t>
         </is>
       </c>
     </row>
@@ -40338,7 +40338,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KATHREIN|742222V01</t>
+          <t>HUAWEI|AAU5336v</t>
         </is>
       </c>
     </row>
@@ -40355,7 +40355,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KATHREIN|742266V02</t>
+          <t>HUAWEI|AAU5356</t>
         </is>
       </c>
     </row>
@@ -40372,7 +40372,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KATHREIN|800 10492V01</t>
+          <t>HUAWEI|AAU5636m</t>
         </is>
       </c>
     </row>
@@ -40389,7 +40389,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KATHREIN|80010428</t>
+          <t>HUAWEI|AAU5636v</t>
         </is>
       </c>
     </row>
@@ -40406,7 +40406,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MOBI|MB3F-65-18DE10</t>
+          <t>HUAWEI|ADU4517R51v06</t>
         </is>
       </c>
     </row>
@@ -40423,7 +40423,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MOBI|MB900/1800-65-17/18DE10/8-C-VN</t>
+          <t>HUAWEI|AMB4519R47v06</t>
         </is>
       </c>
     </row>
@@ -40440,7 +40440,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NETOP|S-WAVE U-65-12D</t>
+          <t>Hengxin|HX4W6518DEF</t>
         </is>
       </c>
     </row>
@@ -40452,7 +40452,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>POWERSTORM|C-BXH-65606580-M</t>
+          <t>KATHREIN|739623</t>
         </is>
       </c>
     </row>
@@ -40464,7 +40464,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PROSE|2G4W4XBF-27</t>
+          <t>KATHREIN|741 785</t>
         </is>
       </c>
     </row>
@@ -40476,7 +40476,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROSE|S-WAVE EW_EW-65-14D-64F-O1</t>
+          <t>KATHREIN|741322</t>
         </is>
       </c>
     </row>
@@ -40488,7 +40488,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RFS|APX-906516L-0T0</t>
+          <t>KATHREIN|742215</t>
         </is>
       </c>
     </row>
@@ -40500,7 +40500,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RFS|APX86-906516L-T6</t>
+          <t>KATHREIN|742222V01</t>
         </is>
       </c>
     </row>
@@ -40512,7 +40512,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RFS|APXE20F-T6</t>
+          <t>KATHREIN|742266V02</t>
         </is>
       </c>
     </row>
@@ -40524,7 +40524,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ROSENBERGER|4WC-11M</t>
+          <t>KATHREIN|800 10492V01</t>
         </is>
       </c>
     </row>
@@ -40536,7 +40536,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ROSENBERGER|CA-D3W5V32F-SD01</t>
+          <t>KATHREIN|80010428</t>
         </is>
       </c>
     </row>
@@ -40548,7 +40548,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ROSENBERGER|G3WF-11M</t>
+          <t>MOBI|MB3F-65-18DE10</t>
         </is>
       </c>
     </row>
@@ -40560,7 +40560,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 0809/U-65-18DV8</t>
+          <t>MOBI|MB900/1800-65-17/18DE10/8-C-VN</t>
         </is>
       </c>
     </row>
@@ -40572,7 +40572,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 0809/U/U-65-18DV8-B5</t>
+          <t>NETOP|S-WAVE U-65-12D</t>
         </is>
       </c>
     </row>
@@ -40584,7 +40584,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 09-65-18DV10-B3</t>
+          <t>NOKIA|AQHC</t>
         </is>
       </c>
     </row>
@@ -40596,7 +40596,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 1800-65-18DT6</t>
+          <t>NOKIA|AQQV</t>
         </is>
       </c>
     </row>
@@ -40608,7 +40608,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-10/12-LP</t>
+          <t>NOKIA|AVHA</t>
         </is>
       </c>
     </row>
@@ -40620,7 +40620,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-180-4/4.5-O2</t>
+          <t>NOKIA|AVQG</t>
         </is>
       </c>
     </row>
@@ -40632,7 +40632,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE 7FW-OD-3-L500</t>
+          <t>POWERSTORM|C-BXH-65606580-M</t>
         </is>
       </c>
     </row>
@@ -40644,7 +40644,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-14D-O1</t>
+          <t>PROSE|2G4W4XBF-27</t>
         </is>
       </c>
     </row>
@@ -40656,7 +40656,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-18DV2/12-VN1</t>
+          <t>PROSE|S-WAVE EW_EW-65-14D-64F-O1</t>
         </is>
       </c>
     </row>
@@ -40668,7 +40668,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE EW/EW-65-9D-O1</t>
+          <t>RFS|APX-906516L-0T0</t>
         </is>
       </c>
     </row>
@@ -40680,7 +40680,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U-33-20DV10</t>
+          <t>RFS|APX86-906516L-T6</t>
         </is>
       </c>
     </row>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U-65-18DV10-B4</t>
+          <t>RFS|APXE20F-T6</t>
         </is>
       </c>
     </row>
@@ -40704,7 +40704,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U/U-33-20DV10-BS</t>
+          <t>ROSENBERGER|4WC-11M</t>
         </is>
       </c>
     </row>
@@ -40716,7 +40716,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROSENBERGER|S-WAVE U/U/U-33-21DT6-TS</t>
+          <t>ROSENBERGER|CA-D3W5V32F-SD01</t>
         </is>
       </c>
     </row>
@@ -40728,7 +40728,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TONGYU|T0004M3V011</t>
+          <t>ROSENBERGER|G3WF-11M</t>
         </is>
       </c>
     </row>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-809018DM-65FT0</t>
+          <t>ROSENBERGER|S-WAVE 0809/U-65-18DV8</t>
         </is>
       </c>
     </row>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+          <t>ROSENBERGER|S-WAVE 0809/U/U-65-18DV8-B5</t>
         </is>
       </c>
     </row>
@@ -40764,7 +40764,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TONGYU|TDJ-9018DM-65FT0</t>
+          <t>ROSENBERGER|S-WAVE 09-65-18DV10-B3</t>
         </is>
       </c>
     </row>
@@ -40776,7 +40776,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TONGYU|TDJH-182018DE-65F</t>
+          <t>ROSENBERGER|S-WAVE 1800-65-18DT6</t>
         </is>
       </c>
     </row>
@@ -40788,7 +40788,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+          <t>ROSENBERGER|S-WAVE 7FW-10/12-LP</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+          <t>ROSENBERGER|S-WAVE 7FW-180-4/4.5-O2</t>
         </is>
       </c>
     </row>
@@ -40812,7 +40812,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>ROSENBERGER|S-WAVE 7FW-OD-3-L500</t>
         </is>
       </c>
     </row>
@@ -40824,7 +40824,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-14D-O1</t>
         </is>
       </c>
     </row>
@@ -40836,7 +40836,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-18DV2/12-VN1</t>
         </is>
       </c>
     </row>
@@ -40846,6 +40846,11 @@
           <t>Phường Bình Khê</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE EW/EW-65-9D-O1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
@@ -40853,6 +40858,11 @@
           <t>Phường Bình Kiến</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U-33-20DV10</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
@@ -40860,6 +40870,11 @@
           <t>Phường Bình Long</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U-65-18DV10-B4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -40867,6 +40882,11 @@
           <t>Phường Bình Lộc</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U/U-33-20DV10-BS</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -40874,6 +40894,11 @@
           <t>Phường Bình Lợi Trung</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ROSENBERGER|S-WAVE U/U/U-33-21DT6-TS</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
@@ -40881,6 +40906,11 @@
           <t>Phường Bình Minh</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TONGYU|T0004M3V011</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -40888,6 +40918,11 @@
           <t>Phường Bình Phú</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-809018DM-65FT0</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
@@ -40895,6 +40930,11 @@
           <t>Phường Bình Phước</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-9018/1818DM-65PT6-C</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
@@ -40902,6 +40942,11 @@
           <t>Phường Bình Quới</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJ-9018DM-65FT0</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -40909,6 +40954,11 @@
           <t>Phường Bình Thuận</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TONGYU|TDJH-182018DE-65F</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -40916,6 +40966,11 @@
           <t>Phường Bình Thạnh</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TONGYU|TDQ-172722DEI-33FT2V3</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
@@ -40923,6 +40978,11 @@
           <t>Phường Bình Thới</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>YOLYCOM|YLPXT3S17216518-6MP</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
@@ -40930,6 +40990,11 @@
           <t>Phường Bình Thủy</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
@@ -40937,11 +41002,21 @@
           <t>Phường Bình Tiên</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>test1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
           <t>Phường Bình Trưng</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>test2</t>
         </is>
       </c>
     </row>

--- a/backend/templates/template_cell_5g.xlsx
+++ b/backend/templates/template_cell_5g.xlsx
@@ -38829,7 +38829,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AJ1"/>
-  <dataValidations count="19">
+  <dataValidations count="14">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
@@ -38858,26 +38858,6 @@
     </dataValidation>
     <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"Ericsson,Nokia,Huawei,ZTE,Samsung"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Độ cao không hợp lệ" error="Phải là số dương (m)" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>999</formula2>
-    </dataValidation>
-    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Azimuth không hợp lệ" error="Azimuth phải trong khoảng 0–359" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>359</formula2>
-    </dataValidation>
-    <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="M-tilt không hợp lệ" error="M-tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
-    </dataValidation>
-    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="E-Tilt không hợp lệ" error="E-Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
-    </dataValidation>
-    <dataValidation sqref="R2:R1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Total Tilt không hợp lệ" error="Total Tilt thường trong khoảng -30 đến 30" type="decimal" operator="between">
-      <formula1>-30</formula1>
-      <formula2>30</formula2>
     </dataValidation>
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$C$2:$C$83</formula1>
@@ -39445,7 +39425,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Độ cao anten (m) – bắt buộc, số dương</t>
+          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -39462,7 +39442,7 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Góc phương vị – bắt buộc, trong 0–359</t>
+          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -39479,7 +39459,7 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Mechanical tilt – bắt buộc</t>
+          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -39496,7 +39476,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Electrical tilt – bắt buộc</t>
+          <t>Electrical tilt – bắt buộc (số hoặc chuỗi, vd: 4 hoặc IBC)</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -39513,7 +39493,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Tổng tilt = M-tilt + E-Tilt (tự tính hoặc để trống)</t>
+          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">

--- a/backend/templates/template_cell_5g.xlsx
+++ b/backend/templates/template_cell_5g.xlsx
@@ -12,7 +12,7 @@
     <sheet name="_Lookups" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cell_5G'!$A$1:$AJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cell_5G'!$A$1:$AK$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1001"/>
+  <dimension ref="A1:AK1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -584,10 +584,10 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="35" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="26" customWidth="1" min="26" max="26"/>
@@ -600,7 +600,8 @@
     <col width="14" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="16" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -701,7 +702,7 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Baseband</t>
+          <t>Chung anten</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -782,6 +783,11 @@
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>MU-MIMO</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OSS</t>
         </is>
       </c>
     </row>
@@ -837,7 +843,11 @@
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>5G only</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="inlineStr">
@@ -864,6 +874,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AK2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -902,6 +913,7 @@
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -940,6 +952,7 @@
       <c r="AH4" s="2" t="n"/>
       <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="2" t="n"/>
+      <c r="AK4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
@@ -978,6 +991,7 @@
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1016,6 +1030,7 @@
       <c r="AH6" s="2" t="n"/>
       <c r="AI6" s="2" t="n"/>
       <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -1054,6 +1069,7 @@
       <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1092,6 +1108,7 @@
       <c r="AH8" s="2" t="n"/>
       <c r="AI8" s="2" t="n"/>
       <c r="AJ8" s="2" t="n"/>
+      <c r="AK8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -1130,6 +1147,7 @@
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1168,6 +1186,7 @@
       <c r="AH10" s="2" t="n"/>
       <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="2" t="n"/>
+      <c r="AK10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -1206,6 +1225,7 @@
       <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
+      <c r="AK11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1244,6 +1264,7 @@
       <c r="AH12" s="2" t="n"/>
       <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="2" t="n"/>
+      <c r="AK12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -1282,6 +1303,7 @@
       <c r="AH13" s="4" t="n"/>
       <c r="AI13" s="4" t="n"/>
       <c r="AJ13" s="4" t="n"/>
+      <c r="AK13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1320,6 +1342,7 @@
       <c r="AH14" s="2" t="n"/>
       <c r="AI14" s="2" t="n"/>
       <c r="AJ14" s="2" t="n"/>
+      <c r="AK14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -1358,6 +1381,7 @@
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
+      <c r="AK15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1396,6 +1420,7 @@
       <c r="AH16" s="2" t="n"/>
       <c r="AI16" s="2" t="n"/>
       <c r="AJ16" s="2" t="n"/>
+      <c r="AK16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1434,6 +1459,7 @@
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1472,6 +1498,7 @@
       <c r="AH18" s="2" t="n"/>
       <c r="AI18" s="2" t="n"/>
       <c r="AJ18" s="2" t="n"/>
+      <c r="AK18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1510,6 +1537,7 @@
       <c r="AH19" s="4" t="n"/>
       <c r="AI19" s="4" t="n"/>
       <c r="AJ19" s="4" t="n"/>
+      <c r="AK19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1548,6 +1576,7 @@
       <c r="AH20" s="2" t="n"/>
       <c r="AI20" s="2" t="n"/>
       <c r="AJ20" s="2" t="n"/>
+      <c r="AK20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1586,6 +1615,7 @@
       <c r="AH21" s="4" t="n"/>
       <c r="AI21" s="4" t="n"/>
       <c r="AJ21" s="4" t="n"/>
+      <c r="AK21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1624,6 +1654,7 @@
       <c r="AH22" s="2" t="n"/>
       <c r="AI22" s="2" t="n"/>
       <c r="AJ22" s="2" t="n"/>
+      <c r="AK22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1662,6 +1693,7 @@
       <c r="AH23" s="4" t="n"/>
       <c r="AI23" s="4" t="n"/>
       <c r="AJ23" s="4" t="n"/>
+      <c r="AK23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1700,6 +1732,7 @@
       <c r="AH24" s="2" t="n"/>
       <c r="AI24" s="2" t="n"/>
       <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1738,6 +1771,7 @@
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1776,6 +1810,7 @@
       <c r="AH26" s="2" t="n"/>
       <c r="AI26" s="2" t="n"/>
       <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -1814,6 +1849,7 @@
       <c r="AH27" s="4" t="n"/>
       <c r="AI27" s="4" t="n"/>
       <c r="AJ27" s="4" t="n"/>
+      <c r="AK27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1852,6 +1888,7 @@
       <c r="AH28" s="2" t="n"/>
       <c r="AI28" s="2" t="n"/>
       <c r="AJ28" s="2" t="n"/>
+      <c r="AK28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -1890,6 +1927,7 @@
       <c r="AH29" s="4" t="n"/>
       <c r="AI29" s="4" t="n"/>
       <c r="AJ29" s="4" t="n"/>
+      <c r="AK29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1928,6 +1966,7 @@
       <c r="AH30" s="2" t="n"/>
       <c r="AI30" s="2" t="n"/>
       <c r="AJ30" s="2" t="n"/>
+      <c r="AK30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1966,6 +2005,7 @@
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
+      <c r="AK31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2004,6 +2044,7 @@
       <c r="AH32" s="2" t="n"/>
       <c r="AI32" s="2" t="n"/>
       <c r="AJ32" s="2" t="n"/>
+      <c r="AK32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -2042,6 +2083,7 @@
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
       <c r="AJ33" s="4" t="n"/>
+      <c r="AK33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2080,6 +2122,7 @@
       <c r="AH34" s="2" t="n"/>
       <c r="AI34" s="2" t="n"/>
       <c r="AJ34" s="2" t="n"/>
+      <c r="AK34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -2118,6 +2161,7 @@
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="n"/>
       <c r="AJ35" s="4" t="n"/>
+      <c r="AK35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2156,6 +2200,7 @@
       <c r="AH36" s="2" t="n"/>
       <c r="AI36" s="2" t="n"/>
       <c r="AJ36" s="2" t="n"/>
+      <c r="AK36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -2194,6 +2239,7 @@
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
       <c r="AJ37" s="4" t="n"/>
+      <c r="AK37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2232,6 +2278,7 @@
       <c r="AH38" s="2" t="n"/>
       <c r="AI38" s="2" t="n"/>
       <c r="AJ38" s="2" t="n"/>
+      <c r="AK38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -2270,6 +2317,7 @@
       <c r="AH39" s="4" t="n"/>
       <c r="AI39" s="4" t="n"/>
       <c r="AJ39" s="4" t="n"/>
+      <c r="AK39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2308,6 +2356,7 @@
       <c r="AH40" s="2" t="n"/>
       <c r="AI40" s="2" t="n"/>
       <c r="AJ40" s="2" t="n"/>
+      <c r="AK40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2346,6 +2395,7 @@
       <c r="AH41" s="4" t="n"/>
       <c r="AI41" s="4" t="n"/>
       <c r="AJ41" s="4" t="n"/>
+      <c r="AK41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2384,6 +2434,7 @@
       <c r="AH42" s="2" t="n"/>
       <c r="AI42" s="2" t="n"/>
       <c r="AJ42" s="2" t="n"/>
+      <c r="AK42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -2422,6 +2473,7 @@
       <c r="AH43" s="4" t="n"/>
       <c r="AI43" s="4" t="n"/>
       <c r="AJ43" s="4" t="n"/>
+      <c r="AK43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2460,6 +2512,7 @@
       <c r="AH44" s="2" t="n"/>
       <c r="AI44" s="2" t="n"/>
       <c r="AJ44" s="2" t="n"/>
+      <c r="AK44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -2498,6 +2551,7 @@
       <c r="AH45" s="4" t="n"/>
       <c r="AI45" s="4" t="n"/>
       <c r="AJ45" s="4" t="n"/>
+      <c r="AK45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2536,6 +2590,7 @@
       <c r="AH46" s="2" t="n"/>
       <c r="AI46" s="2" t="n"/>
       <c r="AJ46" s="2" t="n"/>
+      <c r="AK46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -2574,6 +2629,7 @@
       <c r="AH47" s="4" t="n"/>
       <c r="AI47" s="4" t="n"/>
       <c r="AJ47" s="4" t="n"/>
+      <c r="AK47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2612,6 +2668,7 @@
       <c r="AH48" s="2" t="n"/>
       <c r="AI48" s="2" t="n"/>
       <c r="AJ48" s="2" t="n"/>
+      <c r="AK48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2650,6 +2707,7 @@
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="n"/>
       <c r="AJ49" s="4" t="n"/>
+      <c r="AK49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2688,6 +2746,7 @@
       <c r="AH50" s="2" t="n"/>
       <c r="AI50" s="2" t="n"/>
       <c r="AJ50" s="2" t="n"/>
+      <c r="AK50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2726,6 +2785,7 @@
       <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="n"/>
       <c r="AJ51" s="4" t="n"/>
+      <c r="AK51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2764,6 +2824,7 @@
       <c r="AH52" s="2" t="n"/>
       <c r="AI52" s="2" t="n"/>
       <c r="AJ52" s="2" t="n"/>
+      <c r="AK52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2802,6 +2863,7 @@
       <c r="AH53" s="4" t="n"/>
       <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
+      <c r="AK53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -2840,6 +2902,7 @@
       <c r="AH54" s="2" t="n"/>
       <c r="AI54" s="2" t="n"/>
       <c r="AJ54" s="2" t="n"/>
+      <c r="AK54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2878,6 +2941,7 @@
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
       <c r="AJ55" s="4" t="n"/>
+      <c r="AK55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -2916,6 +2980,7 @@
       <c r="AH56" s="2" t="n"/>
       <c r="AI56" s="2" t="n"/>
       <c r="AJ56" s="2" t="n"/>
+      <c r="AK56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2954,6 +3019,7 @@
       <c r="AH57" s="4" t="n"/>
       <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
+      <c r="AK57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -2992,6 +3058,7 @@
       <c r="AH58" s="2" t="n"/>
       <c r="AI58" s="2" t="n"/>
       <c r="AJ58" s="2" t="n"/>
+      <c r="AK58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -3030,6 +3097,7 @@
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="n"/>
       <c r="AJ59" s="4" t="n"/>
+      <c r="AK59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3068,6 +3136,7 @@
       <c r="AH60" s="2" t="n"/>
       <c r="AI60" s="2" t="n"/>
       <c r="AJ60" s="2" t="n"/>
+      <c r="AK60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -3106,6 +3175,7 @@
       <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="n"/>
       <c r="AJ61" s="4" t="n"/>
+      <c r="AK61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -3144,6 +3214,7 @@
       <c r="AH62" s="2" t="n"/>
       <c r="AI62" s="2" t="n"/>
       <c r="AJ62" s="2" t="n"/>
+      <c r="AK62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -3182,6 +3253,7 @@
       <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="n"/>
       <c r="AJ63" s="4" t="n"/>
+      <c r="AK63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -3220,6 +3292,7 @@
       <c r="AH64" s="2" t="n"/>
       <c r="AI64" s="2" t="n"/>
       <c r="AJ64" s="2" t="n"/>
+      <c r="AK64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -3258,6 +3331,7 @@
       <c r="AH65" s="4" t="n"/>
       <c r="AI65" s="4" t="n"/>
       <c r="AJ65" s="4" t="n"/>
+      <c r="AK65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -3296,6 +3370,7 @@
       <c r="AH66" s="2" t="n"/>
       <c r="AI66" s="2" t="n"/>
       <c r="AJ66" s="2" t="n"/>
+      <c r="AK66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -3334,6 +3409,7 @@
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="n"/>
       <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -3372,6 +3448,7 @@
       <c r="AH68" s="2" t="n"/>
       <c r="AI68" s="2" t="n"/>
       <c r="AJ68" s="2" t="n"/>
+      <c r="AK68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -3410,6 +3487,7 @@
       <c r="AH69" s="4" t="n"/>
       <c r="AI69" s="4" t="n"/>
       <c r="AJ69" s="4" t="n"/>
+      <c r="AK69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -3448,6 +3526,7 @@
       <c r="AH70" s="2" t="n"/>
       <c r="AI70" s="2" t="n"/>
       <c r="AJ70" s="2" t="n"/>
+      <c r="AK70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -3486,6 +3565,7 @@
       <c r="AH71" s="4" t="n"/>
       <c r="AI71" s="4" t="n"/>
       <c r="AJ71" s="4" t="n"/>
+      <c r="AK71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -3524,6 +3604,7 @@
       <c r="AH72" s="2" t="n"/>
       <c r="AI72" s="2" t="n"/>
       <c r="AJ72" s="2" t="n"/>
+      <c r="AK72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -3562,6 +3643,7 @@
       <c r="AH73" s="4" t="n"/>
       <c r="AI73" s="4" t="n"/>
       <c r="AJ73" s="4" t="n"/>
+      <c r="AK73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -3600,6 +3682,7 @@
       <c r="AH74" s="2" t="n"/>
       <c r="AI74" s="2" t="n"/>
       <c r="AJ74" s="2" t="n"/>
+      <c r="AK74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -3638,6 +3721,7 @@
       <c r="AH75" s="4" t="n"/>
       <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
+      <c r="AK75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -3676,6 +3760,7 @@
       <c r="AH76" s="2" t="n"/>
       <c r="AI76" s="2" t="n"/>
       <c r="AJ76" s="2" t="n"/>
+      <c r="AK76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -3714,6 +3799,7 @@
       <c r="AH77" s="4" t="n"/>
       <c r="AI77" s="4" t="n"/>
       <c r="AJ77" s="4" t="n"/>
+      <c r="AK77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -3752,6 +3838,7 @@
       <c r="AH78" s="2" t="n"/>
       <c r="AI78" s="2" t="n"/>
       <c r="AJ78" s="2" t="n"/>
+      <c r="AK78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -3790,6 +3877,7 @@
       <c r="AH79" s="4" t="n"/>
       <c r="AI79" s="4" t="n"/>
       <c r="AJ79" s="4" t="n"/>
+      <c r="AK79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -3828,6 +3916,7 @@
       <c r="AH80" s="2" t="n"/>
       <c r="AI80" s="2" t="n"/>
       <c r="AJ80" s="2" t="n"/>
+      <c r="AK80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -3866,6 +3955,7 @@
       <c r="AH81" s="4" t="n"/>
       <c r="AI81" s="4" t="n"/>
       <c r="AJ81" s="4" t="n"/>
+      <c r="AK81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -3904,6 +3994,7 @@
       <c r="AH82" s="2" t="n"/>
       <c r="AI82" s="2" t="n"/>
       <c r="AJ82" s="2" t="n"/>
+      <c r="AK82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -3942,6 +4033,7 @@
       <c r="AH83" s="4" t="n"/>
       <c r="AI83" s="4" t="n"/>
       <c r="AJ83" s="4" t="n"/>
+      <c r="AK83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -3980,6 +4072,7 @@
       <c r="AH84" s="2" t="n"/>
       <c r="AI84" s="2" t="n"/>
       <c r="AJ84" s="2" t="n"/>
+      <c r="AK84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -4018,6 +4111,7 @@
       <c r="AH85" s="4" t="n"/>
       <c r="AI85" s="4" t="n"/>
       <c r="AJ85" s="4" t="n"/>
+      <c r="AK85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -4056,6 +4150,7 @@
       <c r="AH86" s="2" t="n"/>
       <c r="AI86" s="2" t="n"/>
       <c r="AJ86" s="2" t="n"/>
+      <c r="AK86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -4094,6 +4189,7 @@
       <c r="AH87" s="4" t="n"/>
       <c r="AI87" s="4" t="n"/>
       <c r="AJ87" s="4" t="n"/>
+      <c r="AK87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -4132,6 +4228,7 @@
       <c r="AH88" s="2" t="n"/>
       <c r="AI88" s="2" t="n"/>
       <c r="AJ88" s="2" t="n"/>
+      <c r="AK88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -4170,6 +4267,7 @@
       <c r="AH89" s="4" t="n"/>
       <c r="AI89" s="4" t="n"/>
       <c r="AJ89" s="4" t="n"/>
+      <c r="AK89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -4208,6 +4306,7 @@
       <c r="AH90" s="2" t="n"/>
       <c r="AI90" s="2" t="n"/>
       <c r="AJ90" s="2" t="n"/>
+      <c r="AK90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -4246,6 +4345,7 @@
       <c r="AH91" s="4" t="n"/>
       <c r="AI91" s="4" t="n"/>
       <c r="AJ91" s="4" t="n"/>
+      <c r="AK91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -4284,6 +4384,7 @@
       <c r="AH92" s="2" t="n"/>
       <c r="AI92" s="2" t="n"/>
       <c r="AJ92" s="2" t="n"/>
+      <c r="AK92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -4322,6 +4423,7 @@
       <c r="AH93" s="4" t="n"/>
       <c r="AI93" s="4" t="n"/>
       <c r="AJ93" s="4" t="n"/>
+      <c r="AK93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -4360,6 +4462,7 @@
       <c r="AH94" s="2" t="n"/>
       <c r="AI94" s="2" t="n"/>
       <c r="AJ94" s="2" t="n"/>
+      <c r="AK94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -4398,6 +4501,7 @@
       <c r="AH95" s="4" t="n"/>
       <c r="AI95" s="4" t="n"/>
       <c r="AJ95" s="4" t="n"/>
+      <c r="AK95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -4436,6 +4540,7 @@
       <c r="AH96" s="2" t="n"/>
       <c r="AI96" s="2" t="n"/>
       <c r="AJ96" s="2" t="n"/>
+      <c r="AK96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -4474,6 +4579,7 @@
       <c r="AH97" s="4" t="n"/>
       <c r="AI97" s="4" t="n"/>
       <c r="AJ97" s="4" t="n"/>
+      <c r="AK97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -4512,6 +4618,7 @@
       <c r="AH98" s="2" t="n"/>
       <c r="AI98" s="2" t="n"/>
       <c r="AJ98" s="2" t="n"/>
+      <c r="AK98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -4550,6 +4657,7 @@
       <c r="AH99" s="4" t="n"/>
       <c r="AI99" s="4" t="n"/>
       <c r="AJ99" s="4" t="n"/>
+      <c r="AK99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -4588,6 +4696,7 @@
       <c r="AH100" s="2" t="n"/>
       <c r="AI100" s="2" t="n"/>
       <c r="AJ100" s="2" t="n"/>
+      <c r="AK100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -4626,6 +4735,7 @@
       <c r="AH101" s="4" t="n"/>
       <c r="AI101" s="4" t="n"/>
       <c r="AJ101" s="4" t="n"/>
+      <c r="AK101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -4664,6 +4774,7 @@
       <c r="AH102" s="2" t="n"/>
       <c r="AI102" s="2" t="n"/>
       <c r="AJ102" s="2" t="n"/>
+      <c r="AK102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -4702,6 +4813,7 @@
       <c r="AH103" s="4" t="n"/>
       <c r="AI103" s="4" t="n"/>
       <c r="AJ103" s="4" t="n"/>
+      <c r="AK103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -4740,6 +4852,7 @@
       <c r="AH104" s="2" t="n"/>
       <c r="AI104" s="2" t="n"/>
       <c r="AJ104" s="2" t="n"/>
+      <c r="AK104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -4778,6 +4891,7 @@
       <c r="AH105" s="4" t="n"/>
       <c r="AI105" s="4" t="n"/>
       <c r="AJ105" s="4" t="n"/>
+      <c r="AK105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -4816,6 +4930,7 @@
       <c r="AH106" s="2" t="n"/>
       <c r="AI106" s="2" t="n"/>
       <c r="AJ106" s="2" t="n"/>
+      <c r="AK106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -4854,6 +4969,7 @@
       <c r="AH107" s="4" t="n"/>
       <c r="AI107" s="4" t="n"/>
       <c r="AJ107" s="4" t="n"/>
+      <c r="AK107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -4892,6 +5008,7 @@
       <c r="AH108" s="2" t="n"/>
       <c r="AI108" s="2" t="n"/>
       <c r="AJ108" s="2" t="n"/>
+      <c r="AK108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -4930,6 +5047,7 @@
       <c r="AH109" s="4" t="n"/>
       <c r="AI109" s="4" t="n"/>
       <c r="AJ109" s="4" t="n"/>
+      <c r="AK109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -4968,6 +5086,7 @@
       <c r="AH110" s="2" t="n"/>
       <c r="AI110" s="2" t="n"/>
       <c r="AJ110" s="2" t="n"/>
+      <c r="AK110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -5006,6 +5125,7 @@
       <c r="AH111" s="4" t="n"/>
       <c r="AI111" s="4" t="n"/>
       <c r="AJ111" s="4" t="n"/>
+      <c r="AK111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -5044,6 +5164,7 @@
       <c r="AH112" s="2" t="n"/>
       <c r="AI112" s="2" t="n"/>
       <c r="AJ112" s="2" t="n"/>
+      <c r="AK112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -5082,6 +5203,7 @@
       <c r="AH113" s="4" t="n"/>
       <c r="AI113" s="4" t="n"/>
       <c r="AJ113" s="4" t="n"/>
+      <c r="AK113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -5120,6 +5242,7 @@
       <c r="AH114" s="2" t="n"/>
       <c r="AI114" s="2" t="n"/>
       <c r="AJ114" s="2" t="n"/>
+      <c r="AK114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -5158,6 +5281,7 @@
       <c r="AH115" s="4" t="n"/>
       <c r="AI115" s="4" t="n"/>
       <c r="AJ115" s="4" t="n"/>
+      <c r="AK115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -5196,6 +5320,7 @@
       <c r="AH116" s="2" t="n"/>
       <c r="AI116" s="2" t="n"/>
       <c r="AJ116" s="2" t="n"/>
+      <c r="AK116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -5234,6 +5359,7 @@
       <c r="AH117" s="4" t="n"/>
       <c r="AI117" s="4" t="n"/>
       <c r="AJ117" s="4" t="n"/>
+      <c r="AK117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -5272,6 +5398,7 @@
       <c r="AH118" s="2" t="n"/>
       <c r="AI118" s="2" t="n"/>
       <c r="AJ118" s="2" t="n"/>
+      <c r="AK118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -5310,6 +5437,7 @@
       <c r="AH119" s="4" t="n"/>
       <c r="AI119" s="4" t="n"/>
       <c r="AJ119" s="4" t="n"/>
+      <c r="AK119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -5348,6 +5476,7 @@
       <c r="AH120" s="2" t="n"/>
       <c r="AI120" s="2" t="n"/>
       <c r="AJ120" s="2" t="n"/>
+      <c r="AK120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -5386,6 +5515,7 @@
       <c r="AH121" s="4" t="n"/>
       <c r="AI121" s="4" t="n"/>
       <c r="AJ121" s="4" t="n"/>
+      <c r="AK121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -5424,6 +5554,7 @@
       <c r="AH122" s="2" t="n"/>
       <c r="AI122" s="2" t="n"/>
       <c r="AJ122" s="2" t="n"/>
+      <c r="AK122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -5462,6 +5593,7 @@
       <c r="AH123" s="4" t="n"/>
       <c r="AI123" s="4" t="n"/>
       <c r="AJ123" s="4" t="n"/>
+      <c r="AK123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -5500,6 +5632,7 @@
       <c r="AH124" s="2" t="n"/>
       <c r="AI124" s="2" t="n"/>
       <c r="AJ124" s="2" t="n"/>
+      <c r="AK124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -5538,6 +5671,7 @@
       <c r="AH125" s="4" t="n"/>
       <c r="AI125" s="4" t="n"/>
       <c r="AJ125" s="4" t="n"/>
+      <c r="AK125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -5576,6 +5710,7 @@
       <c r="AH126" s="2" t="n"/>
       <c r="AI126" s="2" t="n"/>
       <c r="AJ126" s="2" t="n"/>
+      <c r="AK126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -5614,6 +5749,7 @@
       <c r="AH127" s="4" t="n"/>
       <c r="AI127" s="4" t="n"/>
       <c r="AJ127" s="4" t="n"/>
+      <c r="AK127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -5652,6 +5788,7 @@
       <c r="AH128" s="2" t="n"/>
       <c r="AI128" s="2" t="n"/>
       <c r="AJ128" s="2" t="n"/>
+      <c r="AK128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -5690,6 +5827,7 @@
       <c r="AH129" s="4" t="n"/>
       <c r="AI129" s="4" t="n"/>
       <c r="AJ129" s="4" t="n"/>
+      <c r="AK129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -5728,6 +5866,7 @@
       <c r="AH130" s="2" t="n"/>
       <c r="AI130" s="2" t="n"/>
       <c r="AJ130" s="2" t="n"/>
+      <c r="AK130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -5766,6 +5905,7 @@
       <c r="AH131" s="4" t="n"/>
       <c r="AI131" s="4" t="n"/>
       <c r="AJ131" s="4" t="n"/>
+      <c r="AK131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -5804,6 +5944,7 @@
       <c r="AH132" s="2" t="n"/>
       <c r="AI132" s="2" t="n"/>
       <c r="AJ132" s="2" t="n"/>
+      <c r="AK132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -5842,6 +5983,7 @@
       <c r="AH133" s="4" t="n"/>
       <c r="AI133" s="4" t="n"/>
       <c r="AJ133" s="4" t="n"/>
+      <c r="AK133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -5880,6 +6022,7 @@
       <c r="AH134" s="2" t="n"/>
       <c r="AI134" s="2" t="n"/>
       <c r="AJ134" s="2" t="n"/>
+      <c r="AK134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -5918,6 +6061,7 @@
       <c r="AH135" s="4" t="n"/>
       <c r="AI135" s="4" t="n"/>
       <c r="AJ135" s="4" t="n"/>
+      <c r="AK135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -5956,6 +6100,7 @@
       <c r="AH136" s="2" t="n"/>
       <c r="AI136" s="2" t="n"/>
       <c r="AJ136" s="2" t="n"/>
+      <c r="AK136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -5994,6 +6139,7 @@
       <c r="AH137" s="4" t="n"/>
       <c r="AI137" s="4" t="n"/>
       <c r="AJ137" s="4" t="n"/>
+      <c r="AK137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -6032,6 +6178,7 @@
       <c r="AH138" s="2" t="n"/>
       <c r="AI138" s="2" t="n"/>
       <c r="AJ138" s="2" t="n"/>
+      <c r="AK138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -6070,6 +6217,7 @@
       <c r="AH139" s="4" t="n"/>
       <c r="AI139" s="4" t="n"/>
       <c r="AJ139" s="4" t="n"/>
+      <c r="AK139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -6108,6 +6256,7 @@
       <c r="AH140" s="2" t="n"/>
       <c r="AI140" s="2" t="n"/>
       <c r="AJ140" s="2" t="n"/>
+      <c r="AK140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -6146,6 +6295,7 @@
       <c r="AH141" s="4" t="n"/>
       <c r="AI141" s="4" t="n"/>
       <c r="AJ141" s="4" t="n"/>
+      <c r="AK141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -6184,6 +6334,7 @@
       <c r="AH142" s="2" t="n"/>
       <c r="AI142" s="2" t="n"/>
       <c r="AJ142" s="2" t="n"/>
+      <c r="AK142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -6222,6 +6373,7 @@
       <c r="AH143" s="4" t="n"/>
       <c r="AI143" s="4" t="n"/>
       <c r="AJ143" s="4" t="n"/>
+      <c r="AK143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -6260,6 +6412,7 @@
       <c r="AH144" s="2" t="n"/>
       <c r="AI144" s="2" t="n"/>
       <c r="AJ144" s="2" t="n"/>
+      <c r="AK144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -6298,6 +6451,7 @@
       <c r="AH145" s="4" t="n"/>
       <c r="AI145" s="4" t="n"/>
       <c r="AJ145" s="4" t="n"/>
+      <c r="AK145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -6336,6 +6490,7 @@
       <c r="AH146" s="2" t="n"/>
       <c r="AI146" s="2" t="n"/>
       <c r="AJ146" s="2" t="n"/>
+      <c r="AK146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -6374,6 +6529,7 @@
       <c r="AH147" s="4" t="n"/>
       <c r="AI147" s="4" t="n"/>
       <c r="AJ147" s="4" t="n"/>
+      <c r="AK147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -6412,6 +6568,7 @@
       <c r="AH148" s="2" t="n"/>
       <c r="AI148" s="2" t="n"/>
       <c r="AJ148" s="2" t="n"/>
+      <c r="AK148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -6450,6 +6607,7 @@
       <c r="AH149" s="4" t="n"/>
       <c r="AI149" s="4" t="n"/>
       <c r="AJ149" s="4" t="n"/>
+      <c r="AK149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -6488,6 +6646,7 @@
       <c r="AH150" s="2" t="n"/>
       <c r="AI150" s="2" t="n"/>
       <c r="AJ150" s="2" t="n"/>
+      <c r="AK150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -6526,6 +6685,7 @@
       <c r="AH151" s="4" t="n"/>
       <c r="AI151" s="4" t="n"/>
       <c r="AJ151" s="4" t="n"/>
+      <c r="AK151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -6564,6 +6724,7 @@
       <c r="AH152" s="2" t="n"/>
       <c r="AI152" s="2" t="n"/>
       <c r="AJ152" s="2" t="n"/>
+      <c r="AK152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -6602,6 +6763,7 @@
       <c r="AH153" s="4" t="n"/>
       <c r="AI153" s="4" t="n"/>
       <c r="AJ153" s="4" t="n"/>
+      <c r="AK153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -6640,6 +6802,7 @@
       <c r="AH154" s="2" t="n"/>
       <c r="AI154" s="2" t="n"/>
       <c r="AJ154" s="2" t="n"/>
+      <c r="AK154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -6678,6 +6841,7 @@
       <c r="AH155" s="4" t="n"/>
       <c r="AI155" s="4" t="n"/>
       <c r="AJ155" s="4" t="n"/>
+      <c r="AK155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -6716,6 +6880,7 @@
       <c r="AH156" s="2" t="n"/>
       <c r="AI156" s="2" t="n"/>
       <c r="AJ156" s="2" t="n"/>
+      <c r="AK156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -6754,6 +6919,7 @@
       <c r="AH157" s="4" t="n"/>
       <c r="AI157" s="4" t="n"/>
       <c r="AJ157" s="4" t="n"/>
+      <c r="AK157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -6792,6 +6958,7 @@
       <c r="AH158" s="2" t="n"/>
       <c r="AI158" s="2" t="n"/>
       <c r="AJ158" s="2" t="n"/>
+      <c r="AK158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -6830,6 +6997,7 @@
       <c r="AH159" s="4" t="n"/>
       <c r="AI159" s="4" t="n"/>
       <c r="AJ159" s="4" t="n"/>
+      <c r="AK159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -6868,6 +7036,7 @@
       <c r="AH160" s="2" t="n"/>
       <c r="AI160" s="2" t="n"/>
       <c r="AJ160" s="2" t="n"/>
+      <c r="AK160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -6906,6 +7075,7 @@
       <c r="AH161" s="4" t="n"/>
       <c r="AI161" s="4" t="n"/>
       <c r="AJ161" s="4" t="n"/>
+      <c r="AK161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -6944,6 +7114,7 @@
       <c r="AH162" s="2" t="n"/>
       <c r="AI162" s="2" t="n"/>
       <c r="AJ162" s="2" t="n"/>
+      <c r="AK162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -6982,6 +7153,7 @@
       <c r="AH163" s="4" t="n"/>
       <c r="AI163" s="4" t="n"/>
       <c r="AJ163" s="4" t="n"/>
+      <c r="AK163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -7020,6 +7192,7 @@
       <c r="AH164" s="2" t="n"/>
       <c r="AI164" s="2" t="n"/>
       <c r="AJ164" s="2" t="n"/>
+      <c r="AK164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -7058,6 +7231,7 @@
       <c r="AH165" s="4" t="n"/>
       <c r="AI165" s="4" t="n"/>
       <c r="AJ165" s="4" t="n"/>
+      <c r="AK165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -7096,6 +7270,7 @@
       <c r="AH166" s="2" t="n"/>
       <c r="AI166" s="2" t="n"/>
       <c r="AJ166" s="2" t="n"/>
+      <c r="AK166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -7134,6 +7309,7 @@
       <c r="AH167" s="4" t="n"/>
       <c r="AI167" s="4" t="n"/>
       <c r="AJ167" s="4" t="n"/>
+      <c r="AK167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -7172,6 +7348,7 @@
       <c r="AH168" s="2" t="n"/>
       <c r="AI168" s="2" t="n"/>
       <c r="AJ168" s="2" t="n"/>
+      <c r="AK168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -7210,6 +7387,7 @@
       <c r="AH169" s="4" t="n"/>
       <c r="AI169" s="4" t="n"/>
       <c r="AJ169" s="4" t="n"/>
+      <c r="AK169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -7248,6 +7426,7 @@
       <c r="AH170" s="2" t="n"/>
       <c r="AI170" s="2" t="n"/>
       <c r="AJ170" s="2" t="n"/>
+      <c r="AK170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -7286,6 +7465,7 @@
       <c r="AH171" s="4" t="n"/>
       <c r="AI171" s="4" t="n"/>
       <c r="AJ171" s="4" t="n"/>
+      <c r="AK171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -7324,6 +7504,7 @@
       <c r="AH172" s="2" t="n"/>
       <c r="AI172" s="2" t="n"/>
       <c r="AJ172" s="2" t="n"/>
+      <c r="AK172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -7362,6 +7543,7 @@
       <c r="AH173" s="4" t="n"/>
       <c r="AI173" s="4" t="n"/>
       <c r="AJ173" s="4" t="n"/>
+      <c r="AK173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -7400,6 +7582,7 @@
       <c r="AH174" s="2" t="n"/>
       <c r="AI174" s="2" t="n"/>
       <c r="AJ174" s="2" t="n"/>
+      <c r="AK174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -7438,6 +7621,7 @@
       <c r="AH175" s="4" t="n"/>
       <c r="AI175" s="4" t="n"/>
       <c r="AJ175" s="4" t="n"/>
+      <c r="AK175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -7476,6 +7660,7 @@
       <c r="AH176" s="2" t="n"/>
       <c r="AI176" s="2" t="n"/>
       <c r="AJ176" s="2" t="n"/>
+      <c r="AK176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -7514,6 +7699,7 @@
       <c r="AH177" s="4" t="n"/>
       <c r="AI177" s="4" t="n"/>
       <c r="AJ177" s="4" t="n"/>
+      <c r="AK177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -7552,6 +7738,7 @@
       <c r="AH178" s="2" t="n"/>
       <c r="AI178" s="2" t="n"/>
       <c r="AJ178" s="2" t="n"/>
+      <c r="AK178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -7590,6 +7777,7 @@
       <c r="AH179" s="4" t="n"/>
       <c r="AI179" s="4" t="n"/>
       <c r="AJ179" s="4" t="n"/>
+      <c r="AK179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -7628,6 +7816,7 @@
       <c r="AH180" s="2" t="n"/>
       <c r="AI180" s="2" t="n"/>
       <c r="AJ180" s="2" t="n"/>
+      <c r="AK180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -7666,6 +7855,7 @@
       <c r="AH181" s="4" t="n"/>
       <c r="AI181" s="4" t="n"/>
       <c r="AJ181" s="4" t="n"/>
+      <c r="AK181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -7704,6 +7894,7 @@
       <c r="AH182" s="2" t="n"/>
       <c r="AI182" s="2" t="n"/>
       <c r="AJ182" s="2" t="n"/>
+      <c r="AK182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -7742,6 +7933,7 @@
       <c r="AH183" s="4" t="n"/>
       <c r="AI183" s="4" t="n"/>
       <c r="AJ183" s="4" t="n"/>
+      <c r="AK183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -7780,6 +7972,7 @@
       <c r="AH184" s="2" t="n"/>
       <c r="AI184" s="2" t="n"/>
       <c r="AJ184" s="2" t="n"/>
+      <c r="AK184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -7818,6 +8011,7 @@
       <c r="AH185" s="4" t="n"/>
       <c r="AI185" s="4" t="n"/>
       <c r="AJ185" s="4" t="n"/>
+      <c r="AK185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -7856,6 +8050,7 @@
       <c r="AH186" s="2" t="n"/>
       <c r="AI186" s="2" t="n"/>
       <c r="AJ186" s="2" t="n"/>
+      <c r="AK186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -7894,6 +8089,7 @@
       <c r="AH187" s="4" t="n"/>
       <c r="AI187" s="4" t="n"/>
       <c r="AJ187" s="4" t="n"/>
+      <c r="AK187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -7932,6 +8128,7 @@
       <c r="AH188" s="2" t="n"/>
       <c r="AI188" s="2" t="n"/>
       <c r="AJ188" s="2" t="n"/>
+      <c r="AK188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -7970,6 +8167,7 @@
       <c r="AH189" s="4" t="n"/>
       <c r="AI189" s="4" t="n"/>
       <c r="AJ189" s="4" t="n"/>
+      <c r="AK189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -8008,6 +8206,7 @@
       <c r="AH190" s="2" t="n"/>
       <c r="AI190" s="2" t="n"/>
       <c r="AJ190" s="2" t="n"/>
+      <c r="AK190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -8046,6 +8245,7 @@
       <c r="AH191" s="4" t="n"/>
       <c r="AI191" s="4" t="n"/>
       <c r="AJ191" s="4" t="n"/>
+      <c r="AK191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -8084,6 +8284,7 @@
       <c r="AH192" s="2" t="n"/>
       <c r="AI192" s="2" t="n"/>
       <c r="AJ192" s="2" t="n"/>
+      <c r="AK192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -8122,6 +8323,7 @@
       <c r="AH193" s="4" t="n"/>
       <c r="AI193" s="4" t="n"/>
       <c r="AJ193" s="4" t="n"/>
+      <c r="AK193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -8160,6 +8362,7 @@
       <c r="AH194" s="2" t="n"/>
       <c r="AI194" s="2" t="n"/>
       <c r="AJ194" s="2" t="n"/>
+      <c r="AK194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -8198,6 +8401,7 @@
       <c r="AH195" s="4" t="n"/>
       <c r="AI195" s="4" t="n"/>
       <c r="AJ195" s="4" t="n"/>
+      <c r="AK195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -8236,6 +8440,7 @@
       <c r="AH196" s="2" t="n"/>
       <c r="AI196" s="2" t="n"/>
       <c r="AJ196" s="2" t="n"/>
+      <c r="AK196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -8274,6 +8479,7 @@
       <c r="AH197" s="4" t="n"/>
       <c r="AI197" s="4" t="n"/>
       <c r="AJ197" s="4" t="n"/>
+      <c r="AK197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -8312,6 +8518,7 @@
       <c r="AH198" s="2" t="n"/>
       <c r="AI198" s="2" t="n"/>
       <c r="AJ198" s="2" t="n"/>
+      <c r="AK198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -8350,6 +8557,7 @@
       <c r="AH199" s="4" t="n"/>
       <c r="AI199" s="4" t="n"/>
       <c r="AJ199" s="4" t="n"/>
+      <c r="AK199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -8388,6 +8596,7 @@
       <c r="AH200" s="2" t="n"/>
       <c r="AI200" s="2" t="n"/>
       <c r="AJ200" s="2" t="n"/>
+      <c r="AK200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -8426,6 +8635,7 @@
       <c r="AH201" s="4" t="n"/>
       <c r="AI201" s="4" t="n"/>
       <c r="AJ201" s="4" t="n"/>
+      <c r="AK201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -8464,6 +8674,7 @@
       <c r="AH202" s="2" t="n"/>
       <c r="AI202" s="2" t="n"/>
       <c r="AJ202" s="2" t="n"/>
+      <c r="AK202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -8502,6 +8713,7 @@
       <c r="AH203" s="4" t="n"/>
       <c r="AI203" s="4" t="n"/>
       <c r="AJ203" s="4" t="n"/>
+      <c r="AK203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -8540,6 +8752,7 @@
       <c r="AH204" s="2" t="n"/>
       <c r="AI204" s="2" t="n"/>
       <c r="AJ204" s="2" t="n"/>
+      <c r="AK204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n"/>
@@ -8578,6 +8791,7 @@
       <c r="AH205" s="4" t="n"/>
       <c r="AI205" s="4" t="n"/>
       <c r="AJ205" s="4" t="n"/>
+      <c r="AK205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -8616,6 +8830,7 @@
       <c r="AH206" s="2" t="n"/>
       <c r="AI206" s="2" t="n"/>
       <c r="AJ206" s="2" t="n"/>
+      <c r="AK206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
@@ -8654,6 +8869,7 @@
       <c r="AH207" s="4" t="n"/>
       <c r="AI207" s="4" t="n"/>
       <c r="AJ207" s="4" t="n"/>
+      <c r="AK207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -8692,6 +8908,7 @@
       <c r="AH208" s="2" t="n"/>
       <c r="AI208" s="2" t="n"/>
       <c r="AJ208" s="2" t="n"/>
+      <c r="AK208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -8730,6 +8947,7 @@
       <c r="AH209" s="4" t="n"/>
       <c r="AI209" s="4" t="n"/>
       <c r="AJ209" s="4" t="n"/>
+      <c r="AK209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -8768,6 +8986,7 @@
       <c r="AH210" s="2" t="n"/>
       <c r="AI210" s="2" t="n"/>
       <c r="AJ210" s="2" t="n"/>
+      <c r="AK210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
@@ -8806,6 +9025,7 @@
       <c r="AH211" s="4" t="n"/>
       <c r="AI211" s="4" t="n"/>
       <c r="AJ211" s="4" t="n"/>
+      <c r="AK211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -8844,6 +9064,7 @@
       <c r="AH212" s="2" t="n"/>
       <c r="AI212" s="2" t="n"/>
       <c r="AJ212" s="2" t="n"/>
+      <c r="AK212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
@@ -8882,6 +9103,7 @@
       <c r="AH213" s="4" t="n"/>
       <c r="AI213" s="4" t="n"/>
       <c r="AJ213" s="4" t="n"/>
+      <c r="AK213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -8920,6 +9142,7 @@
       <c r="AH214" s="2" t="n"/>
       <c r="AI214" s="2" t="n"/>
       <c r="AJ214" s="2" t="n"/>
+      <c r="AK214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -8958,6 +9181,7 @@
       <c r="AH215" s="4" t="n"/>
       <c r="AI215" s="4" t="n"/>
       <c r="AJ215" s="4" t="n"/>
+      <c r="AK215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -8996,6 +9220,7 @@
       <c r="AH216" s="2" t="n"/>
       <c r="AI216" s="2" t="n"/>
       <c r="AJ216" s="2" t="n"/>
+      <c r="AK216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -9034,6 +9259,7 @@
       <c r="AH217" s="4" t="n"/>
       <c r="AI217" s="4" t="n"/>
       <c r="AJ217" s="4" t="n"/>
+      <c r="AK217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -9072,6 +9298,7 @@
       <c r="AH218" s="2" t="n"/>
       <c r="AI218" s="2" t="n"/>
       <c r="AJ218" s="2" t="n"/>
+      <c r="AK218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n"/>
@@ -9110,6 +9337,7 @@
       <c r="AH219" s="4" t="n"/>
       <c r="AI219" s="4" t="n"/>
       <c r="AJ219" s="4" t="n"/>
+      <c r="AK219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -9148,6 +9376,7 @@
       <c r="AH220" s="2" t="n"/>
       <c r="AI220" s="2" t="n"/>
       <c r="AJ220" s="2" t="n"/>
+      <c r="AK220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n"/>
@@ -9186,6 +9415,7 @@
       <c r="AH221" s="4" t="n"/>
       <c r="AI221" s="4" t="n"/>
       <c r="AJ221" s="4" t="n"/>
+      <c r="AK221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -9224,6 +9454,7 @@
       <c r="AH222" s="2" t="n"/>
       <c r="AI222" s="2" t="n"/>
       <c r="AJ222" s="2" t="n"/>
+      <c r="AK222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n"/>
@@ -9262,6 +9493,7 @@
       <c r="AH223" s="4" t="n"/>
       <c r="AI223" s="4" t="n"/>
       <c r="AJ223" s="4" t="n"/>
+      <c r="AK223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -9300,6 +9532,7 @@
       <c r="AH224" s="2" t="n"/>
       <c r="AI224" s="2" t="n"/>
       <c r="AJ224" s="2" t="n"/>
+      <c r="AK224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n"/>
@@ -9338,6 +9571,7 @@
       <c r="AH225" s="4" t="n"/>
       <c r="AI225" s="4" t="n"/>
       <c r="AJ225" s="4" t="n"/>
+      <c r="AK225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -9376,6 +9610,7 @@
       <c r="AH226" s="2" t="n"/>
       <c r="AI226" s="2" t="n"/>
       <c r="AJ226" s="2" t="n"/>
+      <c r="AK226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n"/>
@@ -9414,6 +9649,7 @@
       <c r="AH227" s="4" t="n"/>
       <c r="AI227" s="4" t="n"/>
       <c r="AJ227" s="4" t="n"/>
+      <c r="AK227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -9452,6 +9688,7 @@
       <c r="AH228" s="2" t="n"/>
       <c r="AI228" s="2" t="n"/>
       <c r="AJ228" s="2" t="n"/>
+      <c r="AK228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n"/>
@@ -9490,6 +9727,7 @@
       <c r="AH229" s="4" t="n"/>
       <c r="AI229" s="4" t="n"/>
       <c r="AJ229" s="4" t="n"/>
+      <c r="AK229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -9528,6 +9766,7 @@
       <c r="AH230" s="2" t="n"/>
       <c r="AI230" s="2" t="n"/>
       <c r="AJ230" s="2" t="n"/>
+      <c r="AK230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n"/>
@@ -9566,6 +9805,7 @@
       <c r="AH231" s="4" t="n"/>
       <c r="AI231" s="4" t="n"/>
       <c r="AJ231" s="4" t="n"/>
+      <c r="AK231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -9604,6 +9844,7 @@
       <c r="AH232" s="2" t="n"/>
       <c r="AI232" s="2" t="n"/>
       <c r="AJ232" s="2" t="n"/>
+      <c r="AK232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n"/>
@@ -9642,6 +9883,7 @@
       <c r="AH233" s="4" t="n"/>
       <c r="AI233" s="4" t="n"/>
       <c r="AJ233" s="4" t="n"/>
+      <c r="AK233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -9680,6 +9922,7 @@
       <c r="AH234" s="2" t="n"/>
       <c r="AI234" s="2" t="n"/>
       <c r="AJ234" s="2" t="n"/>
+      <c r="AK234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
@@ -9718,6 +9961,7 @@
       <c r="AH235" s="4" t="n"/>
       <c r="AI235" s="4" t="n"/>
       <c r="AJ235" s="4" t="n"/>
+      <c r="AK235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -9756,6 +10000,7 @@
       <c r="AH236" s="2" t="n"/>
       <c r="AI236" s="2" t="n"/>
       <c r="AJ236" s="2" t="n"/>
+      <c r="AK236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
@@ -9794,6 +10039,7 @@
       <c r="AH237" s="4" t="n"/>
       <c r="AI237" s="4" t="n"/>
       <c r="AJ237" s="4" t="n"/>
+      <c r="AK237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -9832,6 +10078,7 @@
       <c r="AH238" s="2" t="n"/>
       <c r="AI238" s="2" t="n"/>
       <c r="AJ238" s="2" t="n"/>
+      <c r="AK238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
@@ -9870,6 +10117,7 @@
       <c r="AH239" s="4" t="n"/>
       <c r="AI239" s="4" t="n"/>
       <c r="AJ239" s="4" t="n"/>
+      <c r="AK239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -9908,6 +10156,7 @@
       <c r="AH240" s="2" t="n"/>
       <c r="AI240" s="2" t="n"/>
       <c r="AJ240" s="2" t="n"/>
+      <c r="AK240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
@@ -9946,6 +10195,7 @@
       <c r="AH241" s="4" t="n"/>
       <c r="AI241" s="4" t="n"/>
       <c r="AJ241" s="4" t="n"/>
+      <c r="AK241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -9984,6 +10234,7 @@
       <c r="AH242" s="2" t="n"/>
       <c r="AI242" s="2" t="n"/>
       <c r="AJ242" s="2" t="n"/>
+      <c r="AK242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n"/>
@@ -10022,6 +10273,7 @@
       <c r="AH243" s="4" t="n"/>
       <c r="AI243" s="4" t="n"/>
       <c r="AJ243" s="4" t="n"/>
+      <c r="AK243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -10060,6 +10312,7 @@
       <c r="AH244" s="2" t="n"/>
       <c r="AI244" s="2" t="n"/>
       <c r="AJ244" s="2" t="n"/>
+      <c r="AK244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n"/>
@@ -10098,6 +10351,7 @@
       <c r="AH245" s="4" t="n"/>
       <c r="AI245" s="4" t="n"/>
       <c r="AJ245" s="4" t="n"/>
+      <c r="AK245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -10136,6 +10390,7 @@
       <c r="AH246" s="2" t="n"/>
       <c r="AI246" s="2" t="n"/>
       <c r="AJ246" s="2" t="n"/>
+      <c r="AK246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -10174,6 +10429,7 @@
       <c r="AH247" s="4" t="n"/>
       <c r="AI247" s="4" t="n"/>
       <c r="AJ247" s="4" t="n"/>
+      <c r="AK247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -10212,6 +10468,7 @@
       <c r="AH248" s="2" t="n"/>
       <c r="AI248" s="2" t="n"/>
       <c r="AJ248" s="2" t="n"/>
+      <c r="AK248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n"/>
@@ -10250,6 +10507,7 @@
       <c r="AH249" s="4" t="n"/>
       <c r="AI249" s="4" t="n"/>
       <c r="AJ249" s="4" t="n"/>
+      <c r="AK249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -10288,6 +10546,7 @@
       <c r="AH250" s="2" t="n"/>
       <c r="AI250" s="2" t="n"/>
       <c r="AJ250" s="2" t="n"/>
+      <c r="AK250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n"/>
@@ -10326,6 +10585,7 @@
       <c r="AH251" s="4" t="n"/>
       <c r="AI251" s="4" t="n"/>
       <c r="AJ251" s="4" t="n"/>
+      <c r="AK251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -10364,6 +10624,7 @@
       <c r="AH252" s="2" t="n"/>
       <c r="AI252" s="2" t="n"/>
       <c r="AJ252" s="2" t="n"/>
+      <c r="AK252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
@@ -10402,6 +10663,7 @@
       <c r="AH253" s="4" t="n"/>
       <c r="AI253" s="4" t="n"/>
       <c r="AJ253" s="4" t="n"/>
+      <c r="AK253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -10440,6 +10702,7 @@
       <c r="AH254" s="2" t="n"/>
       <c r="AI254" s="2" t="n"/>
       <c r="AJ254" s="2" t="n"/>
+      <c r="AK254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n"/>
@@ -10478,6 +10741,7 @@
       <c r="AH255" s="4" t="n"/>
       <c r="AI255" s="4" t="n"/>
       <c r="AJ255" s="4" t="n"/>
+      <c r="AK255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -10516,6 +10780,7 @@
       <c r="AH256" s="2" t="n"/>
       <c r="AI256" s="2" t="n"/>
       <c r="AJ256" s="2" t="n"/>
+      <c r="AK256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
@@ -10554,6 +10819,7 @@
       <c r="AH257" s="4" t="n"/>
       <c r="AI257" s="4" t="n"/>
       <c r="AJ257" s="4" t="n"/>
+      <c r="AK257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -10592,6 +10858,7 @@
       <c r="AH258" s="2" t="n"/>
       <c r="AI258" s="2" t="n"/>
       <c r="AJ258" s="2" t="n"/>
+      <c r="AK258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
@@ -10630,6 +10897,7 @@
       <c r="AH259" s="4" t="n"/>
       <c r="AI259" s="4" t="n"/>
       <c r="AJ259" s="4" t="n"/>
+      <c r="AK259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -10668,6 +10936,7 @@
       <c r="AH260" s="2" t="n"/>
       <c r="AI260" s="2" t="n"/>
       <c r="AJ260" s="2" t="n"/>
+      <c r="AK260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
@@ -10706,6 +10975,7 @@
       <c r="AH261" s="4" t="n"/>
       <c r="AI261" s="4" t="n"/>
       <c r="AJ261" s="4" t="n"/>
+      <c r="AK261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -10744,6 +11014,7 @@
       <c r="AH262" s="2" t="n"/>
       <c r="AI262" s="2" t="n"/>
       <c r="AJ262" s="2" t="n"/>
+      <c r="AK262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n"/>
@@ -10782,6 +11053,7 @@
       <c r="AH263" s="4" t="n"/>
       <c r="AI263" s="4" t="n"/>
       <c r="AJ263" s="4" t="n"/>
+      <c r="AK263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -10820,6 +11092,7 @@
       <c r="AH264" s="2" t="n"/>
       <c r="AI264" s="2" t="n"/>
       <c r="AJ264" s="2" t="n"/>
+      <c r="AK264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
@@ -10858,6 +11131,7 @@
       <c r="AH265" s="4" t="n"/>
       <c r="AI265" s="4" t="n"/>
       <c r="AJ265" s="4" t="n"/>
+      <c r="AK265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -10896,6 +11170,7 @@
       <c r="AH266" s="2" t="n"/>
       <c r="AI266" s="2" t="n"/>
       <c r="AJ266" s="2" t="n"/>
+      <c r="AK266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
@@ -10934,6 +11209,7 @@
       <c r="AH267" s="4" t="n"/>
       <c r="AI267" s="4" t="n"/>
       <c r="AJ267" s="4" t="n"/>
+      <c r="AK267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -10972,6 +11248,7 @@
       <c r="AH268" s="2" t="n"/>
       <c r="AI268" s="2" t="n"/>
       <c r="AJ268" s="2" t="n"/>
+      <c r="AK268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n"/>
@@ -11010,6 +11287,7 @@
       <c r="AH269" s="4" t="n"/>
       <c r="AI269" s="4" t="n"/>
       <c r="AJ269" s="4" t="n"/>
+      <c r="AK269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -11048,6 +11326,7 @@
       <c r="AH270" s="2" t="n"/>
       <c r="AI270" s="2" t="n"/>
       <c r="AJ270" s="2" t="n"/>
+      <c r="AK270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
@@ -11086,6 +11365,7 @@
       <c r="AH271" s="4" t="n"/>
       <c r="AI271" s="4" t="n"/>
       <c r="AJ271" s="4" t="n"/>
+      <c r="AK271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -11124,6 +11404,7 @@
       <c r="AH272" s="2" t="n"/>
       <c r="AI272" s="2" t="n"/>
       <c r="AJ272" s="2" t="n"/>
+      <c r="AK272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n"/>
@@ -11162,6 +11443,7 @@
       <c r="AH273" s="4" t="n"/>
       <c r="AI273" s="4" t="n"/>
       <c r="AJ273" s="4" t="n"/>
+      <c r="AK273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -11200,6 +11482,7 @@
       <c r="AH274" s="2" t="n"/>
       <c r="AI274" s="2" t="n"/>
       <c r="AJ274" s="2" t="n"/>
+      <c r="AK274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n"/>
@@ -11238,6 +11521,7 @@
       <c r="AH275" s="4" t="n"/>
       <c r="AI275" s="4" t="n"/>
       <c r="AJ275" s="4" t="n"/>
+      <c r="AK275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -11276,6 +11560,7 @@
       <c r="AH276" s="2" t="n"/>
       <c r="AI276" s="2" t="n"/>
       <c r="AJ276" s="2" t="n"/>
+      <c r="AK276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n"/>
@@ -11314,6 +11599,7 @@
       <c r="AH277" s="4" t="n"/>
       <c r="AI277" s="4" t="n"/>
       <c r="AJ277" s="4" t="n"/>
+      <c r="AK277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -11352,6 +11638,7 @@
       <c r="AH278" s="2" t="n"/>
       <c r="AI278" s="2" t="n"/>
       <c r="AJ278" s="2" t="n"/>
+      <c r="AK278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n"/>
@@ -11390,6 +11677,7 @@
       <c r="AH279" s="4" t="n"/>
       <c r="AI279" s="4" t="n"/>
       <c r="AJ279" s="4" t="n"/>
+      <c r="AK279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -11428,6 +11716,7 @@
       <c r="AH280" s="2" t="n"/>
       <c r="AI280" s="2" t="n"/>
       <c r="AJ280" s="2" t="n"/>
+      <c r="AK280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n"/>
@@ -11466,6 +11755,7 @@
       <c r="AH281" s="4" t="n"/>
       <c r="AI281" s="4" t="n"/>
       <c r="AJ281" s="4" t="n"/>
+      <c r="AK281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -11504,6 +11794,7 @@
       <c r="AH282" s="2" t="n"/>
       <c r="AI282" s="2" t="n"/>
       <c r="AJ282" s="2" t="n"/>
+      <c r="AK282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n"/>
@@ -11542,6 +11833,7 @@
       <c r="AH283" s="4" t="n"/>
       <c r="AI283" s="4" t="n"/>
       <c r="AJ283" s="4" t="n"/>
+      <c r="AK283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -11580,6 +11872,7 @@
       <c r="AH284" s="2" t="n"/>
       <c r="AI284" s="2" t="n"/>
       <c r="AJ284" s="2" t="n"/>
+      <c r="AK284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n"/>
@@ -11618,6 +11911,7 @@
       <c r="AH285" s="4" t="n"/>
       <c r="AI285" s="4" t="n"/>
       <c r="AJ285" s="4" t="n"/>
+      <c r="AK285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -11656,6 +11950,7 @@
       <c r="AH286" s="2" t="n"/>
       <c r="AI286" s="2" t="n"/>
       <c r="AJ286" s="2" t="n"/>
+      <c r="AK286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n"/>
@@ -11694,6 +11989,7 @@
       <c r="AH287" s="4" t="n"/>
       <c r="AI287" s="4" t="n"/>
       <c r="AJ287" s="4" t="n"/>
+      <c r="AK287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -11732,6 +12028,7 @@
       <c r="AH288" s="2" t="n"/>
       <c r="AI288" s="2" t="n"/>
       <c r="AJ288" s="2" t="n"/>
+      <c r="AK288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n"/>
@@ -11770,6 +12067,7 @@
       <c r="AH289" s="4" t="n"/>
       <c r="AI289" s="4" t="n"/>
       <c r="AJ289" s="4" t="n"/>
+      <c r="AK289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -11808,6 +12106,7 @@
       <c r="AH290" s="2" t="n"/>
       <c r="AI290" s="2" t="n"/>
       <c r="AJ290" s="2" t="n"/>
+      <c r="AK290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n"/>
@@ -11846,6 +12145,7 @@
       <c r="AH291" s="4" t="n"/>
       <c r="AI291" s="4" t="n"/>
       <c r="AJ291" s="4" t="n"/>
+      <c r="AK291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -11884,6 +12184,7 @@
       <c r="AH292" s="2" t="n"/>
       <c r="AI292" s="2" t="n"/>
       <c r="AJ292" s="2" t="n"/>
+      <c r="AK292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n"/>
@@ -11922,6 +12223,7 @@
       <c r="AH293" s="4" t="n"/>
       <c r="AI293" s="4" t="n"/>
       <c r="AJ293" s="4" t="n"/>
+      <c r="AK293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -11960,6 +12262,7 @@
       <c r="AH294" s="2" t="n"/>
       <c r="AI294" s="2" t="n"/>
       <c r="AJ294" s="2" t="n"/>
+      <c r="AK294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n"/>
@@ -11998,6 +12301,7 @@
       <c r="AH295" s="4" t="n"/>
       <c r="AI295" s="4" t="n"/>
       <c r="AJ295" s="4" t="n"/>
+      <c r="AK295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -12036,6 +12340,7 @@
       <c r="AH296" s="2" t="n"/>
       <c r="AI296" s="2" t="n"/>
       <c r="AJ296" s="2" t="n"/>
+      <c r="AK296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n"/>
@@ -12074,6 +12379,7 @@
       <c r="AH297" s="4" t="n"/>
       <c r="AI297" s="4" t="n"/>
       <c r="AJ297" s="4" t="n"/>
+      <c r="AK297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -12112,6 +12418,7 @@
       <c r="AH298" s="2" t="n"/>
       <c r="AI298" s="2" t="n"/>
       <c r="AJ298" s="2" t="n"/>
+      <c r="AK298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n"/>
@@ -12150,6 +12457,7 @@
       <c r="AH299" s="4" t="n"/>
       <c r="AI299" s="4" t="n"/>
       <c r="AJ299" s="4" t="n"/>
+      <c r="AK299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -12188,6 +12496,7 @@
       <c r="AH300" s="2" t="n"/>
       <c r="AI300" s="2" t="n"/>
       <c r="AJ300" s="2" t="n"/>
+      <c r="AK300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n"/>
@@ -12226,6 +12535,7 @@
       <c r="AH301" s="4" t="n"/>
       <c r="AI301" s="4" t="n"/>
       <c r="AJ301" s="4" t="n"/>
+      <c r="AK301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -12264,6 +12574,7 @@
       <c r="AH302" s="2" t="n"/>
       <c r="AI302" s="2" t="n"/>
       <c r="AJ302" s="2" t="n"/>
+      <c r="AK302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n"/>
@@ -12302,6 +12613,7 @@
       <c r="AH303" s="4" t="n"/>
       <c r="AI303" s="4" t="n"/>
       <c r="AJ303" s="4" t="n"/>
+      <c r="AK303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -12340,6 +12652,7 @@
       <c r="AH304" s="2" t="n"/>
       <c r="AI304" s="2" t="n"/>
       <c r="AJ304" s="2" t="n"/>
+      <c r="AK304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n"/>
@@ -12378,6 +12691,7 @@
       <c r="AH305" s="4" t="n"/>
       <c r="AI305" s="4" t="n"/>
       <c r="AJ305" s="4" t="n"/>
+      <c r="AK305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -12416,6 +12730,7 @@
       <c r="AH306" s="2" t="n"/>
       <c r="AI306" s="2" t="n"/>
       <c r="AJ306" s="2" t="n"/>
+      <c r="AK306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n"/>
@@ -12454,6 +12769,7 @@
       <c r="AH307" s="4" t="n"/>
       <c r="AI307" s="4" t="n"/>
       <c r="AJ307" s="4" t="n"/>
+      <c r="AK307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -12492,6 +12808,7 @@
       <c r="AH308" s="2" t="n"/>
       <c r="AI308" s="2" t="n"/>
       <c r="AJ308" s="2" t="n"/>
+      <c r="AK308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n"/>
@@ -12530,6 +12847,7 @@
       <c r="AH309" s="4" t="n"/>
       <c r="AI309" s="4" t="n"/>
       <c r="AJ309" s="4" t="n"/>
+      <c r="AK309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -12568,6 +12886,7 @@
       <c r="AH310" s="2" t="n"/>
       <c r="AI310" s="2" t="n"/>
       <c r="AJ310" s="2" t="n"/>
+      <c r="AK310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n"/>
@@ -12606,6 +12925,7 @@
       <c r="AH311" s="4" t="n"/>
       <c r="AI311" s="4" t="n"/>
       <c r="AJ311" s="4" t="n"/>
+      <c r="AK311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -12644,6 +12964,7 @@
       <c r="AH312" s="2" t="n"/>
       <c r="AI312" s="2" t="n"/>
       <c r="AJ312" s="2" t="n"/>
+      <c r="AK312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="n"/>
@@ -12682,6 +13003,7 @@
       <c r="AH313" s="4" t="n"/>
       <c r="AI313" s="4" t="n"/>
       <c r="AJ313" s="4" t="n"/>
+      <c r="AK313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -12720,6 +13042,7 @@
       <c r="AH314" s="2" t="n"/>
       <c r="AI314" s="2" t="n"/>
       <c r="AJ314" s="2" t="n"/>
+      <c r="AK314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n"/>
@@ -12758,6 +13081,7 @@
       <c r="AH315" s="4" t="n"/>
       <c r="AI315" s="4" t="n"/>
       <c r="AJ315" s="4" t="n"/>
+      <c r="AK315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -12796,6 +13120,7 @@
       <c r="AH316" s="2" t="n"/>
       <c r="AI316" s="2" t="n"/>
       <c r="AJ316" s="2" t="n"/>
+      <c r="AK316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n"/>
@@ -12834,6 +13159,7 @@
       <c r="AH317" s="4" t="n"/>
       <c r="AI317" s="4" t="n"/>
       <c r="AJ317" s="4" t="n"/>
+      <c r="AK317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -12872,6 +13198,7 @@
       <c r="AH318" s="2" t="n"/>
       <c r="AI318" s="2" t="n"/>
       <c r="AJ318" s="2" t="n"/>
+      <c r="AK318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n"/>
@@ -12910,6 +13237,7 @@
       <c r="AH319" s="4" t="n"/>
       <c r="AI319" s="4" t="n"/>
       <c r="AJ319" s="4" t="n"/>
+      <c r="AK319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -12948,6 +13276,7 @@
       <c r="AH320" s="2" t="n"/>
       <c r="AI320" s="2" t="n"/>
       <c r="AJ320" s="2" t="n"/>
+      <c r="AK320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n"/>
@@ -12986,6 +13315,7 @@
       <c r="AH321" s="4" t="n"/>
       <c r="AI321" s="4" t="n"/>
       <c r="AJ321" s="4" t="n"/>
+      <c r="AK321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -13024,6 +13354,7 @@
       <c r="AH322" s="2" t="n"/>
       <c r="AI322" s="2" t="n"/>
       <c r="AJ322" s="2" t="n"/>
+      <c r="AK322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n"/>
@@ -13062,6 +13393,7 @@
       <c r="AH323" s="4" t="n"/>
       <c r="AI323" s="4" t="n"/>
       <c r="AJ323" s="4" t="n"/>
+      <c r="AK323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -13100,6 +13432,7 @@
       <c r="AH324" s="2" t="n"/>
       <c r="AI324" s="2" t="n"/>
       <c r="AJ324" s="2" t="n"/>
+      <c r="AK324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n"/>
@@ -13138,6 +13471,7 @@
       <c r="AH325" s="4" t="n"/>
       <c r="AI325" s="4" t="n"/>
       <c r="AJ325" s="4" t="n"/>
+      <c r="AK325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -13176,6 +13510,7 @@
       <c r="AH326" s="2" t="n"/>
       <c r="AI326" s="2" t="n"/>
       <c r="AJ326" s="2" t="n"/>
+      <c r="AK326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="n"/>
@@ -13214,6 +13549,7 @@
       <c r="AH327" s="4" t="n"/>
       <c r="AI327" s="4" t="n"/>
       <c r="AJ327" s="4" t="n"/>
+      <c r="AK327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -13252,6 +13588,7 @@
       <c r="AH328" s="2" t="n"/>
       <c r="AI328" s="2" t="n"/>
       <c r="AJ328" s="2" t="n"/>
+      <c r="AK328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="n"/>
@@ -13290,6 +13627,7 @@
       <c r="AH329" s="4" t="n"/>
       <c r="AI329" s="4" t="n"/>
       <c r="AJ329" s="4" t="n"/>
+      <c r="AK329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -13328,6 +13666,7 @@
       <c r="AH330" s="2" t="n"/>
       <c r="AI330" s="2" t="n"/>
       <c r="AJ330" s="2" t="n"/>
+      <c r="AK330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="n"/>
@@ -13366,6 +13705,7 @@
       <c r="AH331" s="4" t="n"/>
       <c r="AI331" s="4" t="n"/>
       <c r="AJ331" s="4" t="n"/>
+      <c r="AK331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -13404,6 +13744,7 @@
       <c r="AH332" s="2" t="n"/>
       <c r="AI332" s="2" t="n"/>
       <c r="AJ332" s="2" t="n"/>
+      <c r="AK332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="n"/>
@@ -13442,6 +13783,7 @@
       <c r="AH333" s="4" t="n"/>
       <c r="AI333" s="4" t="n"/>
       <c r="AJ333" s="4" t="n"/>
+      <c r="AK333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -13480,6 +13822,7 @@
       <c r="AH334" s="2" t="n"/>
       <c r="AI334" s="2" t="n"/>
       <c r="AJ334" s="2" t="n"/>
+      <c r="AK334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="n"/>
@@ -13518,6 +13861,7 @@
       <c r="AH335" s="4" t="n"/>
       <c r="AI335" s="4" t="n"/>
       <c r="AJ335" s="4" t="n"/>
+      <c r="AK335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -13556,6 +13900,7 @@
       <c r="AH336" s="2" t="n"/>
       <c r="AI336" s="2" t="n"/>
       <c r="AJ336" s="2" t="n"/>
+      <c r="AK336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n"/>
@@ -13594,6 +13939,7 @@
       <c r="AH337" s="4" t="n"/>
       <c r="AI337" s="4" t="n"/>
       <c r="AJ337" s="4" t="n"/>
+      <c r="AK337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -13632,6 +13978,7 @@
       <c r="AH338" s="2" t="n"/>
       <c r="AI338" s="2" t="n"/>
       <c r="AJ338" s="2" t="n"/>
+      <c r="AK338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n"/>
@@ -13670,6 +14017,7 @@
       <c r="AH339" s="4" t="n"/>
       <c r="AI339" s="4" t="n"/>
       <c r="AJ339" s="4" t="n"/>
+      <c r="AK339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -13708,6 +14056,7 @@
       <c r="AH340" s="2" t="n"/>
       <c r="AI340" s="2" t="n"/>
       <c r="AJ340" s="2" t="n"/>
+      <c r="AK340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n"/>
@@ -13746,6 +14095,7 @@
       <c r="AH341" s="4" t="n"/>
       <c r="AI341" s="4" t="n"/>
       <c r="AJ341" s="4" t="n"/>
+      <c r="AK341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -13784,6 +14134,7 @@
       <c r="AH342" s="2" t="n"/>
       <c r="AI342" s="2" t="n"/>
       <c r="AJ342" s="2" t="n"/>
+      <c r="AK342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n"/>
@@ -13822,6 +14173,7 @@
       <c r="AH343" s="4" t="n"/>
       <c r="AI343" s="4" t="n"/>
       <c r="AJ343" s="4" t="n"/>
+      <c r="AK343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -13860,6 +14212,7 @@
       <c r="AH344" s="2" t="n"/>
       <c r="AI344" s="2" t="n"/>
       <c r="AJ344" s="2" t="n"/>
+      <c r="AK344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n"/>
@@ -13898,6 +14251,7 @@
       <c r="AH345" s="4" t="n"/>
       <c r="AI345" s="4" t="n"/>
       <c r="AJ345" s="4" t="n"/>
+      <c r="AK345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -13936,6 +14290,7 @@
       <c r="AH346" s="2" t="n"/>
       <c r="AI346" s="2" t="n"/>
       <c r="AJ346" s="2" t="n"/>
+      <c r="AK346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n"/>
@@ -13974,6 +14329,7 @@
       <c r="AH347" s="4" t="n"/>
       <c r="AI347" s="4" t="n"/>
       <c r="AJ347" s="4" t="n"/>
+      <c r="AK347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -14012,6 +14368,7 @@
       <c r="AH348" s="2" t="n"/>
       <c r="AI348" s="2" t="n"/>
       <c r="AJ348" s="2" t="n"/>
+      <c r="AK348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n"/>
@@ -14050,6 +14407,7 @@
       <c r="AH349" s="4" t="n"/>
       <c r="AI349" s="4" t="n"/>
       <c r="AJ349" s="4" t="n"/>
+      <c r="AK349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -14088,6 +14446,7 @@
       <c r="AH350" s="2" t="n"/>
       <c r="AI350" s="2" t="n"/>
       <c r="AJ350" s="2" t="n"/>
+      <c r="AK350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n"/>
@@ -14126,6 +14485,7 @@
       <c r="AH351" s="4" t="n"/>
       <c r="AI351" s="4" t="n"/>
       <c r="AJ351" s="4" t="n"/>
+      <c r="AK351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -14164,6 +14524,7 @@
       <c r="AH352" s="2" t="n"/>
       <c r="AI352" s="2" t="n"/>
       <c r="AJ352" s="2" t="n"/>
+      <c r="AK352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n"/>
@@ -14202,6 +14563,7 @@
       <c r="AH353" s="4" t="n"/>
       <c r="AI353" s="4" t="n"/>
       <c r="AJ353" s="4" t="n"/>
+      <c r="AK353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -14240,6 +14602,7 @@
       <c r="AH354" s="2" t="n"/>
       <c r="AI354" s="2" t="n"/>
       <c r="AJ354" s="2" t="n"/>
+      <c r="AK354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n"/>
@@ -14278,6 +14641,7 @@
       <c r="AH355" s="4" t="n"/>
       <c r="AI355" s="4" t="n"/>
       <c r="AJ355" s="4" t="n"/>
+      <c r="AK355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -14316,6 +14680,7 @@
       <c r="AH356" s="2" t="n"/>
       <c r="AI356" s="2" t="n"/>
       <c r="AJ356" s="2" t="n"/>
+      <c r="AK356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n"/>
@@ -14354,6 +14719,7 @@
       <c r="AH357" s="4" t="n"/>
       <c r="AI357" s="4" t="n"/>
       <c r="AJ357" s="4" t="n"/>
+      <c r="AK357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -14392,6 +14758,7 @@
       <c r="AH358" s="2" t="n"/>
       <c r="AI358" s="2" t="n"/>
       <c r="AJ358" s="2" t="n"/>
+      <c r="AK358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n"/>
@@ -14430,6 +14797,7 @@
       <c r="AH359" s="4" t="n"/>
       <c r="AI359" s="4" t="n"/>
       <c r="AJ359" s="4" t="n"/>
+      <c r="AK359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -14468,6 +14836,7 @@
       <c r="AH360" s="2" t="n"/>
       <c r="AI360" s="2" t="n"/>
       <c r="AJ360" s="2" t="n"/>
+      <c r="AK360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n"/>
@@ -14506,6 +14875,7 @@
       <c r="AH361" s="4" t="n"/>
       <c r="AI361" s="4" t="n"/>
       <c r="AJ361" s="4" t="n"/>
+      <c r="AK361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -14544,6 +14914,7 @@
       <c r="AH362" s="2" t="n"/>
       <c r="AI362" s="2" t="n"/>
       <c r="AJ362" s="2" t="n"/>
+      <c r="AK362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n"/>
@@ -14582,6 +14953,7 @@
       <c r="AH363" s="4" t="n"/>
       <c r="AI363" s="4" t="n"/>
       <c r="AJ363" s="4" t="n"/>
+      <c r="AK363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -14620,6 +14992,7 @@
       <c r="AH364" s="2" t="n"/>
       <c r="AI364" s="2" t="n"/>
       <c r="AJ364" s="2" t="n"/>
+      <c r="AK364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n"/>
@@ -14658,6 +15031,7 @@
       <c r="AH365" s="4" t="n"/>
       <c r="AI365" s="4" t="n"/>
       <c r="AJ365" s="4" t="n"/>
+      <c r="AK365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -14696,6 +15070,7 @@
       <c r="AH366" s="2" t="n"/>
       <c r="AI366" s="2" t="n"/>
       <c r="AJ366" s="2" t="n"/>
+      <c r="AK366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n"/>
@@ -14734,6 +15109,7 @@
       <c r="AH367" s="4" t="n"/>
       <c r="AI367" s="4" t="n"/>
       <c r="AJ367" s="4" t="n"/>
+      <c r="AK367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -14772,6 +15148,7 @@
       <c r="AH368" s="2" t="n"/>
       <c r="AI368" s="2" t="n"/>
       <c r="AJ368" s="2" t="n"/>
+      <c r="AK368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n"/>
@@ -14810,6 +15187,7 @@
       <c r="AH369" s="4" t="n"/>
       <c r="AI369" s="4" t="n"/>
       <c r="AJ369" s="4" t="n"/>
+      <c r="AK369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -14848,6 +15226,7 @@
       <c r="AH370" s="2" t="n"/>
       <c r="AI370" s="2" t="n"/>
       <c r="AJ370" s="2" t="n"/>
+      <c r="AK370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="4" t="n"/>
@@ -14886,6 +15265,7 @@
       <c r="AH371" s="4" t="n"/>
       <c r="AI371" s="4" t="n"/>
       <c r="AJ371" s="4" t="n"/>
+      <c r="AK371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -14924,6 +15304,7 @@
       <c r="AH372" s="2" t="n"/>
       <c r="AI372" s="2" t="n"/>
       <c r="AJ372" s="2" t="n"/>
+      <c r="AK372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n"/>
@@ -14962,6 +15343,7 @@
       <c r="AH373" s="4" t="n"/>
       <c r="AI373" s="4" t="n"/>
       <c r="AJ373" s="4" t="n"/>
+      <c r="AK373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -15000,6 +15382,7 @@
       <c r="AH374" s="2" t="n"/>
       <c r="AI374" s="2" t="n"/>
       <c r="AJ374" s="2" t="n"/>
+      <c r="AK374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="4" t="n"/>
@@ -15038,6 +15421,7 @@
       <c r="AH375" s="4" t="n"/>
       <c r="AI375" s="4" t="n"/>
       <c r="AJ375" s="4" t="n"/>
+      <c r="AK375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -15076,6 +15460,7 @@
       <c r="AH376" s="2" t="n"/>
       <c r="AI376" s="2" t="n"/>
       <c r="AJ376" s="2" t="n"/>
+      <c r="AK376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n"/>
@@ -15114,6 +15499,7 @@
       <c r="AH377" s="4" t="n"/>
       <c r="AI377" s="4" t="n"/>
       <c r="AJ377" s="4" t="n"/>
+      <c r="AK377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -15152,6 +15538,7 @@
       <c r="AH378" s="2" t="n"/>
       <c r="AI378" s="2" t="n"/>
       <c r="AJ378" s="2" t="n"/>
+      <c r="AK378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n"/>
@@ -15190,6 +15577,7 @@
       <c r="AH379" s="4" t="n"/>
       <c r="AI379" s="4" t="n"/>
       <c r="AJ379" s="4" t="n"/>
+      <c r="AK379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -15228,6 +15616,7 @@
       <c r="AH380" s="2" t="n"/>
       <c r="AI380" s="2" t="n"/>
       <c r="AJ380" s="2" t="n"/>
+      <c r="AK380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n"/>
@@ -15266,6 +15655,7 @@
       <c r="AH381" s="4" t="n"/>
       <c r="AI381" s="4" t="n"/>
       <c r="AJ381" s="4" t="n"/>
+      <c r="AK381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -15304,6 +15694,7 @@
       <c r="AH382" s="2" t="n"/>
       <c r="AI382" s="2" t="n"/>
       <c r="AJ382" s="2" t="n"/>
+      <c r="AK382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n"/>
@@ -15342,6 +15733,7 @@
       <c r="AH383" s="4" t="n"/>
       <c r="AI383" s="4" t="n"/>
       <c r="AJ383" s="4" t="n"/>
+      <c r="AK383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -15380,6 +15772,7 @@
       <c r="AH384" s="2" t="n"/>
       <c r="AI384" s="2" t="n"/>
       <c r="AJ384" s="2" t="n"/>
+      <c r="AK384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="4" t="n"/>
@@ -15418,6 +15811,7 @@
       <c r="AH385" s="4" t="n"/>
       <c r="AI385" s="4" t="n"/>
       <c r="AJ385" s="4" t="n"/>
+      <c r="AK385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -15456,6 +15850,7 @@
       <c r="AH386" s="2" t="n"/>
       <c r="AI386" s="2" t="n"/>
       <c r="AJ386" s="2" t="n"/>
+      <c r="AK386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n"/>
@@ -15494,6 +15889,7 @@
       <c r="AH387" s="4" t="n"/>
       <c r="AI387" s="4" t="n"/>
       <c r="AJ387" s="4" t="n"/>
+      <c r="AK387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -15532,6 +15928,7 @@
       <c r="AH388" s="2" t="n"/>
       <c r="AI388" s="2" t="n"/>
       <c r="AJ388" s="2" t="n"/>
+      <c r="AK388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n"/>
@@ -15570,6 +15967,7 @@
       <c r="AH389" s="4" t="n"/>
       <c r="AI389" s="4" t="n"/>
       <c r="AJ389" s="4" t="n"/>
+      <c r="AK389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -15608,6 +16006,7 @@
       <c r="AH390" s="2" t="n"/>
       <c r="AI390" s="2" t="n"/>
       <c r="AJ390" s="2" t="n"/>
+      <c r="AK390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="4" t="n"/>
@@ -15646,6 +16045,7 @@
       <c r="AH391" s="4" t="n"/>
       <c r="AI391" s="4" t="n"/>
       <c r="AJ391" s="4" t="n"/>
+      <c r="AK391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -15684,6 +16084,7 @@
       <c r="AH392" s="2" t="n"/>
       <c r="AI392" s="2" t="n"/>
       <c r="AJ392" s="2" t="n"/>
+      <c r="AK392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n"/>
@@ -15722,6 +16123,7 @@
       <c r="AH393" s="4" t="n"/>
       <c r="AI393" s="4" t="n"/>
       <c r="AJ393" s="4" t="n"/>
+      <c r="AK393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -15760,6 +16162,7 @@
       <c r="AH394" s="2" t="n"/>
       <c r="AI394" s="2" t="n"/>
       <c r="AJ394" s="2" t="n"/>
+      <c r="AK394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n"/>
@@ -15798,6 +16201,7 @@
       <c r="AH395" s="4" t="n"/>
       <c r="AI395" s="4" t="n"/>
       <c r="AJ395" s="4" t="n"/>
+      <c r="AK395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -15836,6 +16240,7 @@
       <c r="AH396" s="2" t="n"/>
       <c r="AI396" s="2" t="n"/>
       <c r="AJ396" s="2" t="n"/>
+      <c r="AK396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n"/>
@@ -15874,6 +16279,7 @@
       <c r="AH397" s="4" t="n"/>
       <c r="AI397" s="4" t="n"/>
       <c r="AJ397" s="4" t="n"/>
+      <c r="AK397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -15912,6 +16318,7 @@
       <c r="AH398" s="2" t="n"/>
       <c r="AI398" s="2" t="n"/>
       <c r="AJ398" s="2" t="n"/>
+      <c r="AK398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n"/>
@@ -15950,6 +16357,7 @@
       <c r="AH399" s="4" t="n"/>
       <c r="AI399" s="4" t="n"/>
       <c r="AJ399" s="4" t="n"/>
+      <c r="AK399" s="4" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -15988,6 +16396,7 @@
       <c r="AH400" s="2" t="n"/>
       <c r="AI400" s="2" t="n"/>
       <c r="AJ400" s="2" t="n"/>
+      <c r="AK400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n"/>
@@ -16026,6 +16435,7 @@
       <c r="AH401" s="4" t="n"/>
       <c r="AI401" s="4" t="n"/>
       <c r="AJ401" s="4" t="n"/>
+      <c r="AK401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -16064,6 +16474,7 @@
       <c r="AH402" s="2" t="n"/>
       <c r="AI402" s="2" t="n"/>
       <c r="AJ402" s="2" t="n"/>
+      <c r="AK402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="4" t="n"/>
@@ -16102,6 +16513,7 @@
       <c r="AH403" s="4" t="n"/>
       <c r="AI403" s="4" t="n"/>
       <c r="AJ403" s="4" t="n"/>
+      <c r="AK403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -16140,6 +16552,7 @@
       <c r="AH404" s="2" t="n"/>
       <c r="AI404" s="2" t="n"/>
       <c r="AJ404" s="2" t="n"/>
+      <c r="AK404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="4" t="n"/>
@@ -16178,6 +16591,7 @@
       <c r="AH405" s="4" t="n"/>
       <c r="AI405" s="4" t="n"/>
       <c r="AJ405" s="4" t="n"/>
+      <c r="AK405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -16216,6 +16630,7 @@
       <c r="AH406" s="2" t="n"/>
       <c r="AI406" s="2" t="n"/>
       <c r="AJ406" s="2" t="n"/>
+      <c r="AK406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="4" t="n"/>
@@ -16254,6 +16669,7 @@
       <c r="AH407" s="4" t="n"/>
       <c r="AI407" s="4" t="n"/>
       <c r="AJ407" s="4" t="n"/>
+      <c r="AK407" s="4" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -16292,6 +16708,7 @@
       <c r="AH408" s="2" t="n"/>
       <c r="AI408" s="2" t="n"/>
       <c r="AJ408" s="2" t="n"/>
+      <c r="AK408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="4" t="n"/>
@@ -16330,6 +16747,7 @@
       <c r="AH409" s="4" t="n"/>
       <c r="AI409" s="4" t="n"/>
       <c r="AJ409" s="4" t="n"/>
+      <c r="AK409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -16368,6 +16786,7 @@
       <c r="AH410" s="2" t="n"/>
       <c r="AI410" s="2" t="n"/>
       <c r="AJ410" s="2" t="n"/>
+      <c r="AK410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="4" t="n"/>
@@ -16406,6 +16825,7 @@
       <c r="AH411" s="4" t="n"/>
       <c r="AI411" s="4" t="n"/>
       <c r="AJ411" s="4" t="n"/>
+      <c r="AK411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -16444,6 +16864,7 @@
       <c r="AH412" s="2" t="n"/>
       <c r="AI412" s="2" t="n"/>
       <c r="AJ412" s="2" t="n"/>
+      <c r="AK412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="4" t="n"/>
@@ -16482,6 +16903,7 @@
       <c r="AH413" s="4" t="n"/>
       <c r="AI413" s="4" t="n"/>
       <c r="AJ413" s="4" t="n"/>
+      <c r="AK413" s="4" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -16520,6 +16942,7 @@
       <c r="AH414" s="2" t="n"/>
       <c r="AI414" s="2" t="n"/>
       <c r="AJ414" s="2" t="n"/>
+      <c r="AK414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n"/>
@@ -16558,6 +16981,7 @@
       <c r="AH415" s="4" t="n"/>
       <c r="AI415" s="4" t="n"/>
       <c r="AJ415" s="4" t="n"/>
+      <c r="AK415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -16596,6 +17020,7 @@
       <c r="AH416" s="2" t="n"/>
       <c r="AI416" s="2" t="n"/>
       <c r="AJ416" s="2" t="n"/>
+      <c r="AK416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="4" t="n"/>
@@ -16634,6 +17059,7 @@
       <c r="AH417" s="4" t="n"/>
       <c r="AI417" s="4" t="n"/>
       <c r="AJ417" s="4" t="n"/>
+      <c r="AK417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -16672,6 +17098,7 @@
       <c r="AH418" s="2" t="n"/>
       <c r="AI418" s="2" t="n"/>
       <c r="AJ418" s="2" t="n"/>
+      <c r="AK418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="4" t="n"/>
@@ -16710,6 +17137,7 @@
       <c r="AH419" s="4" t="n"/>
       <c r="AI419" s="4" t="n"/>
       <c r="AJ419" s="4" t="n"/>
+      <c r="AK419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -16748,6 +17176,7 @@
       <c r="AH420" s="2" t="n"/>
       <c r="AI420" s="2" t="n"/>
       <c r="AJ420" s="2" t="n"/>
+      <c r="AK420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="4" t="n"/>
@@ -16786,6 +17215,7 @@
       <c r="AH421" s="4" t="n"/>
       <c r="AI421" s="4" t="n"/>
       <c r="AJ421" s="4" t="n"/>
+      <c r="AK421" s="4" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -16824,6 +17254,7 @@
       <c r="AH422" s="2" t="n"/>
       <c r="AI422" s="2" t="n"/>
       <c r="AJ422" s="2" t="n"/>
+      <c r="AK422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="4" t="n"/>
@@ -16862,6 +17293,7 @@
       <c r="AH423" s="4" t="n"/>
       <c r="AI423" s="4" t="n"/>
       <c r="AJ423" s="4" t="n"/>
+      <c r="AK423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -16900,6 +17332,7 @@
       <c r="AH424" s="2" t="n"/>
       <c r="AI424" s="2" t="n"/>
       <c r="AJ424" s="2" t="n"/>
+      <c r="AK424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="4" t="n"/>
@@ -16938,6 +17371,7 @@
       <c r="AH425" s="4" t="n"/>
       <c r="AI425" s="4" t="n"/>
       <c r="AJ425" s="4" t="n"/>
+      <c r="AK425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -16976,6 +17410,7 @@
       <c r="AH426" s="2" t="n"/>
       <c r="AI426" s="2" t="n"/>
       <c r="AJ426" s="2" t="n"/>
+      <c r="AK426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="4" t="n"/>
@@ -17014,6 +17449,7 @@
       <c r="AH427" s="4" t="n"/>
       <c r="AI427" s="4" t="n"/>
       <c r="AJ427" s="4" t="n"/>
+      <c r="AK427" s="4" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -17052,6 +17488,7 @@
       <c r="AH428" s="2" t="n"/>
       <c r="AI428" s="2" t="n"/>
       <c r="AJ428" s="2" t="n"/>
+      <c r="AK428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n"/>
@@ -17090,6 +17527,7 @@
       <c r="AH429" s="4" t="n"/>
       <c r="AI429" s="4" t="n"/>
       <c r="AJ429" s="4" t="n"/>
+      <c r="AK429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -17128,6 +17566,7 @@
       <c r="AH430" s="2" t="n"/>
       <c r="AI430" s="2" t="n"/>
       <c r="AJ430" s="2" t="n"/>
+      <c r="AK430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="4" t="n"/>
@@ -17166,6 +17605,7 @@
       <c r="AH431" s="4" t="n"/>
       <c r="AI431" s="4" t="n"/>
       <c r="AJ431" s="4" t="n"/>
+      <c r="AK431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -17204,6 +17644,7 @@
       <c r="AH432" s="2" t="n"/>
       <c r="AI432" s="2" t="n"/>
       <c r="AJ432" s="2" t="n"/>
+      <c r="AK432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="4" t="n"/>
@@ -17242,6 +17683,7 @@
       <c r="AH433" s="4" t="n"/>
       <c r="AI433" s="4" t="n"/>
       <c r="AJ433" s="4" t="n"/>
+      <c r="AK433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -17280,6 +17722,7 @@
       <c r="AH434" s="2" t="n"/>
       <c r="AI434" s="2" t="n"/>
       <c r="AJ434" s="2" t="n"/>
+      <c r="AK434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="4" t="n"/>
@@ -17318,6 +17761,7 @@
       <c r="AH435" s="4" t="n"/>
       <c r="AI435" s="4" t="n"/>
       <c r="AJ435" s="4" t="n"/>
+      <c r="AK435" s="4" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -17356,6 +17800,7 @@
       <c r="AH436" s="2" t="n"/>
       <c r="AI436" s="2" t="n"/>
       <c r="AJ436" s="2" t="n"/>
+      <c r="AK436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="4" t="n"/>
@@ -17394,6 +17839,7 @@
       <c r="AH437" s="4" t="n"/>
       <c r="AI437" s="4" t="n"/>
       <c r="AJ437" s="4" t="n"/>
+      <c r="AK437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -17432,6 +17878,7 @@
       <c r="AH438" s="2" t="n"/>
       <c r="AI438" s="2" t="n"/>
       <c r="AJ438" s="2" t="n"/>
+      <c r="AK438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="4" t="n"/>
@@ -17470,6 +17917,7 @@
       <c r="AH439" s="4" t="n"/>
       <c r="AI439" s="4" t="n"/>
       <c r="AJ439" s="4" t="n"/>
+      <c r="AK439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -17508,6 +17956,7 @@
       <c r="AH440" s="2" t="n"/>
       <c r="AI440" s="2" t="n"/>
       <c r="AJ440" s="2" t="n"/>
+      <c r="AK440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="4" t="n"/>
@@ -17546,6 +17995,7 @@
       <c r="AH441" s="4" t="n"/>
       <c r="AI441" s="4" t="n"/>
       <c r="AJ441" s="4" t="n"/>
+      <c r="AK441" s="4" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -17584,6 +18034,7 @@
       <c r="AH442" s="2" t="n"/>
       <c r="AI442" s="2" t="n"/>
       <c r="AJ442" s="2" t="n"/>
+      <c r="AK442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n"/>
@@ -17622,6 +18073,7 @@
       <c r="AH443" s="4" t="n"/>
       <c r="AI443" s="4" t="n"/>
       <c r="AJ443" s="4" t="n"/>
+      <c r="AK443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -17660,6 +18112,7 @@
       <c r="AH444" s="2" t="n"/>
       <c r="AI444" s="2" t="n"/>
       <c r="AJ444" s="2" t="n"/>
+      <c r="AK444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="4" t="n"/>
@@ -17698,6 +18151,7 @@
       <c r="AH445" s="4" t="n"/>
       <c r="AI445" s="4" t="n"/>
       <c r="AJ445" s="4" t="n"/>
+      <c r="AK445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -17736,6 +18190,7 @@
       <c r="AH446" s="2" t="n"/>
       <c r="AI446" s="2" t="n"/>
       <c r="AJ446" s="2" t="n"/>
+      <c r="AK446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="4" t="n"/>
@@ -17774,6 +18229,7 @@
       <c r="AH447" s="4" t="n"/>
       <c r="AI447" s="4" t="n"/>
       <c r="AJ447" s="4" t="n"/>
+      <c r="AK447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -17812,6 +18268,7 @@
       <c r="AH448" s="2" t="n"/>
       <c r="AI448" s="2" t="n"/>
       <c r="AJ448" s="2" t="n"/>
+      <c r="AK448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="4" t="n"/>
@@ -17850,6 +18307,7 @@
       <c r="AH449" s="4" t="n"/>
       <c r="AI449" s="4" t="n"/>
       <c r="AJ449" s="4" t="n"/>
+      <c r="AK449" s="4" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -17888,6 +18346,7 @@
       <c r="AH450" s="2" t="n"/>
       <c r="AI450" s="2" t="n"/>
       <c r="AJ450" s="2" t="n"/>
+      <c r="AK450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="4" t="n"/>
@@ -17926,6 +18385,7 @@
       <c r="AH451" s="4" t="n"/>
       <c r="AI451" s="4" t="n"/>
       <c r="AJ451" s="4" t="n"/>
+      <c r="AK451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -17964,6 +18424,7 @@
       <c r="AH452" s="2" t="n"/>
       <c r="AI452" s="2" t="n"/>
       <c r="AJ452" s="2" t="n"/>
+      <c r="AK452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="4" t="n"/>
@@ -18002,6 +18463,7 @@
       <c r="AH453" s="4" t="n"/>
       <c r="AI453" s="4" t="n"/>
       <c r="AJ453" s="4" t="n"/>
+      <c r="AK453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -18040,6 +18502,7 @@
       <c r="AH454" s="2" t="n"/>
       <c r="AI454" s="2" t="n"/>
       <c r="AJ454" s="2" t="n"/>
+      <c r="AK454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="4" t="n"/>
@@ -18078,6 +18541,7 @@
       <c r="AH455" s="4" t="n"/>
       <c r="AI455" s="4" t="n"/>
       <c r="AJ455" s="4" t="n"/>
+      <c r="AK455" s="4" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -18116,6 +18580,7 @@
       <c r="AH456" s="2" t="n"/>
       <c r="AI456" s="2" t="n"/>
       <c r="AJ456" s="2" t="n"/>
+      <c r="AK456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="4" t="n"/>
@@ -18154,6 +18619,7 @@
       <c r="AH457" s="4" t="n"/>
       <c r="AI457" s="4" t="n"/>
       <c r="AJ457" s="4" t="n"/>
+      <c r="AK457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -18192,6 +18658,7 @@
       <c r="AH458" s="2" t="n"/>
       <c r="AI458" s="2" t="n"/>
       <c r="AJ458" s="2" t="n"/>
+      <c r="AK458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="4" t="n"/>
@@ -18230,6 +18697,7 @@
       <c r="AH459" s="4" t="n"/>
       <c r="AI459" s="4" t="n"/>
       <c r="AJ459" s="4" t="n"/>
+      <c r="AK459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -18268,6 +18736,7 @@
       <c r="AH460" s="2" t="n"/>
       <c r="AI460" s="2" t="n"/>
       <c r="AJ460" s="2" t="n"/>
+      <c r="AK460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="4" t="n"/>
@@ -18306,6 +18775,7 @@
       <c r="AH461" s="4" t="n"/>
       <c r="AI461" s="4" t="n"/>
       <c r="AJ461" s="4" t="n"/>
+      <c r="AK461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -18344,6 +18814,7 @@
       <c r="AH462" s="2" t="n"/>
       <c r="AI462" s="2" t="n"/>
       <c r="AJ462" s="2" t="n"/>
+      <c r="AK462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="4" t="n"/>
@@ -18382,6 +18853,7 @@
       <c r="AH463" s="4" t="n"/>
       <c r="AI463" s="4" t="n"/>
       <c r="AJ463" s="4" t="n"/>
+      <c r="AK463" s="4" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -18420,6 +18892,7 @@
       <c r="AH464" s="2" t="n"/>
       <c r="AI464" s="2" t="n"/>
       <c r="AJ464" s="2" t="n"/>
+      <c r="AK464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="4" t="n"/>
@@ -18458,6 +18931,7 @@
       <c r="AH465" s="4" t="n"/>
       <c r="AI465" s="4" t="n"/>
       <c r="AJ465" s="4" t="n"/>
+      <c r="AK465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -18496,6 +18970,7 @@
       <c r="AH466" s="2" t="n"/>
       <c r="AI466" s="2" t="n"/>
       <c r="AJ466" s="2" t="n"/>
+      <c r="AK466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="4" t="n"/>
@@ -18534,6 +19009,7 @@
       <c r="AH467" s="4" t="n"/>
       <c r="AI467" s="4" t="n"/>
       <c r="AJ467" s="4" t="n"/>
+      <c r="AK467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -18572,6 +19048,7 @@
       <c r="AH468" s="2" t="n"/>
       <c r="AI468" s="2" t="n"/>
       <c r="AJ468" s="2" t="n"/>
+      <c r="AK468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="4" t="n"/>
@@ -18610,6 +19087,7 @@
       <c r="AH469" s="4" t="n"/>
       <c r="AI469" s="4" t="n"/>
       <c r="AJ469" s="4" t="n"/>
+      <c r="AK469" s="4" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -18648,6 +19126,7 @@
       <c r="AH470" s="2" t="n"/>
       <c r="AI470" s="2" t="n"/>
       <c r="AJ470" s="2" t="n"/>
+      <c r="AK470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="4" t="n"/>
@@ -18686,6 +19165,7 @@
       <c r="AH471" s="4" t="n"/>
       <c r="AI471" s="4" t="n"/>
       <c r="AJ471" s="4" t="n"/>
+      <c r="AK471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -18724,6 +19204,7 @@
       <c r="AH472" s="2" t="n"/>
       <c r="AI472" s="2" t="n"/>
       <c r="AJ472" s="2" t="n"/>
+      <c r="AK472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="4" t="n"/>
@@ -18762,6 +19243,7 @@
       <c r="AH473" s="4" t="n"/>
       <c r="AI473" s="4" t="n"/>
       <c r="AJ473" s="4" t="n"/>
+      <c r="AK473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -18800,6 +19282,7 @@
       <c r="AH474" s="2" t="n"/>
       <c r="AI474" s="2" t="n"/>
       <c r="AJ474" s="2" t="n"/>
+      <c r="AK474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="4" t="n"/>
@@ -18838,6 +19321,7 @@
       <c r="AH475" s="4" t="n"/>
       <c r="AI475" s="4" t="n"/>
       <c r="AJ475" s="4" t="n"/>
+      <c r="AK475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -18876,6 +19360,7 @@
       <c r="AH476" s="2" t="n"/>
       <c r="AI476" s="2" t="n"/>
       <c r="AJ476" s="2" t="n"/>
+      <c r="AK476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="n"/>
@@ -18914,6 +19399,7 @@
       <c r="AH477" s="4" t="n"/>
       <c r="AI477" s="4" t="n"/>
       <c r="AJ477" s="4" t="n"/>
+      <c r="AK477" s="4" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -18952,6 +19438,7 @@
       <c r="AH478" s="2" t="n"/>
       <c r="AI478" s="2" t="n"/>
       <c r="AJ478" s="2" t="n"/>
+      <c r="AK478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="n"/>
@@ -18990,6 +19477,7 @@
       <c r="AH479" s="4" t="n"/>
       <c r="AI479" s="4" t="n"/>
       <c r="AJ479" s="4" t="n"/>
+      <c r="AK479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -19028,6 +19516,7 @@
       <c r="AH480" s="2" t="n"/>
       <c r="AI480" s="2" t="n"/>
       <c r="AJ480" s="2" t="n"/>
+      <c r="AK480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="n"/>
@@ -19066,6 +19555,7 @@
       <c r="AH481" s="4" t="n"/>
       <c r="AI481" s="4" t="n"/>
       <c r="AJ481" s="4" t="n"/>
+      <c r="AK481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -19104,6 +19594,7 @@
       <c r="AH482" s="2" t="n"/>
       <c r="AI482" s="2" t="n"/>
       <c r="AJ482" s="2" t="n"/>
+      <c r="AK482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="n"/>
@@ -19142,6 +19633,7 @@
       <c r="AH483" s="4" t="n"/>
       <c r="AI483" s="4" t="n"/>
       <c r="AJ483" s="4" t="n"/>
+      <c r="AK483" s="4" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -19180,6 +19672,7 @@
       <c r="AH484" s="2" t="n"/>
       <c r="AI484" s="2" t="n"/>
       <c r="AJ484" s="2" t="n"/>
+      <c r="AK484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="n"/>
@@ -19218,6 +19711,7 @@
       <c r="AH485" s="4" t="n"/>
       <c r="AI485" s="4" t="n"/>
       <c r="AJ485" s="4" t="n"/>
+      <c r="AK485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -19256,6 +19750,7 @@
       <c r="AH486" s="2" t="n"/>
       <c r="AI486" s="2" t="n"/>
       <c r="AJ486" s="2" t="n"/>
+      <c r="AK486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="n"/>
@@ -19294,6 +19789,7 @@
       <c r="AH487" s="4" t="n"/>
       <c r="AI487" s="4" t="n"/>
       <c r="AJ487" s="4" t="n"/>
+      <c r="AK487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -19332,6 +19828,7 @@
       <c r="AH488" s="2" t="n"/>
       <c r="AI488" s="2" t="n"/>
       <c r="AJ488" s="2" t="n"/>
+      <c r="AK488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="4" t="n"/>
@@ -19370,6 +19867,7 @@
       <c r="AH489" s="4" t="n"/>
       <c r="AI489" s="4" t="n"/>
       <c r="AJ489" s="4" t="n"/>
+      <c r="AK489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -19408,6 +19906,7 @@
       <c r="AH490" s="2" t="n"/>
       <c r="AI490" s="2" t="n"/>
       <c r="AJ490" s="2" t="n"/>
+      <c r="AK490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="4" t="n"/>
@@ -19446,6 +19945,7 @@
       <c r="AH491" s="4" t="n"/>
       <c r="AI491" s="4" t="n"/>
       <c r="AJ491" s="4" t="n"/>
+      <c r="AK491" s="4" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -19484,6 +19984,7 @@
       <c r="AH492" s="2" t="n"/>
       <c r="AI492" s="2" t="n"/>
       <c r="AJ492" s="2" t="n"/>
+      <c r="AK492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="n"/>
@@ -19522,6 +20023,7 @@
       <c r="AH493" s="4" t="n"/>
       <c r="AI493" s="4" t="n"/>
       <c r="AJ493" s="4" t="n"/>
+      <c r="AK493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -19560,6 +20062,7 @@
       <c r="AH494" s="2" t="n"/>
       <c r="AI494" s="2" t="n"/>
       <c r="AJ494" s="2" t="n"/>
+      <c r="AK494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="4" t="n"/>
@@ -19598,6 +20101,7 @@
       <c r="AH495" s="4" t="n"/>
       <c r="AI495" s="4" t="n"/>
       <c r="AJ495" s="4" t="n"/>
+      <c r="AK495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -19636,6 +20140,7 @@
       <c r="AH496" s="2" t="n"/>
       <c r="AI496" s="2" t="n"/>
       <c r="AJ496" s="2" t="n"/>
+      <c r="AK496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="4" t="n"/>
@@ -19674,6 +20179,7 @@
       <c r="AH497" s="4" t="n"/>
       <c r="AI497" s="4" t="n"/>
       <c r="AJ497" s="4" t="n"/>
+      <c r="AK497" s="4" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -19712,6 +20218,7 @@
       <c r="AH498" s="2" t="n"/>
       <c r="AI498" s="2" t="n"/>
       <c r="AJ498" s="2" t="n"/>
+      <c r="AK498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="4" t="n"/>
@@ -19750,6 +20257,7 @@
       <c r="AH499" s="4" t="n"/>
       <c r="AI499" s="4" t="n"/>
       <c r="AJ499" s="4" t="n"/>
+      <c r="AK499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -19788,6 +20296,7 @@
       <c r="AH500" s="2" t="n"/>
       <c r="AI500" s="2" t="n"/>
       <c r="AJ500" s="2" t="n"/>
+      <c r="AK500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="4" t="n"/>
@@ -19826,6 +20335,7 @@
       <c r="AH501" s="4" t="n"/>
       <c r="AI501" s="4" t="n"/>
       <c r="AJ501" s="4" t="n"/>
+      <c r="AK501" s="4" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n"/>
@@ -19864,6 +20374,7 @@
       <c r="AH502" s="2" t="n"/>
       <c r="AI502" s="2" t="n"/>
       <c r="AJ502" s="2" t="n"/>
+      <c r="AK502" s="2" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="4" t="n"/>
@@ -19902,6 +20413,7 @@
       <c r="AH503" s="4" t="n"/>
       <c r="AI503" s="4" t="n"/>
       <c r="AJ503" s="4" t="n"/>
+      <c r="AK503" s="4" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n"/>
@@ -19940,6 +20452,7 @@
       <c r="AH504" s="2" t="n"/>
       <c r="AI504" s="2" t="n"/>
       <c r="AJ504" s="2" t="n"/>
+      <c r="AK504" s="2" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="4" t="n"/>
@@ -19978,6 +20491,7 @@
       <c r="AH505" s="4" t="n"/>
       <c r="AI505" s="4" t="n"/>
       <c r="AJ505" s="4" t="n"/>
+      <c r="AK505" s="4" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n"/>
@@ -20016,6 +20530,7 @@
       <c r="AH506" s="2" t="n"/>
       <c r="AI506" s="2" t="n"/>
       <c r="AJ506" s="2" t="n"/>
+      <c r="AK506" s="2" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="4" t="n"/>
@@ -20054,6 +20569,7 @@
       <c r="AH507" s="4" t="n"/>
       <c r="AI507" s="4" t="n"/>
       <c r="AJ507" s="4" t="n"/>
+      <c r="AK507" s="4" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n"/>
@@ -20092,6 +20608,7 @@
       <c r="AH508" s="2" t="n"/>
       <c r="AI508" s="2" t="n"/>
       <c r="AJ508" s="2" t="n"/>
+      <c r="AK508" s="2" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="4" t="n"/>
@@ -20130,6 +20647,7 @@
       <c r="AH509" s="4" t="n"/>
       <c r="AI509" s="4" t="n"/>
       <c r="AJ509" s="4" t="n"/>
+      <c r="AK509" s="4" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n"/>
@@ -20168,6 +20686,7 @@
       <c r="AH510" s="2" t="n"/>
       <c r="AI510" s="2" t="n"/>
       <c r="AJ510" s="2" t="n"/>
+      <c r="AK510" s="2" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="4" t="n"/>
@@ -20206,6 +20725,7 @@
       <c r="AH511" s="4" t="n"/>
       <c r="AI511" s="4" t="n"/>
       <c r="AJ511" s="4" t="n"/>
+      <c r="AK511" s="4" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n"/>
@@ -20244,6 +20764,7 @@
       <c r="AH512" s="2" t="n"/>
       <c r="AI512" s="2" t="n"/>
       <c r="AJ512" s="2" t="n"/>
+      <c r="AK512" s="2" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="4" t="n"/>
@@ -20282,6 +20803,7 @@
       <c r="AH513" s="4" t="n"/>
       <c r="AI513" s="4" t="n"/>
       <c r="AJ513" s="4" t="n"/>
+      <c r="AK513" s="4" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n"/>
@@ -20320,6 +20842,7 @@
       <c r="AH514" s="2" t="n"/>
       <c r="AI514" s="2" t="n"/>
       <c r="AJ514" s="2" t="n"/>
+      <c r="AK514" s="2" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="4" t="n"/>
@@ -20358,6 +20881,7 @@
       <c r="AH515" s="4" t="n"/>
       <c r="AI515" s="4" t="n"/>
       <c r="AJ515" s="4" t="n"/>
+      <c r="AK515" s="4" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n"/>
@@ -20396,6 +20920,7 @@
       <c r="AH516" s="2" t="n"/>
       <c r="AI516" s="2" t="n"/>
       <c r="AJ516" s="2" t="n"/>
+      <c r="AK516" s="2" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="4" t="n"/>
@@ -20434,6 +20959,7 @@
       <c r="AH517" s="4" t="n"/>
       <c r="AI517" s="4" t="n"/>
       <c r="AJ517" s="4" t="n"/>
+      <c r="AK517" s="4" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n"/>
@@ -20472,6 +20998,7 @@
       <c r="AH518" s="2" t="n"/>
       <c r="AI518" s="2" t="n"/>
       <c r="AJ518" s="2" t="n"/>
+      <c r="AK518" s="2" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="4" t="n"/>
@@ -20510,6 +21037,7 @@
       <c r="AH519" s="4" t="n"/>
       <c r="AI519" s="4" t="n"/>
       <c r="AJ519" s="4" t="n"/>
+      <c r="AK519" s="4" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n"/>
@@ -20548,6 +21076,7 @@
       <c r="AH520" s="2" t="n"/>
       <c r="AI520" s="2" t="n"/>
       <c r="AJ520" s="2" t="n"/>
+      <c r="AK520" s="2" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="4" t="n"/>
@@ -20586,6 +21115,7 @@
       <c r="AH521" s="4" t="n"/>
       <c r="AI521" s="4" t="n"/>
       <c r="AJ521" s="4" t="n"/>
+      <c r="AK521" s="4" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n"/>
@@ -20624,6 +21154,7 @@
       <c r="AH522" s="2" t="n"/>
       <c r="AI522" s="2" t="n"/>
       <c r="AJ522" s="2" t="n"/>
+      <c r="AK522" s="2" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="4" t="n"/>
@@ -20662,6 +21193,7 @@
       <c r="AH523" s="4" t="n"/>
       <c r="AI523" s="4" t="n"/>
       <c r="AJ523" s="4" t="n"/>
+      <c r="AK523" s="4" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n"/>
@@ -20700,6 +21232,7 @@
       <c r="AH524" s="2" t="n"/>
       <c r="AI524" s="2" t="n"/>
       <c r="AJ524" s="2" t="n"/>
+      <c r="AK524" s="2" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="4" t="n"/>
@@ -20738,6 +21271,7 @@
       <c r="AH525" s="4" t="n"/>
       <c r="AI525" s="4" t="n"/>
       <c r="AJ525" s="4" t="n"/>
+      <c r="AK525" s="4" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n"/>
@@ -20776,6 +21310,7 @@
       <c r="AH526" s="2" t="n"/>
       <c r="AI526" s="2" t="n"/>
       <c r="AJ526" s="2" t="n"/>
+      <c r="AK526" s="2" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="4" t="n"/>
@@ -20814,6 +21349,7 @@
       <c r="AH527" s="4" t="n"/>
       <c r="AI527" s="4" t="n"/>
       <c r="AJ527" s="4" t="n"/>
+      <c r="AK527" s="4" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n"/>
@@ -20852,6 +21388,7 @@
       <c r="AH528" s="2" t="n"/>
       <c r="AI528" s="2" t="n"/>
       <c r="AJ528" s="2" t="n"/>
+      <c r="AK528" s="2" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="4" t="n"/>
@@ -20890,6 +21427,7 @@
       <c r="AH529" s="4" t="n"/>
       <c r="AI529" s="4" t="n"/>
       <c r="AJ529" s="4" t="n"/>
+      <c r="AK529" s="4" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n"/>
@@ -20928,6 +21466,7 @@
       <c r="AH530" s="2" t="n"/>
       <c r="AI530" s="2" t="n"/>
       <c r="AJ530" s="2" t="n"/>
+      <c r="AK530" s="2" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="4" t="n"/>
@@ -20966,6 +21505,7 @@
       <c r="AH531" s="4" t="n"/>
       <c r="AI531" s="4" t="n"/>
       <c r="AJ531" s="4" t="n"/>
+      <c r="AK531" s="4" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n"/>
@@ -21004,6 +21544,7 @@
       <c r="AH532" s="2" t="n"/>
       <c r="AI532" s="2" t="n"/>
       <c r="AJ532" s="2" t="n"/>
+      <c r="AK532" s="2" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="4" t="n"/>
@@ -21042,6 +21583,7 @@
       <c r="AH533" s="4" t="n"/>
       <c r="AI533" s="4" t="n"/>
       <c r="AJ533" s="4" t="n"/>
+      <c r="AK533" s="4" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n"/>
@@ -21080,6 +21622,7 @@
       <c r="AH534" s="2" t="n"/>
       <c r="AI534" s="2" t="n"/>
       <c r="AJ534" s="2" t="n"/>
+      <c r="AK534" s="2" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="4" t="n"/>
@@ -21118,6 +21661,7 @@
       <c r="AH535" s="4" t="n"/>
       <c r="AI535" s="4" t="n"/>
       <c r="AJ535" s="4" t="n"/>
+      <c r="AK535" s="4" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n"/>
@@ -21156,6 +21700,7 @@
       <c r="AH536" s="2" t="n"/>
       <c r="AI536" s="2" t="n"/>
       <c r="AJ536" s="2" t="n"/>
+      <c r="AK536" s="2" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="4" t="n"/>
@@ -21194,6 +21739,7 @@
       <c r="AH537" s="4" t="n"/>
       <c r="AI537" s="4" t="n"/>
       <c r="AJ537" s="4" t="n"/>
+      <c r="AK537" s="4" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n"/>
@@ -21232,6 +21778,7 @@
       <c r="AH538" s="2" t="n"/>
       <c r="AI538" s="2" t="n"/>
       <c r="AJ538" s="2" t="n"/>
+      <c r="AK538" s="2" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="4" t="n"/>
@@ -21270,6 +21817,7 @@
       <c r="AH539" s="4" t="n"/>
       <c r="AI539" s="4" t="n"/>
       <c r="AJ539" s="4" t="n"/>
+      <c r="AK539" s="4" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n"/>
@@ -21308,6 +21856,7 @@
       <c r="AH540" s="2" t="n"/>
       <c r="AI540" s="2" t="n"/>
       <c r="AJ540" s="2" t="n"/>
+      <c r="AK540" s="2" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="4" t="n"/>
@@ -21346,6 +21895,7 @@
       <c r="AH541" s="4" t="n"/>
       <c r="AI541" s="4" t="n"/>
       <c r="AJ541" s="4" t="n"/>
+      <c r="AK541" s="4" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n"/>
@@ -21384,6 +21934,7 @@
       <c r="AH542" s="2" t="n"/>
       <c r="AI542" s="2" t="n"/>
       <c r="AJ542" s="2" t="n"/>
+      <c r="AK542" s="2" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="4" t="n"/>
@@ -21422,6 +21973,7 @@
       <c r="AH543" s="4" t="n"/>
       <c r="AI543" s="4" t="n"/>
       <c r="AJ543" s="4" t="n"/>
+      <c r="AK543" s="4" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n"/>
@@ -21460,6 +22012,7 @@
       <c r="AH544" s="2" t="n"/>
       <c r="AI544" s="2" t="n"/>
       <c r="AJ544" s="2" t="n"/>
+      <c r="AK544" s="2" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="4" t="n"/>
@@ -21498,6 +22051,7 @@
       <c r="AH545" s="4" t="n"/>
       <c r="AI545" s="4" t="n"/>
       <c r="AJ545" s="4" t="n"/>
+      <c r="AK545" s="4" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n"/>
@@ -21536,6 +22090,7 @@
       <c r="AH546" s="2" t="n"/>
       <c r="AI546" s="2" t="n"/>
       <c r="AJ546" s="2" t="n"/>
+      <c r="AK546" s="2" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="4" t="n"/>
@@ -21574,6 +22129,7 @@
       <c r="AH547" s="4" t="n"/>
       <c r="AI547" s="4" t="n"/>
       <c r="AJ547" s="4" t="n"/>
+      <c r="AK547" s="4" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n"/>
@@ -21612,6 +22168,7 @@
       <c r="AH548" s="2" t="n"/>
       <c r="AI548" s="2" t="n"/>
       <c r="AJ548" s="2" t="n"/>
+      <c r="AK548" s="2" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="4" t="n"/>
@@ -21650,6 +22207,7 @@
       <c r="AH549" s="4" t="n"/>
       <c r="AI549" s="4" t="n"/>
       <c r="AJ549" s="4" t="n"/>
+      <c r="AK549" s="4" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n"/>
@@ -21688,6 +22246,7 @@
       <c r="AH550" s="2" t="n"/>
       <c r="AI550" s="2" t="n"/>
       <c r="AJ550" s="2" t="n"/>
+      <c r="AK550" s="2" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="4" t="n"/>
@@ -21726,6 +22285,7 @@
       <c r="AH551" s="4" t="n"/>
       <c r="AI551" s="4" t="n"/>
       <c r="AJ551" s="4" t="n"/>
+      <c r="AK551" s="4" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n"/>
@@ -21764,6 +22324,7 @@
       <c r="AH552" s="2" t="n"/>
       <c r="AI552" s="2" t="n"/>
       <c r="AJ552" s="2" t="n"/>
+      <c r="AK552" s="2" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="4" t="n"/>
@@ -21802,6 +22363,7 @@
       <c r="AH553" s="4" t="n"/>
       <c r="AI553" s="4" t="n"/>
       <c r="AJ553" s="4" t="n"/>
+      <c r="AK553" s="4" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n"/>
@@ -21840,6 +22402,7 @@
       <c r="AH554" s="2" t="n"/>
       <c r="AI554" s="2" t="n"/>
       <c r="AJ554" s="2" t="n"/>
+      <c r="AK554" s="2" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="4" t="n"/>
@@ -21878,6 +22441,7 @@
       <c r="AH555" s="4" t="n"/>
       <c r="AI555" s="4" t="n"/>
       <c r="AJ555" s="4" t="n"/>
+      <c r="AK555" s="4" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n"/>
@@ -21916,6 +22480,7 @@
       <c r="AH556" s="2" t="n"/>
       <c r="AI556" s="2" t="n"/>
       <c r="AJ556" s="2" t="n"/>
+      <c r="AK556" s="2" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="4" t="n"/>
@@ -21954,6 +22519,7 @@
       <c r="AH557" s="4" t="n"/>
       <c r="AI557" s="4" t="n"/>
       <c r="AJ557" s="4" t="n"/>
+      <c r="AK557" s="4" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n"/>
@@ -21992,6 +22558,7 @@
       <c r="AH558" s="2" t="n"/>
       <c r="AI558" s="2" t="n"/>
       <c r="AJ558" s="2" t="n"/>
+      <c r="AK558" s="2" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="4" t="n"/>
@@ -22030,6 +22597,7 @@
       <c r="AH559" s="4" t="n"/>
       <c r="AI559" s="4" t="n"/>
       <c r="AJ559" s="4" t="n"/>
+      <c r="AK559" s="4" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n"/>
@@ -22068,6 +22636,7 @@
       <c r="AH560" s="2" t="n"/>
       <c r="AI560" s="2" t="n"/>
       <c r="AJ560" s="2" t="n"/>
+      <c r="AK560" s="2" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="4" t="n"/>
@@ -22106,6 +22675,7 @@
       <c r="AH561" s="4" t="n"/>
       <c r="AI561" s="4" t="n"/>
       <c r="AJ561" s="4" t="n"/>
+      <c r="AK561" s="4" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n"/>
@@ -22144,6 +22714,7 @@
       <c r="AH562" s="2" t="n"/>
       <c r="AI562" s="2" t="n"/>
       <c r="AJ562" s="2" t="n"/>
+      <c r="AK562" s="2" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="4" t="n"/>
@@ -22182,6 +22753,7 @@
       <c r="AH563" s="4" t="n"/>
       <c r="AI563" s="4" t="n"/>
       <c r="AJ563" s="4" t="n"/>
+      <c r="AK563" s="4" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n"/>
@@ -22220,6 +22792,7 @@
       <c r="AH564" s="2" t="n"/>
       <c r="AI564" s="2" t="n"/>
       <c r="AJ564" s="2" t="n"/>
+      <c r="AK564" s="2" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="4" t="n"/>
@@ -22258,6 +22831,7 @@
       <c r="AH565" s="4" t="n"/>
       <c r="AI565" s="4" t="n"/>
       <c r="AJ565" s="4" t="n"/>
+      <c r="AK565" s="4" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n"/>
@@ -22296,6 +22870,7 @@
       <c r="AH566" s="2" t="n"/>
       <c r="AI566" s="2" t="n"/>
       <c r="AJ566" s="2" t="n"/>
+      <c r="AK566" s="2" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="4" t="n"/>
@@ -22334,6 +22909,7 @@
       <c r="AH567" s="4" t="n"/>
       <c r="AI567" s="4" t="n"/>
       <c r="AJ567" s="4" t="n"/>
+      <c r="AK567" s="4" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n"/>
@@ -22372,6 +22948,7 @@
       <c r="AH568" s="2" t="n"/>
       <c r="AI568" s="2" t="n"/>
       <c r="AJ568" s="2" t="n"/>
+      <c r="AK568" s="2" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="4" t="n"/>
@@ -22410,6 +22987,7 @@
       <c r="AH569" s="4" t="n"/>
       <c r="AI569" s="4" t="n"/>
       <c r="AJ569" s="4" t="n"/>
+      <c r="AK569" s="4" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n"/>
@@ -22448,6 +23026,7 @@
       <c r="AH570" s="2" t="n"/>
       <c r="AI570" s="2" t="n"/>
       <c r="AJ570" s="2" t="n"/>
+      <c r="AK570" s="2" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="4" t="n"/>
@@ -22486,6 +23065,7 @@
       <c r="AH571" s="4" t="n"/>
       <c r="AI571" s="4" t="n"/>
       <c r="AJ571" s="4" t="n"/>
+      <c r="AK571" s="4" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n"/>
@@ -22524,6 +23104,7 @@
       <c r="AH572" s="2" t="n"/>
       <c r="AI572" s="2" t="n"/>
       <c r="AJ572" s="2" t="n"/>
+      <c r="AK572" s="2" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="4" t="n"/>
@@ -22562,6 +23143,7 @@
       <c r="AH573" s="4" t="n"/>
       <c r="AI573" s="4" t="n"/>
       <c r="AJ573" s="4" t="n"/>
+      <c r="AK573" s="4" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n"/>
@@ -22600,6 +23182,7 @@
       <c r="AH574" s="2" t="n"/>
       <c r="AI574" s="2" t="n"/>
       <c r="AJ574" s="2" t="n"/>
+      <c r="AK574" s="2" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="4" t="n"/>
@@ -22638,6 +23221,7 @@
       <c r="AH575" s="4" t="n"/>
       <c r="AI575" s="4" t="n"/>
       <c r="AJ575" s="4" t="n"/>
+      <c r="AK575" s="4" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n"/>
@@ -22676,6 +23260,7 @@
       <c r="AH576" s="2" t="n"/>
       <c r="AI576" s="2" t="n"/>
       <c r="AJ576" s="2" t="n"/>
+      <c r="AK576" s="2" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="4" t="n"/>
@@ -22714,6 +23299,7 @@
       <c r="AH577" s="4" t="n"/>
       <c r="AI577" s="4" t="n"/>
       <c r="AJ577" s="4" t="n"/>
+      <c r="AK577" s="4" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n"/>
@@ -22752,6 +23338,7 @@
       <c r="AH578" s="2" t="n"/>
       <c r="AI578" s="2" t="n"/>
       <c r="AJ578" s="2" t="n"/>
+      <c r="AK578" s="2" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="4" t="n"/>
@@ -22790,6 +23377,7 @@
       <c r="AH579" s="4" t="n"/>
       <c r="AI579" s="4" t="n"/>
       <c r="AJ579" s="4" t="n"/>
+      <c r="AK579" s="4" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n"/>
@@ -22828,6 +23416,7 @@
       <c r="AH580" s="2" t="n"/>
       <c r="AI580" s="2" t="n"/>
       <c r="AJ580" s="2" t="n"/>
+      <c r="AK580" s="2" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="4" t="n"/>
@@ -22866,6 +23455,7 @@
       <c r="AH581" s="4" t="n"/>
       <c r="AI581" s="4" t="n"/>
       <c r="AJ581" s="4" t="n"/>
+      <c r="AK581" s="4" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n"/>
@@ -22904,6 +23494,7 @@
       <c r="AH582" s="2" t="n"/>
       <c r="AI582" s="2" t="n"/>
       <c r="AJ582" s="2" t="n"/>
+      <c r="AK582" s="2" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="4" t="n"/>
@@ -22942,6 +23533,7 @@
       <c r="AH583" s="4" t="n"/>
       <c r="AI583" s="4" t="n"/>
       <c r="AJ583" s="4" t="n"/>
+      <c r="AK583" s="4" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n"/>
@@ -22980,6 +23572,7 @@
       <c r="AH584" s="2" t="n"/>
       <c r="AI584" s="2" t="n"/>
       <c r="AJ584" s="2" t="n"/>
+      <c r="AK584" s="2" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="4" t="n"/>
@@ -23018,6 +23611,7 @@
       <c r="AH585" s="4" t="n"/>
       <c r="AI585" s="4" t="n"/>
       <c r="AJ585" s="4" t="n"/>
+      <c r="AK585" s="4" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n"/>
@@ -23056,6 +23650,7 @@
       <c r="AH586" s="2" t="n"/>
       <c r="AI586" s="2" t="n"/>
       <c r="AJ586" s="2" t="n"/>
+      <c r="AK586" s="2" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="4" t="n"/>
@@ -23094,6 +23689,7 @@
       <c r="AH587" s="4" t="n"/>
       <c r="AI587" s="4" t="n"/>
       <c r="AJ587" s="4" t="n"/>
+      <c r="AK587" s="4" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n"/>
@@ -23132,6 +23728,7 @@
       <c r="AH588" s="2" t="n"/>
       <c r="AI588" s="2" t="n"/>
       <c r="AJ588" s="2" t="n"/>
+      <c r="AK588" s="2" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="4" t="n"/>
@@ -23170,6 +23767,7 @@
       <c r="AH589" s="4" t="n"/>
       <c r="AI589" s="4" t="n"/>
       <c r="AJ589" s="4" t="n"/>
+      <c r="AK589" s="4" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n"/>
@@ -23208,6 +23806,7 @@
       <c r="AH590" s="2" t="n"/>
       <c r="AI590" s="2" t="n"/>
       <c r="AJ590" s="2" t="n"/>
+      <c r="AK590" s="2" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="4" t="n"/>
@@ -23246,6 +23845,7 @@
       <c r="AH591" s="4" t="n"/>
       <c r="AI591" s="4" t="n"/>
       <c r="AJ591" s="4" t="n"/>
+      <c r="AK591" s="4" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n"/>
@@ -23284,6 +23884,7 @@
       <c r="AH592" s="2" t="n"/>
       <c r="AI592" s="2" t="n"/>
       <c r="AJ592" s="2" t="n"/>
+      <c r="AK592" s="2" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="4" t="n"/>
@@ -23322,6 +23923,7 @@
       <c r="AH593" s="4" t="n"/>
       <c r="AI593" s="4" t="n"/>
       <c r="AJ593" s="4" t="n"/>
+      <c r="AK593" s="4" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n"/>
@@ -23360,6 +23962,7 @@
       <c r="AH594" s="2" t="n"/>
       <c r="AI594" s="2" t="n"/>
       <c r="AJ594" s="2" t="n"/>
+      <c r="AK594" s="2" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="4" t="n"/>
@@ -23398,6 +24001,7 @@
       <c r="AH595" s="4" t="n"/>
       <c r="AI595" s="4" t="n"/>
       <c r="AJ595" s="4" t="n"/>
+      <c r="AK595" s="4" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n"/>
@@ -23436,6 +24040,7 @@
       <c r="AH596" s="2" t="n"/>
       <c r="AI596" s="2" t="n"/>
       <c r="AJ596" s="2" t="n"/>
+      <c r="AK596" s="2" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="4" t="n"/>
@@ -23474,6 +24079,7 @@
       <c r="AH597" s="4" t="n"/>
       <c r="AI597" s="4" t="n"/>
       <c r="AJ597" s="4" t="n"/>
+      <c r="AK597" s="4" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n"/>
@@ -23512,6 +24118,7 @@
       <c r="AH598" s="2" t="n"/>
       <c r="AI598" s="2" t="n"/>
       <c r="AJ598" s="2" t="n"/>
+      <c r="AK598" s="2" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="4" t="n"/>
@@ -23550,6 +24157,7 @@
       <c r="AH599" s="4" t="n"/>
       <c r="AI599" s="4" t="n"/>
       <c r="AJ599" s="4" t="n"/>
+      <c r="AK599" s="4" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n"/>
@@ -23588,6 +24196,7 @@
       <c r="AH600" s="2" t="n"/>
       <c r="AI600" s="2" t="n"/>
       <c r="AJ600" s="2" t="n"/>
+      <c r="AK600" s="2" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="4" t="n"/>
@@ -23626,6 +24235,7 @@
       <c r="AH601" s="4" t="n"/>
       <c r="AI601" s="4" t="n"/>
       <c r="AJ601" s="4" t="n"/>
+      <c r="AK601" s="4" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n"/>
@@ -23664,6 +24274,7 @@
       <c r="AH602" s="2" t="n"/>
       <c r="AI602" s="2" t="n"/>
       <c r="AJ602" s="2" t="n"/>
+      <c r="AK602" s="2" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="4" t="n"/>
@@ -23702,6 +24313,7 @@
       <c r="AH603" s="4" t="n"/>
       <c r="AI603" s="4" t="n"/>
       <c r="AJ603" s="4" t="n"/>
+      <c r="AK603" s="4" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n"/>
@@ -23740,6 +24352,7 @@
       <c r="AH604" s="2" t="n"/>
       <c r="AI604" s="2" t="n"/>
       <c r="AJ604" s="2" t="n"/>
+      <c r="AK604" s="2" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="4" t="n"/>
@@ -23778,6 +24391,7 @@
       <c r="AH605" s="4" t="n"/>
       <c r="AI605" s="4" t="n"/>
       <c r="AJ605" s="4" t="n"/>
+      <c r="AK605" s="4" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n"/>
@@ -23816,6 +24430,7 @@
       <c r="AH606" s="2" t="n"/>
       <c r="AI606" s="2" t="n"/>
       <c r="AJ606" s="2" t="n"/>
+      <c r="AK606" s="2" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="4" t="n"/>
@@ -23854,6 +24469,7 @@
       <c r="AH607" s="4" t="n"/>
       <c r="AI607" s="4" t="n"/>
       <c r="AJ607" s="4" t="n"/>
+      <c r="AK607" s="4" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n"/>
@@ -23892,6 +24508,7 @@
       <c r="AH608" s="2" t="n"/>
       <c r="AI608" s="2" t="n"/>
       <c r="AJ608" s="2" t="n"/>
+      <c r="AK608" s="2" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="4" t="n"/>
@@ -23930,6 +24547,7 @@
       <c r="AH609" s="4" t="n"/>
       <c r="AI609" s="4" t="n"/>
       <c r="AJ609" s="4" t="n"/>
+      <c r="AK609" s="4" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n"/>
@@ -23968,6 +24586,7 @@
       <c r="AH610" s="2" t="n"/>
       <c r="AI610" s="2" t="n"/>
       <c r="AJ610" s="2" t="n"/>
+      <c r="AK610" s="2" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="4" t="n"/>
@@ -24006,6 +24625,7 @@
       <c r="AH611" s="4" t="n"/>
       <c r="AI611" s="4" t="n"/>
       <c r="AJ611" s="4" t="n"/>
+      <c r="AK611" s="4" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n"/>
@@ -24044,6 +24664,7 @@
       <c r="AH612" s="2" t="n"/>
       <c r="AI612" s="2" t="n"/>
       <c r="AJ612" s="2" t="n"/>
+      <c r="AK612" s="2" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="4" t="n"/>
@@ -24082,6 +24703,7 @@
       <c r="AH613" s="4" t="n"/>
       <c r="AI613" s="4" t="n"/>
       <c r="AJ613" s="4" t="n"/>
+      <c r="AK613" s="4" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n"/>
@@ -24120,6 +24742,7 @@
       <c r="AH614" s="2" t="n"/>
       <c r="AI614" s="2" t="n"/>
       <c r="AJ614" s="2" t="n"/>
+      <c r="AK614" s="2" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="4" t="n"/>
@@ -24158,6 +24781,7 @@
       <c r="AH615" s="4" t="n"/>
       <c r="AI615" s="4" t="n"/>
       <c r="AJ615" s="4" t="n"/>
+      <c r="AK615" s="4" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n"/>
@@ -24196,6 +24820,7 @@
       <c r="AH616" s="2" t="n"/>
       <c r="AI616" s="2" t="n"/>
       <c r="AJ616" s="2" t="n"/>
+      <c r="AK616" s="2" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="4" t="n"/>
@@ -24234,6 +24859,7 @@
       <c r="AH617" s="4" t="n"/>
       <c r="AI617" s="4" t="n"/>
       <c r="AJ617" s="4" t="n"/>
+      <c r="AK617" s="4" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n"/>
@@ -24272,6 +24898,7 @@
       <c r="AH618" s="2" t="n"/>
       <c r="AI618" s="2" t="n"/>
       <c r="AJ618" s="2" t="n"/>
+      <c r="AK618" s="2" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="4" t="n"/>
@@ -24310,6 +24937,7 @@
       <c r="AH619" s="4" t="n"/>
       <c r="AI619" s="4" t="n"/>
       <c r="AJ619" s="4" t="n"/>
+      <c r="AK619" s="4" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n"/>
@@ -24348,6 +24976,7 @@
       <c r="AH620" s="2" t="n"/>
       <c r="AI620" s="2" t="n"/>
       <c r="AJ620" s="2" t="n"/>
+      <c r="AK620" s="2" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="4" t="n"/>
@@ -24386,6 +25015,7 @@
       <c r="AH621" s="4" t="n"/>
       <c r="AI621" s="4" t="n"/>
       <c r="AJ621" s="4" t="n"/>
+      <c r="AK621" s="4" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n"/>
@@ -24424,6 +25054,7 @@
       <c r="AH622" s="2" t="n"/>
       <c r="AI622" s="2" t="n"/>
       <c r="AJ622" s="2" t="n"/>
+      <c r="AK622" s="2" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="4" t="n"/>
@@ -24462,6 +25093,7 @@
       <c r="AH623" s="4" t="n"/>
       <c r="AI623" s="4" t="n"/>
       <c r="AJ623" s="4" t="n"/>
+      <c r="AK623" s="4" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n"/>
@@ -24500,6 +25132,7 @@
       <c r="AH624" s="2" t="n"/>
       <c r="AI624" s="2" t="n"/>
       <c r="AJ624" s="2" t="n"/>
+      <c r="AK624" s="2" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="4" t="n"/>
@@ -24538,6 +25171,7 @@
       <c r="AH625" s="4" t="n"/>
       <c r="AI625" s="4" t="n"/>
       <c r="AJ625" s="4" t="n"/>
+      <c r="AK625" s="4" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n"/>
@@ -24576,6 +25210,7 @@
       <c r="AH626" s="2" t="n"/>
       <c r="AI626" s="2" t="n"/>
       <c r="AJ626" s="2" t="n"/>
+      <c r="AK626" s="2" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="4" t="n"/>
@@ -24614,6 +25249,7 @@
       <c r="AH627" s="4" t="n"/>
       <c r="AI627" s="4" t="n"/>
       <c r="AJ627" s="4" t="n"/>
+      <c r="AK627" s="4" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n"/>
@@ -24652,6 +25288,7 @@
       <c r="AH628" s="2" t="n"/>
       <c r="AI628" s="2" t="n"/>
       <c r="AJ628" s="2" t="n"/>
+      <c r="AK628" s="2" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="4" t="n"/>
@@ -24690,6 +25327,7 @@
       <c r="AH629" s="4" t="n"/>
       <c r="AI629" s="4" t="n"/>
       <c r="AJ629" s="4" t="n"/>
+      <c r="AK629" s="4" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n"/>
@@ -24728,6 +25366,7 @@
       <c r="AH630" s="2" t="n"/>
       <c r="AI630" s="2" t="n"/>
       <c r="AJ630" s="2" t="n"/>
+      <c r="AK630" s="2" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="4" t="n"/>
@@ -24766,6 +25405,7 @@
       <c r="AH631" s="4" t="n"/>
       <c r="AI631" s="4" t="n"/>
       <c r="AJ631" s="4" t="n"/>
+      <c r="AK631" s="4" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n"/>
@@ -24804,6 +25444,7 @@
       <c r="AH632" s="2" t="n"/>
       <c r="AI632" s="2" t="n"/>
       <c r="AJ632" s="2" t="n"/>
+      <c r="AK632" s="2" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="4" t="n"/>
@@ -24842,6 +25483,7 @@
       <c r="AH633" s="4" t="n"/>
       <c r="AI633" s="4" t="n"/>
       <c r="AJ633" s="4" t="n"/>
+      <c r="AK633" s="4" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n"/>
@@ -24880,6 +25522,7 @@
       <c r="AH634" s="2" t="n"/>
       <c r="AI634" s="2" t="n"/>
       <c r="AJ634" s="2" t="n"/>
+      <c r="AK634" s="2" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="4" t="n"/>
@@ -24918,6 +25561,7 @@
       <c r="AH635" s="4" t="n"/>
       <c r="AI635" s="4" t="n"/>
       <c r="AJ635" s="4" t="n"/>
+      <c r="AK635" s="4" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n"/>
@@ -24956,6 +25600,7 @@
       <c r="AH636" s="2" t="n"/>
       <c r="AI636" s="2" t="n"/>
       <c r="AJ636" s="2" t="n"/>
+      <c r="AK636" s="2" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="4" t="n"/>
@@ -24994,6 +25639,7 @@
       <c r="AH637" s="4" t="n"/>
       <c r="AI637" s="4" t="n"/>
       <c r="AJ637" s="4" t="n"/>
+      <c r="AK637" s="4" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n"/>
@@ -25032,6 +25678,7 @@
       <c r="AH638" s="2" t="n"/>
       <c r="AI638" s="2" t="n"/>
       <c r="AJ638" s="2" t="n"/>
+      <c r="AK638" s="2" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="4" t="n"/>
@@ -25070,6 +25717,7 @@
       <c r="AH639" s="4" t="n"/>
       <c r="AI639" s="4" t="n"/>
       <c r="AJ639" s="4" t="n"/>
+      <c r="AK639" s="4" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n"/>
@@ -25108,6 +25756,7 @@
       <c r="AH640" s="2" t="n"/>
       <c r="AI640" s="2" t="n"/>
       <c r="AJ640" s="2" t="n"/>
+      <c r="AK640" s="2" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="4" t="n"/>
@@ -25146,6 +25795,7 @@
       <c r="AH641" s="4" t="n"/>
       <c r="AI641" s="4" t="n"/>
       <c r="AJ641" s="4" t="n"/>
+      <c r="AK641" s="4" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n"/>
@@ -25184,6 +25834,7 @@
       <c r="AH642" s="2" t="n"/>
       <c r="AI642" s="2" t="n"/>
       <c r="AJ642" s="2" t="n"/>
+      <c r="AK642" s="2" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="4" t="n"/>
@@ -25222,6 +25873,7 @@
       <c r="AH643" s="4" t="n"/>
       <c r="AI643" s="4" t="n"/>
       <c r="AJ643" s="4" t="n"/>
+      <c r="AK643" s="4" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n"/>
@@ -25260,6 +25912,7 @@
       <c r="AH644" s="2" t="n"/>
       <c r="AI644" s="2" t="n"/>
       <c r="AJ644" s="2" t="n"/>
+      <c r="AK644" s="2" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="4" t="n"/>
@@ -25298,6 +25951,7 @@
       <c r="AH645" s="4" t="n"/>
       <c r="AI645" s="4" t="n"/>
       <c r="AJ645" s="4" t="n"/>
+      <c r="AK645" s="4" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n"/>
@@ -25336,6 +25990,7 @@
       <c r="AH646" s="2" t="n"/>
       <c r="AI646" s="2" t="n"/>
       <c r="AJ646" s="2" t="n"/>
+      <c r="AK646" s="2" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="4" t="n"/>
@@ -25374,6 +26029,7 @@
       <c r="AH647" s="4" t="n"/>
       <c r="AI647" s="4" t="n"/>
       <c r="AJ647" s="4" t="n"/>
+      <c r="AK647" s="4" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n"/>
@@ -25412,6 +26068,7 @@
       <c r="AH648" s="2" t="n"/>
       <c r="AI648" s="2" t="n"/>
       <c r="AJ648" s="2" t="n"/>
+      <c r="AK648" s="2" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="4" t="n"/>
@@ -25450,6 +26107,7 @@
       <c r="AH649" s="4" t="n"/>
       <c r="AI649" s="4" t="n"/>
       <c r="AJ649" s="4" t="n"/>
+      <c r="AK649" s="4" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n"/>
@@ -25488,6 +26146,7 @@
       <c r="AH650" s="2" t="n"/>
       <c r="AI650" s="2" t="n"/>
       <c r="AJ650" s="2" t="n"/>
+      <c r="AK650" s="2" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="4" t="n"/>
@@ -25526,6 +26185,7 @@
       <c r="AH651" s="4" t="n"/>
       <c r="AI651" s="4" t="n"/>
       <c r="AJ651" s="4" t="n"/>
+      <c r="AK651" s="4" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n"/>
@@ -25564,6 +26224,7 @@
       <c r="AH652" s="2" t="n"/>
       <c r="AI652" s="2" t="n"/>
       <c r="AJ652" s="2" t="n"/>
+      <c r="AK652" s="2" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="4" t="n"/>
@@ -25602,6 +26263,7 @@
       <c r="AH653" s="4" t="n"/>
       <c r="AI653" s="4" t="n"/>
       <c r="AJ653" s="4" t="n"/>
+      <c r="AK653" s="4" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n"/>
@@ -25640,6 +26302,7 @@
       <c r="AH654" s="2" t="n"/>
       <c r="AI654" s="2" t="n"/>
       <c r="AJ654" s="2" t="n"/>
+      <c r="AK654" s="2" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="4" t="n"/>
@@ -25678,6 +26341,7 @@
       <c r="AH655" s="4" t="n"/>
       <c r="AI655" s="4" t="n"/>
       <c r="AJ655" s="4" t="n"/>
+      <c r="AK655" s="4" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n"/>
@@ -25716,6 +26380,7 @@
       <c r="AH656" s="2" t="n"/>
       <c r="AI656" s="2" t="n"/>
       <c r="AJ656" s="2" t="n"/>
+      <c r="AK656" s="2" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="4" t="n"/>
@@ -25754,6 +26419,7 @@
       <c r="AH657" s="4" t="n"/>
       <c r="AI657" s="4" t="n"/>
       <c r="AJ657" s="4" t="n"/>
+      <c r="AK657" s="4" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n"/>
@@ -25792,6 +26458,7 @@
       <c r="AH658" s="2" t="n"/>
       <c r="AI658" s="2" t="n"/>
       <c r="AJ658" s="2" t="n"/>
+      <c r="AK658" s="2" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="4" t="n"/>
@@ -25830,6 +26497,7 @@
       <c r="AH659" s="4" t="n"/>
       <c r="AI659" s="4" t="n"/>
       <c r="AJ659" s="4" t="n"/>
+      <c r="AK659" s="4" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n"/>
@@ -25868,6 +26536,7 @@
       <c r="AH660" s="2" t="n"/>
       <c r="AI660" s="2" t="n"/>
       <c r="AJ660" s="2" t="n"/>
+      <c r="AK660" s="2" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="4" t="n"/>
@@ -25906,6 +26575,7 @@
       <c r="AH661" s="4" t="n"/>
       <c r="AI661" s="4" t="n"/>
       <c r="AJ661" s="4" t="n"/>
+      <c r="AK661" s="4" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n"/>
@@ -25944,6 +26614,7 @@
       <c r="AH662" s="2" t="n"/>
       <c r="AI662" s="2" t="n"/>
       <c r="AJ662" s="2" t="n"/>
+      <c r="AK662" s="2" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="4" t="n"/>
@@ -25982,6 +26653,7 @@
       <c r="AH663" s="4" t="n"/>
       <c r="AI663" s="4" t="n"/>
       <c r="AJ663" s="4" t="n"/>
+      <c r="AK663" s="4" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n"/>
@@ -26020,6 +26692,7 @@
       <c r="AH664" s="2" t="n"/>
       <c r="AI664" s="2" t="n"/>
       <c r="AJ664" s="2" t="n"/>
+      <c r="AK664" s="2" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="4" t="n"/>
@@ -26058,6 +26731,7 @@
       <c r="AH665" s="4" t="n"/>
       <c r="AI665" s="4" t="n"/>
       <c r="AJ665" s="4" t="n"/>
+      <c r="AK665" s="4" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n"/>
@@ -26096,6 +26770,7 @@
       <c r="AH666" s="2" t="n"/>
       <c r="AI666" s="2" t="n"/>
       <c r="AJ666" s="2" t="n"/>
+      <c r="AK666" s="2" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="4" t="n"/>
@@ -26134,6 +26809,7 @@
       <c r="AH667" s="4" t="n"/>
       <c r="AI667" s="4" t="n"/>
       <c r="AJ667" s="4" t="n"/>
+      <c r="AK667" s="4" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n"/>
@@ -26172,6 +26848,7 @@
       <c r="AH668" s="2" t="n"/>
       <c r="AI668" s="2" t="n"/>
       <c r="AJ668" s="2" t="n"/>
+      <c r="AK668" s="2" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="4" t="n"/>
@@ -26210,6 +26887,7 @@
       <c r="AH669" s="4" t="n"/>
       <c r="AI669" s="4" t="n"/>
       <c r="AJ669" s="4" t="n"/>
+      <c r="AK669" s="4" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n"/>
@@ -26248,6 +26926,7 @@
       <c r="AH670" s="2" t="n"/>
       <c r="AI670" s="2" t="n"/>
       <c r="AJ670" s="2" t="n"/>
+      <c r="AK670" s="2" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="4" t="n"/>
@@ -26286,6 +26965,7 @@
       <c r="AH671" s="4" t="n"/>
       <c r="AI671" s="4" t="n"/>
       <c r="AJ671" s="4" t="n"/>
+      <c r="AK671" s="4" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n"/>
@@ -26324,6 +27004,7 @@
       <c r="AH672" s="2" t="n"/>
       <c r="AI672" s="2" t="n"/>
       <c r="AJ672" s="2" t="n"/>
+      <c r="AK672" s="2" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="4" t="n"/>
@@ -26362,6 +27043,7 @@
       <c r="AH673" s="4" t="n"/>
       <c r="AI673" s="4" t="n"/>
       <c r="AJ673" s="4" t="n"/>
+      <c r="AK673" s="4" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n"/>
@@ -26400,6 +27082,7 @@
       <c r="AH674" s="2" t="n"/>
       <c r="AI674" s="2" t="n"/>
       <c r="AJ674" s="2" t="n"/>
+      <c r="AK674" s="2" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="4" t="n"/>
@@ -26438,6 +27121,7 @@
       <c r="AH675" s="4" t="n"/>
       <c r="AI675" s="4" t="n"/>
       <c r="AJ675" s="4" t="n"/>
+      <c r="AK675" s="4" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n"/>
@@ -26476,6 +27160,7 @@
       <c r="AH676" s="2" t="n"/>
       <c r="AI676" s="2" t="n"/>
       <c r="AJ676" s="2" t="n"/>
+      <c r="AK676" s="2" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="4" t="n"/>
@@ -26514,6 +27199,7 @@
       <c r="AH677" s="4" t="n"/>
       <c r="AI677" s="4" t="n"/>
       <c r="AJ677" s="4" t="n"/>
+      <c r="AK677" s="4" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n"/>
@@ -26552,6 +27238,7 @@
       <c r="AH678" s="2" t="n"/>
       <c r="AI678" s="2" t="n"/>
       <c r="AJ678" s="2" t="n"/>
+      <c r="AK678" s="2" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="4" t="n"/>
@@ -26590,6 +27277,7 @@
       <c r="AH679" s="4" t="n"/>
       <c r="AI679" s="4" t="n"/>
       <c r="AJ679" s="4" t="n"/>
+      <c r="AK679" s="4" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n"/>
@@ -26628,6 +27316,7 @@
       <c r="AH680" s="2" t="n"/>
       <c r="AI680" s="2" t="n"/>
       <c r="AJ680" s="2" t="n"/>
+      <c r="AK680" s="2" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="4" t="n"/>
@@ -26666,6 +27355,7 @@
       <c r="AH681" s="4" t="n"/>
       <c r="AI681" s="4" t="n"/>
       <c r="AJ681" s="4" t="n"/>
+      <c r="AK681" s="4" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n"/>
@@ -26704,6 +27394,7 @@
       <c r="AH682" s="2" t="n"/>
       <c r="AI682" s="2" t="n"/>
       <c r="AJ682" s="2" t="n"/>
+      <c r="AK682" s="2" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="4" t="n"/>
@@ -26742,6 +27433,7 @@
       <c r="AH683" s="4" t="n"/>
       <c r="AI683" s="4" t="n"/>
       <c r="AJ683" s="4" t="n"/>
+      <c r="AK683" s="4" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n"/>
@@ -26780,6 +27472,7 @@
       <c r="AH684" s="2" t="n"/>
       <c r="AI684" s="2" t="n"/>
       <c r="AJ684" s="2" t="n"/>
+      <c r="AK684" s="2" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="4" t="n"/>
@@ -26818,6 +27511,7 @@
       <c r="AH685" s="4" t="n"/>
       <c r="AI685" s="4" t="n"/>
       <c r="AJ685" s="4" t="n"/>
+      <c r="AK685" s="4" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n"/>
@@ -26856,6 +27550,7 @@
       <c r="AH686" s="2" t="n"/>
       <c r="AI686" s="2" t="n"/>
       <c r="AJ686" s="2" t="n"/>
+      <c r="AK686" s="2" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="4" t="n"/>
@@ -26894,6 +27589,7 @@
       <c r="AH687" s="4" t="n"/>
       <c r="AI687" s="4" t="n"/>
       <c r="AJ687" s="4" t="n"/>
+      <c r="AK687" s="4" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n"/>
@@ -26932,6 +27628,7 @@
       <c r="AH688" s="2" t="n"/>
       <c r="AI688" s="2" t="n"/>
       <c r="AJ688" s="2" t="n"/>
+      <c r="AK688" s="2" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="4" t="n"/>
@@ -26970,6 +27667,7 @@
       <c r="AH689" s="4" t="n"/>
       <c r="AI689" s="4" t="n"/>
       <c r="AJ689" s="4" t="n"/>
+      <c r="AK689" s="4" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n"/>
@@ -27008,6 +27706,7 @@
       <c r="AH690" s="2" t="n"/>
       <c r="AI690" s="2" t="n"/>
       <c r="AJ690" s="2" t="n"/>
+      <c r="AK690" s="2" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="4" t="n"/>
@@ -27046,6 +27745,7 @@
       <c r="AH691" s="4" t="n"/>
       <c r="AI691" s="4" t="n"/>
       <c r="AJ691" s="4" t="n"/>
+      <c r="AK691" s="4" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n"/>
@@ -27084,6 +27784,7 @@
       <c r="AH692" s="2" t="n"/>
       <c r="AI692" s="2" t="n"/>
       <c r="AJ692" s="2" t="n"/>
+      <c r="AK692" s="2" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="4" t="n"/>
@@ -27122,6 +27823,7 @@
       <c r="AH693" s="4" t="n"/>
       <c r="AI693" s="4" t="n"/>
       <c r="AJ693" s="4" t="n"/>
+      <c r="AK693" s="4" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n"/>
@@ -27160,6 +27862,7 @@
       <c r="AH694" s="2" t="n"/>
       <c r="AI694" s="2" t="n"/>
       <c r="AJ694" s="2" t="n"/>
+      <c r="AK694" s="2" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="4" t="n"/>
@@ -27198,6 +27901,7 @@
       <c r="AH695" s="4" t="n"/>
       <c r="AI695" s="4" t="n"/>
       <c r="AJ695" s="4" t="n"/>
+      <c r="AK695" s="4" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n"/>
@@ -27236,6 +27940,7 @@
       <c r="AH696" s="2" t="n"/>
       <c r="AI696" s="2" t="n"/>
       <c r="AJ696" s="2" t="n"/>
+      <c r="AK696" s="2" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="4" t="n"/>
@@ -27274,6 +27979,7 @@
       <c r="AH697" s="4" t="n"/>
       <c r="AI697" s="4" t="n"/>
       <c r="AJ697" s="4" t="n"/>
+      <c r="AK697" s="4" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n"/>
@@ -27312,6 +28018,7 @@
       <c r="AH698" s="2" t="n"/>
       <c r="AI698" s="2" t="n"/>
       <c r="AJ698" s="2" t="n"/>
+      <c r="AK698" s="2" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="4" t="n"/>
@@ -27350,6 +28057,7 @@
       <c r="AH699" s="4" t="n"/>
       <c r="AI699" s="4" t="n"/>
       <c r="AJ699" s="4" t="n"/>
+      <c r="AK699" s="4" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n"/>
@@ -27388,6 +28096,7 @@
       <c r="AH700" s="2" t="n"/>
       <c r="AI700" s="2" t="n"/>
       <c r="AJ700" s="2" t="n"/>
+      <c r="AK700" s="2" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="4" t="n"/>
@@ -27426,6 +28135,7 @@
       <c r="AH701" s="4" t="n"/>
       <c r="AI701" s="4" t="n"/>
       <c r="AJ701" s="4" t="n"/>
+      <c r="AK701" s="4" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n"/>
@@ -27464,6 +28174,7 @@
       <c r="AH702" s="2" t="n"/>
       <c r="AI702" s="2" t="n"/>
       <c r="AJ702" s="2" t="n"/>
+      <c r="AK702" s="2" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="4" t="n"/>
@@ -27502,6 +28213,7 @@
       <c r="AH703" s="4" t="n"/>
       <c r="AI703" s="4" t="n"/>
       <c r="AJ703" s="4" t="n"/>
+      <c r="AK703" s="4" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n"/>
@@ -27540,6 +28252,7 @@
       <c r="AH704" s="2" t="n"/>
       <c r="AI704" s="2" t="n"/>
       <c r="AJ704" s="2" t="n"/>
+      <c r="AK704" s="2" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="4" t="n"/>
@@ -27578,6 +28291,7 @@
       <c r="AH705" s="4" t="n"/>
       <c r="AI705" s="4" t="n"/>
       <c r="AJ705" s="4" t="n"/>
+      <c r="AK705" s="4" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n"/>
@@ -27616,6 +28330,7 @@
       <c r="AH706" s="2" t="n"/>
       <c r="AI706" s="2" t="n"/>
       <c r="AJ706" s="2" t="n"/>
+      <c r="AK706" s="2" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="4" t="n"/>
@@ -27654,6 +28369,7 @@
       <c r="AH707" s="4" t="n"/>
       <c r="AI707" s="4" t="n"/>
       <c r="AJ707" s="4" t="n"/>
+      <c r="AK707" s="4" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n"/>
@@ -27692,6 +28408,7 @@
       <c r="AH708" s="2" t="n"/>
       <c r="AI708" s="2" t="n"/>
       <c r="AJ708" s="2" t="n"/>
+      <c r="AK708" s="2" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="4" t="n"/>
@@ -27730,6 +28447,7 @@
       <c r="AH709" s="4" t="n"/>
       <c r="AI709" s="4" t="n"/>
       <c r="AJ709" s="4" t="n"/>
+      <c r="AK709" s="4" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n"/>
@@ -27768,6 +28486,7 @@
       <c r="AH710" s="2" t="n"/>
       <c r="AI710" s="2" t="n"/>
       <c r="AJ710" s="2" t="n"/>
+      <c r="AK710" s="2" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="4" t="n"/>
@@ -27806,6 +28525,7 @@
       <c r="AH711" s="4" t="n"/>
       <c r="AI711" s="4" t="n"/>
       <c r="AJ711" s="4" t="n"/>
+      <c r="AK711" s="4" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n"/>
@@ -27844,6 +28564,7 @@
       <c r="AH712" s="2" t="n"/>
       <c r="AI712" s="2" t="n"/>
       <c r="AJ712" s="2" t="n"/>
+      <c r="AK712" s="2" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="4" t="n"/>
@@ -27882,6 +28603,7 @@
       <c r="AH713" s="4" t="n"/>
       <c r="AI713" s="4" t="n"/>
       <c r="AJ713" s="4" t="n"/>
+      <c r="AK713" s="4" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n"/>
@@ -27920,6 +28642,7 @@
       <c r="AH714" s="2" t="n"/>
       <c r="AI714" s="2" t="n"/>
       <c r="AJ714" s="2" t="n"/>
+      <c r="AK714" s="2" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="4" t="n"/>
@@ -27958,6 +28681,7 @@
       <c r="AH715" s="4" t="n"/>
       <c r="AI715" s="4" t="n"/>
       <c r="AJ715" s="4" t="n"/>
+      <c r="AK715" s="4" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n"/>
@@ -27996,6 +28720,7 @@
       <c r="AH716" s="2" t="n"/>
       <c r="AI716" s="2" t="n"/>
       <c r="AJ716" s="2" t="n"/>
+      <c r="AK716" s="2" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="4" t="n"/>
@@ -28034,6 +28759,7 @@
       <c r="AH717" s="4" t="n"/>
       <c r="AI717" s="4" t="n"/>
       <c r="AJ717" s="4" t="n"/>
+      <c r="AK717" s="4" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n"/>
@@ -28072,6 +28798,7 @@
       <c r="AH718" s="2" t="n"/>
       <c r="AI718" s="2" t="n"/>
       <c r="AJ718" s="2" t="n"/>
+      <c r="AK718" s="2" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="4" t="n"/>
@@ -28110,6 +28837,7 @@
       <c r="AH719" s="4" t="n"/>
       <c r="AI719" s="4" t="n"/>
       <c r="AJ719" s="4" t="n"/>
+      <c r="AK719" s="4" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n"/>
@@ -28148,6 +28876,7 @@
       <c r="AH720" s="2" t="n"/>
       <c r="AI720" s="2" t="n"/>
       <c r="AJ720" s="2" t="n"/>
+      <c r="AK720" s="2" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="4" t="n"/>
@@ -28186,6 +28915,7 @@
       <c r="AH721" s="4" t="n"/>
       <c r="AI721" s="4" t="n"/>
       <c r="AJ721" s="4" t="n"/>
+      <c r="AK721" s="4" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n"/>
@@ -28224,6 +28954,7 @@
       <c r="AH722" s="2" t="n"/>
       <c r="AI722" s="2" t="n"/>
       <c r="AJ722" s="2" t="n"/>
+      <c r="AK722" s="2" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="4" t="n"/>
@@ -28262,6 +28993,7 @@
       <c r="AH723" s="4" t="n"/>
       <c r="AI723" s="4" t="n"/>
       <c r="AJ723" s="4" t="n"/>
+      <c r="AK723" s="4" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n"/>
@@ -28300,6 +29032,7 @@
       <c r="AH724" s="2" t="n"/>
       <c r="AI724" s="2" t="n"/>
       <c r="AJ724" s="2" t="n"/>
+      <c r="AK724" s="2" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="4" t="n"/>
@@ -28338,6 +29071,7 @@
       <c r="AH725" s="4" t="n"/>
       <c r="AI725" s="4" t="n"/>
       <c r="AJ725" s="4" t="n"/>
+      <c r="AK725" s="4" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n"/>
@@ -28376,6 +29110,7 @@
       <c r="AH726" s="2" t="n"/>
       <c r="AI726" s="2" t="n"/>
       <c r="AJ726" s="2" t="n"/>
+      <c r="AK726" s="2" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="4" t="n"/>
@@ -28414,6 +29149,7 @@
       <c r="AH727" s="4" t="n"/>
       <c r="AI727" s="4" t="n"/>
       <c r="AJ727" s="4" t="n"/>
+      <c r="AK727" s="4" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n"/>
@@ -28452,6 +29188,7 @@
       <c r="AH728" s="2" t="n"/>
       <c r="AI728" s="2" t="n"/>
       <c r="AJ728" s="2" t="n"/>
+      <c r="AK728" s="2" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="4" t="n"/>
@@ -28490,6 +29227,7 @@
       <c r="AH729" s="4" t="n"/>
       <c r="AI729" s="4" t="n"/>
       <c r="AJ729" s="4" t="n"/>
+      <c r="AK729" s="4" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n"/>
@@ -28528,6 +29266,7 @@
       <c r="AH730" s="2" t="n"/>
       <c r="AI730" s="2" t="n"/>
       <c r="AJ730" s="2" t="n"/>
+      <c r="AK730" s="2" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="4" t="n"/>
@@ -28566,6 +29305,7 @@
       <c r="AH731" s="4" t="n"/>
       <c r="AI731" s="4" t="n"/>
       <c r="AJ731" s="4" t="n"/>
+      <c r="AK731" s="4" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n"/>
@@ -28604,6 +29344,7 @@
       <c r="AH732" s="2" t="n"/>
       <c r="AI732" s="2" t="n"/>
       <c r="AJ732" s="2" t="n"/>
+      <c r="AK732" s="2" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="4" t="n"/>
@@ -28642,6 +29383,7 @@
       <c r="AH733" s="4" t="n"/>
       <c r="AI733" s="4" t="n"/>
       <c r="AJ733" s="4" t="n"/>
+      <c r="AK733" s="4" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n"/>
@@ -28680,6 +29422,7 @@
       <c r="AH734" s="2" t="n"/>
       <c r="AI734" s="2" t="n"/>
       <c r="AJ734" s="2" t="n"/>
+      <c r="AK734" s="2" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="4" t="n"/>
@@ -28718,6 +29461,7 @@
       <c r="AH735" s="4" t="n"/>
       <c r="AI735" s="4" t="n"/>
       <c r="AJ735" s="4" t="n"/>
+      <c r="AK735" s="4" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n"/>
@@ -28756,6 +29500,7 @@
       <c r="AH736" s="2" t="n"/>
       <c r="AI736" s="2" t="n"/>
       <c r="AJ736" s="2" t="n"/>
+      <c r="AK736" s="2" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="4" t="n"/>
@@ -28794,6 +29539,7 @@
       <c r="AH737" s="4" t="n"/>
       <c r="AI737" s="4" t="n"/>
       <c r="AJ737" s="4" t="n"/>
+      <c r="AK737" s="4" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n"/>
@@ -28832,6 +29578,7 @@
       <c r="AH738" s="2" t="n"/>
       <c r="AI738" s="2" t="n"/>
       <c r="AJ738" s="2" t="n"/>
+      <c r="AK738" s="2" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="4" t="n"/>
@@ -28870,6 +29617,7 @@
       <c r="AH739" s="4" t="n"/>
       <c r="AI739" s="4" t="n"/>
       <c r="AJ739" s="4" t="n"/>
+      <c r="AK739" s="4" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n"/>
@@ -28908,6 +29656,7 @@
       <c r="AH740" s="2" t="n"/>
       <c r="AI740" s="2" t="n"/>
       <c r="AJ740" s="2" t="n"/>
+      <c r="AK740" s="2" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="4" t="n"/>
@@ -28946,6 +29695,7 @@
       <c r="AH741" s="4" t="n"/>
       <c r="AI741" s="4" t="n"/>
       <c r="AJ741" s="4" t="n"/>
+      <c r="AK741" s="4" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n"/>
@@ -28984,6 +29734,7 @@
       <c r="AH742" s="2" t="n"/>
       <c r="AI742" s="2" t="n"/>
       <c r="AJ742" s="2" t="n"/>
+      <c r="AK742" s="2" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="4" t="n"/>
@@ -29022,6 +29773,7 @@
       <c r="AH743" s="4" t="n"/>
       <c r="AI743" s="4" t="n"/>
       <c r="AJ743" s="4" t="n"/>
+      <c r="AK743" s="4" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n"/>
@@ -29060,6 +29812,7 @@
       <c r="AH744" s="2" t="n"/>
       <c r="AI744" s="2" t="n"/>
       <c r="AJ744" s="2" t="n"/>
+      <c r="AK744" s="2" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="4" t="n"/>
@@ -29098,6 +29851,7 @@
       <c r="AH745" s="4" t="n"/>
       <c r="AI745" s="4" t="n"/>
       <c r="AJ745" s="4" t="n"/>
+      <c r="AK745" s="4" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n"/>
@@ -29136,6 +29890,7 @@
       <c r="AH746" s="2" t="n"/>
       <c r="AI746" s="2" t="n"/>
       <c r="AJ746" s="2" t="n"/>
+      <c r="AK746" s="2" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="4" t="n"/>
@@ -29174,6 +29929,7 @@
       <c r="AH747" s="4" t="n"/>
       <c r="AI747" s="4" t="n"/>
       <c r="AJ747" s="4" t="n"/>
+      <c r="AK747" s="4" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n"/>
@@ -29212,6 +29968,7 @@
       <c r="AH748" s="2" t="n"/>
       <c r="AI748" s="2" t="n"/>
       <c r="AJ748" s="2" t="n"/>
+      <c r="AK748" s="2" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="4" t="n"/>
@@ -29250,6 +30007,7 @@
       <c r="AH749" s="4" t="n"/>
       <c r="AI749" s="4" t="n"/>
       <c r="AJ749" s="4" t="n"/>
+      <c r="AK749" s="4" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n"/>
@@ -29288,6 +30046,7 @@
       <c r="AH750" s="2" t="n"/>
       <c r="AI750" s="2" t="n"/>
       <c r="AJ750" s="2" t="n"/>
+      <c r="AK750" s="2" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="4" t="n"/>
@@ -29326,6 +30085,7 @@
       <c r="AH751" s="4" t="n"/>
       <c r="AI751" s="4" t="n"/>
       <c r="AJ751" s="4" t="n"/>
+      <c r="AK751" s="4" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n"/>
@@ -29364,6 +30124,7 @@
       <c r="AH752" s="2" t="n"/>
       <c r="AI752" s="2" t="n"/>
       <c r="AJ752" s="2" t="n"/>
+      <c r="AK752" s="2" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="4" t="n"/>
@@ -29402,6 +30163,7 @@
       <c r="AH753" s="4" t="n"/>
       <c r="AI753" s="4" t="n"/>
       <c r="AJ753" s="4" t="n"/>
+      <c r="AK753" s="4" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n"/>
@@ -29440,6 +30202,7 @@
       <c r="AH754" s="2" t="n"/>
       <c r="AI754" s="2" t="n"/>
       <c r="AJ754" s="2" t="n"/>
+      <c r="AK754" s="2" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="4" t="n"/>
@@ -29478,6 +30241,7 @@
       <c r="AH755" s="4" t="n"/>
       <c r="AI755" s="4" t="n"/>
       <c r="AJ755" s="4" t="n"/>
+      <c r="AK755" s="4" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n"/>
@@ -29516,6 +30280,7 @@
       <c r="AH756" s="2" t="n"/>
       <c r="AI756" s="2" t="n"/>
       <c r="AJ756" s="2" t="n"/>
+      <c r="AK756" s="2" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="4" t="n"/>
@@ -29554,6 +30319,7 @@
       <c r="AH757" s="4" t="n"/>
       <c r="AI757" s="4" t="n"/>
       <c r="AJ757" s="4" t="n"/>
+      <c r="AK757" s="4" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n"/>
@@ -29592,6 +30358,7 @@
       <c r="AH758" s="2" t="n"/>
       <c r="AI758" s="2" t="n"/>
       <c r="AJ758" s="2" t="n"/>
+      <c r="AK758" s="2" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="4" t="n"/>
@@ -29630,6 +30397,7 @@
       <c r="AH759" s="4" t="n"/>
       <c r="AI759" s="4" t="n"/>
       <c r="AJ759" s="4" t="n"/>
+      <c r="AK759" s="4" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n"/>
@@ -29668,6 +30436,7 @@
       <c r="AH760" s="2" t="n"/>
       <c r="AI760" s="2" t="n"/>
       <c r="AJ760" s="2" t="n"/>
+      <c r="AK760" s="2" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="4" t="n"/>
@@ -29706,6 +30475,7 @@
       <c r="AH761" s="4" t="n"/>
       <c r="AI761" s="4" t="n"/>
       <c r="AJ761" s="4" t="n"/>
+      <c r="AK761" s="4" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n"/>
@@ -29744,6 +30514,7 @@
       <c r="AH762" s="2" t="n"/>
       <c r="AI762" s="2" t="n"/>
       <c r="AJ762" s="2" t="n"/>
+      <c r="AK762" s="2" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="4" t="n"/>
@@ -29782,6 +30553,7 @@
       <c r="AH763" s="4" t="n"/>
       <c r="AI763" s="4" t="n"/>
       <c r="AJ763" s="4" t="n"/>
+      <c r="AK763" s="4" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n"/>
@@ -29820,6 +30592,7 @@
       <c r="AH764" s="2" t="n"/>
       <c r="AI764" s="2" t="n"/>
       <c r="AJ764" s="2" t="n"/>
+      <c r="AK764" s="2" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="4" t="n"/>
@@ -29858,6 +30631,7 @@
       <c r="AH765" s="4" t="n"/>
       <c r="AI765" s="4" t="n"/>
       <c r="AJ765" s="4" t="n"/>
+      <c r="AK765" s="4" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n"/>
@@ -29896,6 +30670,7 @@
       <c r="AH766" s="2" t="n"/>
       <c r="AI766" s="2" t="n"/>
       <c r="AJ766" s="2" t="n"/>
+      <c r="AK766" s="2" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="4" t="n"/>
@@ -29934,6 +30709,7 @@
       <c r="AH767" s="4" t="n"/>
       <c r="AI767" s="4" t="n"/>
       <c r="AJ767" s="4" t="n"/>
+      <c r="AK767" s="4" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n"/>
@@ -29972,6 +30748,7 @@
       <c r="AH768" s="2" t="n"/>
       <c r="AI768" s="2" t="n"/>
       <c r="AJ768" s="2" t="n"/>
+      <c r="AK768" s="2" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="4" t="n"/>
@@ -30010,6 +30787,7 @@
       <c r="AH769" s="4" t="n"/>
       <c r="AI769" s="4" t="n"/>
       <c r="AJ769" s="4" t="n"/>
+      <c r="AK769" s="4" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n"/>
@@ -30048,6 +30826,7 @@
       <c r="AH770" s="2" t="n"/>
       <c r="AI770" s="2" t="n"/>
       <c r="AJ770" s="2" t="n"/>
+      <c r="AK770" s="2" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="4" t="n"/>
@@ -30086,6 +30865,7 @@
       <c r="AH771" s="4" t="n"/>
       <c r="AI771" s="4" t="n"/>
       <c r="AJ771" s="4" t="n"/>
+      <c r="AK771" s="4" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n"/>
@@ -30124,6 +30904,7 @@
       <c r="AH772" s="2" t="n"/>
       <c r="AI772" s="2" t="n"/>
       <c r="AJ772" s="2" t="n"/>
+      <c r="AK772" s="2" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="4" t="n"/>
@@ -30162,6 +30943,7 @@
       <c r="AH773" s="4" t="n"/>
       <c r="AI773" s="4" t="n"/>
       <c r="AJ773" s="4" t="n"/>
+      <c r="AK773" s="4" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n"/>
@@ -30200,6 +30982,7 @@
       <c r="AH774" s="2" t="n"/>
       <c r="AI774" s="2" t="n"/>
       <c r="AJ774" s="2" t="n"/>
+      <c r="AK774" s="2" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="4" t="n"/>
@@ -30238,6 +31021,7 @@
       <c r="AH775" s="4" t="n"/>
       <c r="AI775" s="4" t="n"/>
       <c r="AJ775" s="4" t="n"/>
+      <c r="AK775" s="4" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n"/>
@@ -30276,6 +31060,7 @@
       <c r="AH776" s="2" t="n"/>
       <c r="AI776" s="2" t="n"/>
       <c r="AJ776" s="2" t="n"/>
+      <c r="AK776" s="2" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="4" t="n"/>
@@ -30314,6 +31099,7 @@
       <c r="AH777" s="4" t="n"/>
       <c r="AI777" s="4" t="n"/>
       <c r="AJ777" s="4" t="n"/>
+      <c r="AK777" s="4" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n"/>
@@ -30352,6 +31138,7 @@
       <c r="AH778" s="2" t="n"/>
       <c r="AI778" s="2" t="n"/>
       <c r="AJ778" s="2" t="n"/>
+      <c r="AK778" s="2" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="4" t="n"/>
@@ -30390,6 +31177,7 @@
       <c r="AH779" s="4" t="n"/>
       <c r="AI779" s="4" t="n"/>
       <c r="AJ779" s="4" t="n"/>
+      <c r="AK779" s="4" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n"/>
@@ -30428,6 +31216,7 @@
       <c r="AH780" s="2" t="n"/>
       <c r="AI780" s="2" t="n"/>
       <c r="AJ780" s="2" t="n"/>
+      <c r="AK780" s="2" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="4" t="n"/>
@@ -30466,6 +31255,7 @@
       <c r="AH781" s="4" t="n"/>
       <c r="AI781" s="4" t="n"/>
       <c r="AJ781" s="4" t="n"/>
+      <c r="AK781" s="4" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n"/>
@@ -30504,6 +31294,7 @@
       <c r="AH782" s="2" t="n"/>
       <c r="AI782" s="2" t="n"/>
       <c r="AJ782" s="2" t="n"/>
+      <c r="AK782" s="2" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="4" t="n"/>
@@ -30542,6 +31333,7 @@
       <c r="AH783" s="4" t="n"/>
       <c r="AI783" s="4" t="n"/>
       <c r="AJ783" s="4" t="n"/>
+      <c r="AK783" s="4" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n"/>
@@ -30580,6 +31372,7 @@
       <c r="AH784" s="2" t="n"/>
       <c r="AI784" s="2" t="n"/>
       <c r="AJ784" s="2" t="n"/>
+      <c r="AK784" s="2" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="4" t="n"/>
@@ -30618,6 +31411,7 @@
       <c r="AH785" s="4" t="n"/>
       <c r="AI785" s="4" t="n"/>
       <c r="AJ785" s="4" t="n"/>
+      <c r="AK785" s="4" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n"/>
@@ -30656,6 +31450,7 @@
       <c r="AH786" s="2" t="n"/>
       <c r="AI786" s="2" t="n"/>
       <c r="AJ786" s="2" t="n"/>
+      <c r="AK786" s="2" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="4" t="n"/>
@@ -30694,6 +31489,7 @@
       <c r="AH787" s="4" t="n"/>
       <c r="AI787" s="4" t="n"/>
       <c r="AJ787" s="4" t="n"/>
+      <c r="AK787" s="4" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n"/>
@@ -30732,6 +31528,7 @@
       <c r="AH788" s="2" t="n"/>
       <c r="AI788" s="2" t="n"/>
       <c r="AJ788" s="2" t="n"/>
+      <c r="AK788" s="2" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="4" t="n"/>
@@ -30770,6 +31567,7 @@
       <c r="AH789" s="4" t="n"/>
       <c r="AI789" s="4" t="n"/>
       <c r="AJ789" s="4" t="n"/>
+      <c r="AK789" s="4" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n"/>
@@ -30808,6 +31606,7 @@
       <c r="AH790" s="2" t="n"/>
       <c r="AI790" s="2" t="n"/>
       <c r="AJ790" s="2" t="n"/>
+      <c r="AK790" s="2" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="4" t="n"/>
@@ -30846,6 +31645,7 @@
       <c r="AH791" s="4" t="n"/>
       <c r="AI791" s="4" t="n"/>
       <c r="AJ791" s="4" t="n"/>
+      <c r="AK791" s="4" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n"/>
@@ -30884,6 +31684,7 @@
       <c r="AH792" s="2" t="n"/>
       <c r="AI792" s="2" t="n"/>
       <c r="AJ792" s="2" t="n"/>
+      <c r="AK792" s="2" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="4" t="n"/>
@@ -30922,6 +31723,7 @@
       <c r="AH793" s="4" t="n"/>
       <c r="AI793" s="4" t="n"/>
       <c r="AJ793" s="4" t="n"/>
+      <c r="AK793" s="4" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n"/>
@@ -30960,6 +31762,7 @@
       <c r="AH794" s="2" t="n"/>
       <c r="AI794" s="2" t="n"/>
       <c r="AJ794" s="2" t="n"/>
+      <c r="AK794" s="2" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="4" t="n"/>
@@ -30998,6 +31801,7 @@
       <c r="AH795" s="4" t="n"/>
       <c r="AI795" s="4" t="n"/>
       <c r="AJ795" s="4" t="n"/>
+      <c r="AK795" s="4" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n"/>
@@ -31036,6 +31840,7 @@
       <c r="AH796" s="2" t="n"/>
       <c r="AI796" s="2" t="n"/>
       <c r="AJ796" s="2" t="n"/>
+      <c r="AK796" s="2" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="4" t="n"/>
@@ -31074,6 +31879,7 @@
       <c r="AH797" s="4" t="n"/>
       <c r="AI797" s="4" t="n"/>
       <c r="AJ797" s="4" t="n"/>
+      <c r="AK797" s="4" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n"/>
@@ -31112,6 +31918,7 @@
       <c r="AH798" s="2" t="n"/>
       <c r="AI798" s="2" t="n"/>
       <c r="AJ798" s="2" t="n"/>
+      <c r="AK798" s="2" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="4" t="n"/>
@@ -31150,6 +31957,7 @@
       <c r="AH799" s="4" t="n"/>
       <c r="AI799" s="4" t="n"/>
       <c r="AJ799" s="4" t="n"/>
+      <c r="AK799" s="4" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n"/>
@@ -31188,6 +31996,7 @@
       <c r="AH800" s="2" t="n"/>
       <c r="AI800" s="2" t="n"/>
       <c r="AJ800" s="2" t="n"/>
+      <c r="AK800" s="2" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="4" t="n"/>
@@ -31226,6 +32035,7 @@
       <c r="AH801" s="4" t="n"/>
       <c r="AI801" s="4" t="n"/>
       <c r="AJ801" s="4" t="n"/>
+      <c r="AK801" s="4" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n"/>
@@ -31264,6 +32074,7 @@
       <c r="AH802" s="2" t="n"/>
       <c r="AI802" s="2" t="n"/>
       <c r="AJ802" s="2" t="n"/>
+      <c r="AK802" s="2" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="4" t="n"/>
@@ -31302,6 +32113,7 @@
       <c r="AH803" s="4" t="n"/>
       <c r="AI803" s="4" t="n"/>
       <c r="AJ803" s="4" t="n"/>
+      <c r="AK803" s="4" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n"/>
@@ -31340,6 +32152,7 @@
       <c r="AH804" s="2" t="n"/>
       <c r="AI804" s="2" t="n"/>
       <c r="AJ804" s="2" t="n"/>
+      <c r="AK804" s="2" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="4" t="n"/>
@@ -31378,6 +32191,7 @@
       <c r="AH805" s="4" t="n"/>
       <c r="AI805" s="4" t="n"/>
       <c r="AJ805" s="4" t="n"/>
+      <c r="AK805" s="4" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n"/>
@@ -31416,6 +32230,7 @@
       <c r="AH806" s="2" t="n"/>
       <c r="AI806" s="2" t="n"/>
       <c r="AJ806" s="2" t="n"/>
+      <c r="AK806" s="2" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="4" t="n"/>
@@ -31454,6 +32269,7 @@
       <c r="AH807" s="4" t="n"/>
       <c r="AI807" s="4" t="n"/>
       <c r="AJ807" s="4" t="n"/>
+      <c r="AK807" s="4" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n"/>
@@ -31492,6 +32308,7 @@
       <c r="AH808" s="2" t="n"/>
       <c r="AI808" s="2" t="n"/>
       <c r="AJ808" s="2" t="n"/>
+      <c r="AK808" s="2" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="4" t="n"/>
@@ -31530,6 +32347,7 @@
       <c r="AH809" s="4" t="n"/>
       <c r="AI809" s="4" t="n"/>
       <c r="AJ809" s="4" t="n"/>
+      <c r="AK809" s="4" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n"/>
@@ -31568,6 +32386,7 @@
       <c r="AH810" s="2" t="n"/>
       <c r="AI810" s="2" t="n"/>
       <c r="AJ810" s="2" t="n"/>
+      <c r="AK810" s="2" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="4" t="n"/>
@@ -31606,6 +32425,7 @@
       <c r="AH811" s="4" t="n"/>
       <c r="AI811" s="4" t="n"/>
       <c r="AJ811" s="4" t="n"/>
+      <c r="AK811" s="4" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n"/>
@@ -31644,6 +32464,7 @@
       <c r="AH812" s="2" t="n"/>
       <c r="AI812" s="2" t="n"/>
       <c r="AJ812" s="2" t="n"/>
+      <c r="AK812" s="2" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="4" t="n"/>
@@ -31682,6 +32503,7 @@
       <c r="AH813" s="4" t="n"/>
       <c r="AI813" s="4" t="n"/>
       <c r="AJ813" s="4" t="n"/>
+      <c r="AK813" s="4" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n"/>
@@ -31720,6 +32542,7 @@
       <c r="AH814" s="2" t="n"/>
       <c r="AI814" s="2" t="n"/>
       <c r="AJ814" s="2" t="n"/>
+      <c r="AK814" s="2" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="4" t="n"/>
@@ -31758,6 +32581,7 @@
       <c r="AH815" s="4" t="n"/>
       <c r="AI815" s="4" t="n"/>
       <c r="AJ815" s="4" t="n"/>
+      <c r="AK815" s="4" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n"/>
@@ -31796,6 +32620,7 @@
       <c r="AH816" s="2" t="n"/>
       <c r="AI816" s="2" t="n"/>
       <c r="AJ816" s="2" t="n"/>
+      <c r="AK816" s="2" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="4" t="n"/>
@@ -31834,6 +32659,7 @@
       <c r="AH817" s="4" t="n"/>
       <c r="AI817" s="4" t="n"/>
       <c r="AJ817" s="4" t="n"/>
+      <c r="AK817" s="4" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n"/>
@@ -31872,6 +32698,7 @@
       <c r="AH818" s="2" t="n"/>
       <c r="AI818" s="2" t="n"/>
       <c r="AJ818" s="2" t="n"/>
+      <c r="AK818" s="2" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="4" t="n"/>
@@ -31910,6 +32737,7 @@
       <c r="AH819" s="4" t="n"/>
       <c r="AI819" s="4" t="n"/>
       <c r="AJ819" s="4" t="n"/>
+      <c r="AK819" s="4" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n"/>
@@ -31948,6 +32776,7 @@
       <c r="AH820" s="2" t="n"/>
       <c r="AI820" s="2" t="n"/>
       <c r="AJ820" s="2" t="n"/>
+      <c r="AK820" s="2" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="4" t="n"/>
@@ -31986,6 +32815,7 @@
       <c r="AH821" s="4" t="n"/>
       <c r="AI821" s="4" t="n"/>
       <c r="AJ821" s="4" t="n"/>
+      <c r="AK821" s="4" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n"/>
@@ -32024,6 +32854,7 @@
       <c r="AH822" s="2" t="n"/>
       <c r="AI822" s="2" t="n"/>
       <c r="AJ822" s="2" t="n"/>
+      <c r="AK822" s="2" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="4" t="n"/>
@@ -32062,6 +32893,7 @@
       <c r="AH823" s="4" t="n"/>
       <c r="AI823" s="4" t="n"/>
       <c r="AJ823" s="4" t="n"/>
+      <c r="AK823" s="4" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n"/>
@@ -32100,6 +32932,7 @@
       <c r="AH824" s="2" t="n"/>
       <c r="AI824" s="2" t="n"/>
       <c r="AJ824" s="2" t="n"/>
+      <c r="AK824" s="2" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="4" t="n"/>
@@ -32138,6 +32971,7 @@
       <c r="AH825" s="4" t="n"/>
       <c r="AI825" s="4" t="n"/>
       <c r="AJ825" s="4" t="n"/>
+      <c r="AK825" s="4" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n"/>
@@ -32176,6 +33010,7 @@
       <c r="AH826" s="2" t="n"/>
       <c r="AI826" s="2" t="n"/>
       <c r="AJ826" s="2" t="n"/>
+      <c r="AK826" s="2" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="4" t="n"/>
@@ -32214,6 +33049,7 @@
       <c r="AH827" s="4" t="n"/>
       <c r="AI827" s="4" t="n"/>
       <c r="AJ827" s="4" t="n"/>
+      <c r="AK827" s="4" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n"/>
@@ -32252,6 +33088,7 @@
       <c r="AH828" s="2" t="n"/>
       <c r="AI828" s="2" t="n"/>
       <c r="AJ828" s="2" t="n"/>
+      <c r="AK828" s="2" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="4" t="n"/>
@@ -32290,6 +33127,7 @@
       <c r="AH829" s="4" t="n"/>
       <c r="AI829" s="4" t="n"/>
       <c r="AJ829" s="4" t="n"/>
+      <c r="AK829" s="4" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n"/>
@@ -32328,6 +33166,7 @@
       <c r="AH830" s="2" t="n"/>
       <c r="AI830" s="2" t="n"/>
       <c r="AJ830" s="2" t="n"/>
+      <c r="AK830" s="2" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="4" t="n"/>
@@ -32366,6 +33205,7 @@
       <c r="AH831" s="4" t="n"/>
       <c r="AI831" s="4" t="n"/>
       <c r="AJ831" s="4" t="n"/>
+      <c r="AK831" s="4" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n"/>
@@ -32404,6 +33244,7 @@
       <c r="AH832" s="2" t="n"/>
       <c r="AI832" s="2" t="n"/>
       <c r="AJ832" s="2" t="n"/>
+      <c r="AK832" s="2" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="4" t="n"/>
@@ -32442,6 +33283,7 @@
       <c r="AH833" s="4" t="n"/>
       <c r="AI833" s="4" t="n"/>
       <c r="AJ833" s="4" t="n"/>
+      <c r="AK833" s="4" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n"/>
@@ -32480,6 +33322,7 @@
       <c r="AH834" s="2" t="n"/>
       <c r="AI834" s="2" t="n"/>
       <c r="AJ834" s="2" t="n"/>
+      <c r="AK834" s="2" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="4" t="n"/>
@@ -32518,6 +33361,7 @@
       <c r="AH835" s="4" t="n"/>
       <c r="AI835" s="4" t="n"/>
       <c r="AJ835" s="4" t="n"/>
+      <c r="AK835" s="4" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n"/>
@@ -32556,6 +33400,7 @@
       <c r="AH836" s="2" t="n"/>
       <c r="AI836" s="2" t="n"/>
       <c r="AJ836" s="2" t="n"/>
+      <c r="AK836" s="2" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="4" t="n"/>
@@ -32594,6 +33439,7 @@
       <c r="AH837" s="4" t="n"/>
       <c r="AI837" s="4" t="n"/>
       <c r="AJ837" s="4" t="n"/>
+      <c r="AK837" s="4" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n"/>
@@ -32632,6 +33478,7 @@
       <c r="AH838" s="2" t="n"/>
       <c r="AI838" s="2" t="n"/>
       <c r="AJ838" s="2" t="n"/>
+      <c r="AK838" s="2" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="4" t="n"/>
@@ -32670,6 +33517,7 @@
       <c r="AH839" s="4" t="n"/>
       <c r="AI839" s="4" t="n"/>
       <c r="AJ839" s="4" t="n"/>
+      <c r="AK839" s="4" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n"/>
@@ -32708,6 +33556,7 @@
       <c r="AH840" s="2" t="n"/>
       <c r="AI840" s="2" t="n"/>
       <c r="AJ840" s="2" t="n"/>
+      <c r="AK840" s="2" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="4" t="n"/>
@@ -32746,6 +33595,7 @@
       <c r="AH841" s="4" t="n"/>
       <c r="AI841" s="4" t="n"/>
       <c r="AJ841" s="4" t="n"/>
+      <c r="AK841" s="4" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n"/>
@@ -32784,6 +33634,7 @@
       <c r="AH842" s="2" t="n"/>
       <c r="AI842" s="2" t="n"/>
       <c r="AJ842" s="2" t="n"/>
+      <c r="AK842" s="2" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="4" t="n"/>
@@ -32822,6 +33673,7 @@
       <c r="AH843" s="4" t="n"/>
       <c r="AI843" s="4" t="n"/>
       <c r="AJ843" s="4" t="n"/>
+      <c r="AK843" s="4" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n"/>
@@ -32860,6 +33712,7 @@
       <c r="AH844" s="2" t="n"/>
       <c r="AI844" s="2" t="n"/>
       <c r="AJ844" s="2" t="n"/>
+      <c r="AK844" s="2" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="4" t="n"/>
@@ -32898,6 +33751,7 @@
       <c r="AH845" s="4" t="n"/>
       <c r="AI845" s="4" t="n"/>
       <c r="AJ845" s="4" t="n"/>
+      <c r="AK845" s="4" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n"/>
@@ -32936,6 +33790,7 @@
       <c r="AH846" s="2" t="n"/>
       <c r="AI846" s="2" t="n"/>
       <c r="AJ846" s="2" t="n"/>
+      <c r="AK846" s="2" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="4" t="n"/>
@@ -32974,6 +33829,7 @@
       <c r="AH847" s="4" t="n"/>
       <c r="AI847" s="4" t="n"/>
       <c r="AJ847" s="4" t="n"/>
+      <c r="AK847" s="4" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n"/>
@@ -33012,6 +33868,7 @@
       <c r="AH848" s="2" t="n"/>
       <c r="AI848" s="2" t="n"/>
       <c r="AJ848" s="2" t="n"/>
+      <c r="AK848" s="2" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="4" t="n"/>
@@ -33050,6 +33907,7 @@
       <c r="AH849" s="4" t="n"/>
       <c r="AI849" s="4" t="n"/>
       <c r="AJ849" s="4" t="n"/>
+      <c r="AK849" s="4" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n"/>
@@ -33088,6 +33946,7 @@
       <c r="AH850" s="2" t="n"/>
       <c r="AI850" s="2" t="n"/>
       <c r="AJ850" s="2" t="n"/>
+      <c r="AK850" s="2" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="4" t="n"/>
@@ -33126,6 +33985,7 @@
       <c r="AH851" s="4" t="n"/>
       <c r="AI851" s="4" t="n"/>
       <c r="AJ851" s="4" t="n"/>
+      <c r="AK851" s="4" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n"/>
@@ -33164,6 +34024,7 @@
       <c r="AH852" s="2" t="n"/>
       <c r="AI852" s="2" t="n"/>
       <c r="AJ852" s="2" t="n"/>
+      <c r="AK852" s="2" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="4" t="n"/>
@@ -33202,6 +34063,7 @@
       <c r="AH853" s="4" t="n"/>
       <c r="AI853" s="4" t="n"/>
       <c r="AJ853" s="4" t="n"/>
+      <c r="AK853" s="4" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n"/>
@@ -33240,6 +34102,7 @@
       <c r="AH854" s="2" t="n"/>
       <c r="AI854" s="2" t="n"/>
       <c r="AJ854" s="2" t="n"/>
+      <c r="AK854" s="2" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="4" t="n"/>
@@ -33278,6 +34141,7 @@
       <c r="AH855" s="4" t="n"/>
       <c r="AI855" s="4" t="n"/>
       <c r="AJ855" s="4" t="n"/>
+      <c r="AK855" s="4" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n"/>
@@ -33316,6 +34180,7 @@
       <c r="AH856" s="2" t="n"/>
       <c r="AI856" s="2" t="n"/>
       <c r="AJ856" s="2" t="n"/>
+      <c r="AK856" s="2" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="4" t="n"/>
@@ -33354,6 +34219,7 @@
       <c r="AH857" s="4" t="n"/>
       <c r="AI857" s="4" t="n"/>
       <c r="AJ857" s="4" t="n"/>
+      <c r="AK857" s="4" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n"/>
@@ -33392,6 +34258,7 @@
       <c r="AH858" s="2" t="n"/>
       <c r="AI858" s="2" t="n"/>
       <c r="AJ858" s="2" t="n"/>
+      <c r="AK858" s="2" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="4" t="n"/>
@@ -33430,6 +34297,7 @@
       <c r="AH859" s="4" t="n"/>
       <c r="AI859" s="4" t="n"/>
       <c r="AJ859" s="4" t="n"/>
+      <c r="AK859" s="4" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n"/>
@@ -33468,6 +34336,7 @@
       <c r="AH860" s="2" t="n"/>
       <c r="AI860" s="2" t="n"/>
       <c r="AJ860" s="2" t="n"/>
+      <c r="AK860" s="2" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="4" t="n"/>
@@ -33506,6 +34375,7 @@
       <c r="AH861" s="4" t="n"/>
       <c r="AI861" s="4" t="n"/>
       <c r="AJ861" s="4" t="n"/>
+      <c r="AK861" s="4" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n"/>
@@ -33544,6 +34414,7 @@
       <c r="AH862" s="2" t="n"/>
       <c r="AI862" s="2" t="n"/>
       <c r="AJ862" s="2" t="n"/>
+      <c r="AK862" s="2" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="4" t="n"/>
@@ -33582,6 +34453,7 @@
       <c r="AH863" s="4" t="n"/>
       <c r="AI863" s="4" t="n"/>
       <c r="AJ863" s="4" t="n"/>
+      <c r="AK863" s="4" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n"/>
@@ -33620,6 +34492,7 @@
       <c r="AH864" s="2" t="n"/>
       <c r="AI864" s="2" t="n"/>
       <c r="AJ864" s="2" t="n"/>
+      <c r="AK864" s="2" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="4" t="n"/>
@@ -33658,6 +34531,7 @@
       <c r="AH865" s="4" t="n"/>
       <c r="AI865" s="4" t="n"/>
       <c r="AJ865" s="4" t="n"/>
+      <c r="AK865" s="4" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n"/>
@@ -33696,6 +34570,7 @@
       <c r="AH866" s="2" t="n"/>
       <c r="AI866" s="2" t="n"/>
       <c r="AJ866" s="2" t="n"/>
+      <c r="AK866" s="2" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="4" t="n"/>
@@ -33734,6 +34609,7 @@
       <c r="AH867" s="4" t="n"/>
       <c r="AI867" s="4" t="n"/>
       <c r="AJ867" s="4" t="n"/>
+      <c r="AK867" s="4" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n"/>
@@ -33772,6 +34648,7 @@
       <c r="AH868" s="2" t="n"/>
       <c r="AI868" s="2" t="n"/>
       <c r="AJ868" s="2" t="n"/>
+      <c r="AK868" s="2" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="4" t="n"/>
@@ -33810,6 +34687,7 @@
       <c r="AH869" s="4" t="n"/>
       <c r="AI869" s="4" t="n"/>
       <c r="AJ869" s="4" t="n"/>
+      <c r="AK869" s="4" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n"/>
@@ -33848,6 +34726,7 @@
       <c r="AH870" s="2" t="n"/>
       <c r="AI870" s="2" t="n"/>
       <c r="AJ870" s="2" t="n"/>
+      <c r="AK870" s="2" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="4" t="n"/>
@@ -33886,6 +34765,7 @@
       <c r="AH871" s="4" t="n"/>
       <c r="AI871" s="4" t="n"/>
       <c r="AJ871" s="4" t="n"/>
+      <c r="AK871" s="4" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n"/>
@@ -33924,6 +34804,7 @@
       <c r="AH872" s="2" t="n"/>
       <c r="AI872" s="2" t="n"/>
       <c r="AJ872" s="2" t="n"/>
+      <c r="AK872" s="2" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="4" t="n"/>
@@ -33962,6 +34843,7 @@
       <c r="AH873" s="4" t="n"/>
       <c r="AI873" s="4" t="n"/>
       <c r="AJ873" s="4" t="n"/>
+      <c r="AK873" s="4" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n"/>
@@ -34000,6 +34882,7 @@
       <c r="AH874" s="2" t="n"/>
       <c r="AI874" s="2" t="n"/>
       <c r="AJ874" s="2" t="n"/>
+      <c r="AK874" s="2" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="4" t="n"/>
@@ -34038,6 +34921,7 @@
       <c r="AH875" s="4" t="n"/>
       <c r="AI875" s="4" t="n"/>
       <c r="AJ875" s="4" t="n"/>
+      <c r="AK875" s="4" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n"/>
@@ -34076,6 +34960,7 @@
       <c r="AH876" s="2" t="n"/>
       <c r="AI876" s="2" t="n"/>
       <c r="AJ876" s="2" t="n"/>
+      <c r="AK876" s="2" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="4" t="n"/>
@@ -34114,6 +34999,7 @@
       <c r="AH877" s="4" t="n"/>
       <c r="AI877" s="4" t="n"/>
       <c r="AJ877" s="4" t="n"/>
+      <c r="AK877" s="4" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n"/>
@@ -34152,6 +35038,7 @@
       <c r="AH878" s="2" t="n"/>
       <c r="AI878" s="2" t="n"/>
       <c r="AJ878" s="2" t="n"/>
+      <c r="AK878" s="2" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="4" t="n"/>
@@ -34190,6 +35077,7 @@
       <c r="AH879" s="4" t="n"/>
       <c r="AI879" s="4" t="n"/>
       <c r="AJ879" s="4" t="n"/>
+      <c r="AK879" s="4" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n"/>
@@ -34228,6 +35116,7 @@
       <c r="AH880" s="2" t="n"/>
       <c r="AI880" s="2" t="n"/>
       <c r="AJ880" s="2" t="n"/>
+      <c r="AK880" s="2" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="4" t="n"/>
@@ -34266,6 +35155,7 @@
       <c r="AH881" s="4" t="n"/>
       <c r="AI881" s="4" t="n"/>
       <c r="AJ881" s="4" t="n"/>
+      <c r="AK881" s="4" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n"/>
@@ -34304,6 +35194,7 @@
       <c r="AH882" s="2" t="n"/>
       <c r="AI882" s="2" t="n"/>
       <c r="AJ882" s="2" t="n"/>
+      <c r="AK882" s="2" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="4" t="n"/>
@@ -34342,6 +35233,7 @@
       <c r="AH883" s="4" t="n"/>
       <c r="AI883" s="4" t="n"/>
       <c r="AJ883" s="4" t="n"/>
+      <c r="AK883" s="4" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n"/>
@@ -34380,6 +35272,7 @@
       <c r="AH884" s="2" t="n"/>
       <c r="AI884" s="2" t="n"/>
       <c r="AJ884" s="2" t="n"/>
+      <c r="AK884" s="2" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="4" t="n"/>
@@ -34418,6 +35311,7 @@
       <c r="AH885" s="4" t="n"/>
       <c r="AI885" s="4" t="n"/>
       <c r="AJ885" s="4" t="n"/>
+      <c r="AK885" s="4" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n"/>
@@ -34456,6 +35350,7 @@
       <c r="AH886" s="2" t="n"/>
       <c r="AI886" s="2" t="n"/>
       <c r="AJ886" s="2" t="n"/>
+      <c r="AK886" s="2" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="4" t="n"/>
@@ -34494,6 +35389,7 @@
       <c r="AH887" s="4" t="n"/>
       <c r="AI887" s="4" t="n"/>
       <c r="AJ887" s="4" t="n"/>
+      <c r="AK887" s="4" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n"/>
@@ -34532,6 +35428,7 @@
       <c r="AH888" s="2" t="n"/>
       <c r="AI888" s="2" t="n"/>
       <c r="AJ888" s="2" t="n"/>
+      <c r="AK888" s="2" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="4" t="n"/>
@@ -34570,6 +35467,7 @@
       <c r="AH889" s="4" t="n"/>
       <c r="AI889" s="4" t="n"/>
       <c r="AJ889" s="4" t="n"/>
+      <c r="AK889" s="4" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n"/>
@@ -34608,6 +35506,7 @@
       <c r="AH890" s="2" t="n"/>
       <c r="AI890" s="2" t="n"/>
       <c r="AJ890" s="2" t="n"/>
+      <c r="AK890" s="2" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="4" t="n"/>
@@ -34646,6 +35545,7 @@
       <c r="AH891" s="4" t="n"/>
       <c r="AI891" s="4" t="n"/>
       <c r="AJ891" s="4" t="n"/>
+      <c r="AK891" s="4" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n"/>
@@ -34684,6 +35584,7 @@
       <c r="AH892" s="2" t="n"/>
       <c r="AI892" s="2" t="n"/>
       <c r="AJ892" s="2" t="n"/>
+      <c r="AK892" s="2" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="4" t="n"/>
@@ -34722,6 +35623,7 @@
       <c r="AH893" s="4" t="n"/>
       <c r="AI893" s="4" t="n"/>
       <c r="AJ893" s="4" t="n"/>
+      <c r="AK893" s="4" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n"/>
@@ -34760,6 +35662,7 @@
       <c r="AH894" s="2" t="n"/>
       <c r="AI894" s="2" t="n"/>
       <c r="AJ894" s="2" t="n"/>
+      <c r="AK894" s="2" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="4" t="n"/>
@@ -34798,6 +35701,7 @@
       <c r="AH895" s="4" t="n"/>
       <c r="AI895" s="4" t="n"/>
       <c r="AJ895" s="4" t="n"/>
+      <c r="AK895" s="4" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n"/>
@@ -34836,6 +35740,7 @@
       <c r="AH896" s="2" t="n"/>
       <c r="AI896" s="2" t="n"/>
       <c r="AJ896" s="2" t="n"/>
+      <c r="AK896" s="2" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="4" t="n"/>
@@ -34874,6 +35779,7 @@
       <c r="AH897" s="4" t="n"/>
       <c r="AI897" s="4" t="n"/>
       <c r="AJ897" s="4" t="n"/>
+      <c r="AK897" s="4" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n"/>
@@ -34912,6 +35818,7 @@
       <c r="AH898" s="2" t="n"/>
       <c r="AI898" s="2" t="n"/>
       <c r="AJ898" s="2" t="n"/>
+      <c r="AK898" s="2" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="4" t="n"/>
@@ -34950,6 +35857,7 @@
       <c r="AH899" s="4" t="n"/>
       <c r="AI899" s="4" t="n"/>
       <c r="AJ899" s="4" t="n"/>
+      <c r="AK899" s="4" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n"/>
@@ -34988,6 +35896,7 @@
       <c r="AH900" s="2" t="n"/>
       <c r="AI900" s="2" t="n"/>
       <c r="AJ900" s="2" t="n"/>
+      <c r="AK900" s="2" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="4" t="n"/>
@@ -35026,6 +35935,7 @@
       <c r="AH901" s="4" t="n"/>
       <c r="AI901" s="4" t="n"/>
       <c r="AJ901" s="4" t="n"/>
+      <c r="AK901" s="4" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n"/>
@@ -35064,6 +35974,7 @@
       <c r="AH902" s="2" t="n"/>
       <c r="AI902" s="2" t="n"/>
       <c r="AJ902" s="2" t="n"/>
+      <c r="AK902" s="2" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="4" t="n"/>
@@ -35102,6 +36013,7 @@
       <c r="AH903" s="4" t="n"/>
       <c r="AI903" s="4" t="n"/>
       <c r="AJ903" s="4" t="n"/>
+      <c r="AK903" s="4" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n"/>
@@ -35140,6 +36052,7 @@
       <c r="AH904" s="2" t="n"/>
       <c r="AI904" s="2" t="n"/>
       <c r="AJ904" s="2" t="n"/>
+      <c r="AK904" s="2" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="4" t="n"/>
@@ -35178,6 +36091,7 @@
       <c r="AH905" s="4" t="n"/>
       <c r="AI905" s="4" t="n"/>
       <c r="AJ905" s="4" t="n"/>
+      <c r="AK905" s="4" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n"/>
@@ -35216,6 +36130,7 @@
       <c r="AH906" s="2" t="n"/>
       <c r="AI906" s="2" t="n"/>
       <c r="AJ906" s="2" t="n"/>
+      <c r="AK906" s="2" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="4" t="n"/>
@@ -35254,6 +36169,7 @@
       <c r="AH907" s="4" t="n"/>
       <c r="AI907" s="4" t="n"/>
       <c r="AJ907" s="4" t="n"/>
+      <c r="AK907" s="4" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n"/>
@@ -35292,6 +36208,7 @@
       <c r="AH908" s="2" t="n"/>
       <c r="AI908" s="2" t="n"/>
       <c r="AJ908" s="2" t="n"/>
+      <c r="AK908" s="2" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="4" t="n"/>
@@ -35330,6 +36247,7 @@
       <c r="AH909" s="4" t="n"/>
       <c r="AI909" s="4" t="n"/>
       <c r="AJ909" s="4" t="n"/>
+      <c r="AK909" s="4" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n"/>
@@ -35368,6 +36286,7 @@
       <c r="AH910" s="2" t="n"/>
       <c r="AI910" s="2" t="n"/>
       <c r="AJ910" s="2" t="n"/>
+      <c r="AK910" s="2" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="4" t="n"/>
@@ -35406,6 +36325,7 @@
       <c r="AH911" s="4" t="n"/>
       <c r="AI911" s="4" t="n"/>
       <c r="AJ911" s="4" t="n"/>
+      <c r="AK911" s="4" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n"/>
@@ -35444,6 +36364,7 @@
       <c r="AH912" s="2" t="n"/>
       <c r="AI912" s="2" t="n"/>
       <c r="AJ912" s="2" t="n"/>
+      <c r="AK912" s="2" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="4" t="n"/>
@@ -35482,6 +36403,7 @@
       <c r="AH913" s="4" t="n"/>
       <c r="AI913" s="4" t="n"/>
       <c r="AJ913" s="4" t="n"/>
+      <c r="AK913" s="4" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n"/>
@@ -35520,6 +36442,7 @@
       <c r="AH914" s="2" t="n"/>
       <c r="AI914" s="2" t="n"/>
       <c r="AJ914" s="2" t="n"/>
+      <c r="AK914" s="2" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="4" t="n"/>
@@ -35558,6 +36481,7 @@
       <c r="AH915" s="4" t="n"/>
       <c r="AI915" s="4" t="n"/>
       <c r="AJ915" s="4" t="n"/>
+      <c r="AK915" s="4" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n"/>
@@ -35596,6 +36520,7 @@
       <c r="AH916" s="2" t="n"/>
       <c r="AI916" s="2" t="n"/>
       <c r="AJ916" s="2" t="n"/>
+      <c r="AK916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="4" t="n"/>
@@ -35634,6 +36559,7 @@
       <c r="AH917" s="4" t="n"/>
       <c r="AI917" s="4" t="n"/>
       <c r="AJ917" s="4" t="n"/>
+      <c r="AK917" s="4" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n"/>
@@ -35672,6 +36598,7 @@
       <c r="AH918" s="2" t="n"/>
       <c r="AI918" s="2" t="n"/>
       <c r="AJ918" s="2" t="n"/>
+      <c r="AK918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="4" t="n"/>
@@ -35710,6 +36637,7 @@
       <c r="AH919" s="4" t="n"/>
       <c r="AI919" s="4" t="n"/>
       <c r="AJ919" s="4" t="n"/>
+      <c r="AK919" s="4" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n"/>
@@ -35748,6 +36676,7 @@
       <c r="AH920" s="2" t="n"/>
       <c r="AI920" s="2" t="n"/>
       <c r="AJ920" s="2" t="n"/>
+      <c r="AK920" s="2" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="4" t="n"/>
@@ -35786,6 +36715,7 @@
       <c r="AH921" s="4" t="n"/>
       <c r="AI921" s="4" t="n"/>
       <c r="AJ921" s="4" t="n"/>
+      <c r="AK921" s="4" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n"/>
@@ -35824,6 +36754,7 @@
       <c r="AH922" s="2" t="n"/>
       <c r="AI922" s="2" t="n"/>
       <c r="AJ922" s="2" t="n"/>
+      <c r="AK922" s="2" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="4" t="n"/>
@@ -35862,6 +36793,7 @@
       <c r="AH923" s="4" t="n"/>
       <c r="AI923" s="4" t="n"/>
       <c r="AJ923" s="4" t="n"/>
+      <c r="AK923" s="4" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n"/>
@@ -35900,6 +36832,7 @@
       <c r="AH924" s="2" t="n"/>
       <c r="AI924" s="2" t="n"/>
       <c r="AJ924" s="2" t="n"/>
+      <c r="AK924" s="2" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="4" t="n"/>
@@ -35938,6 +36871,7 @@
       <c r="AH925" s="4" t="n"/>
       <c r="AI925" s="4" t="n"/>
       <c r="AJ925" s="4" t="n"/>
+      <c r="AK925" s="4" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n"/>
@@ -35976,6 +36910,7 @@
       <c r="AH926" s="2" t="n"/>
       <c r="AI926" s="2" t="n"/>
       <c r="AJ926" s="2" t="n"/>
+      <c r="AK926" s="2" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="4" t="n"/>
@@ -36014,6 +36949,7 @@
       <c r="AH927" s="4" t="n"/>
       <c r="AI927" s="4" t="n"/>
       <c r="AJ927" s="4" t="n"/>
+      <c r="AK927" s="4" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n"/>
@@ -36052,6 +36988,7 @@
       <c r="AH928" s="2" t="n"/>
       <c r="AI928" s="2" t="n"/>
       <c r="AJ928" s="2" t="n"/>
+      <c r="AK928" s="2" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="4" t="n"/>
@@ -36090,6 +37027,7 @@
       <c r="AH929" s="4" t="n"/>
       <c r="AI929" s="4" t="n"/>
       <c r="AJ929" s="4" t="n"/>
+      <c r="AK929" s="4" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n"/>
@@ -36128,6 +37066,7 @@
       <c r="AH930" s="2" t="n"/>
       <c r="AI930" s="2" t="n"/>
       <c r="AJ930" s="2" t="n"/>
+      <c r="AK930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="4" t="n"/>
@@ -36166,6 +37105,7 @@
       <c r="AH931" s="4" t="n"/>
       <c r="AI931" s="4" t="n"/>
       <c r="AJ931" s="4" t="n"/>
+      <c r="AK931" s="4" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n"/>
@@ -36204,6 +37144,7 @@
       <c r="AH932" s="2" t="n"/>
       <c r="AI932" s="2" t="n"/>
       <c r="AJ932" s="2" t="n"/>
+      <c r="AK932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="4" t="n"/>
@@ -36242,6 +37183,7 @@
       <c r="AH933" s="4" t="n"/>
       <c r="AI933" s="4" t="n"/>
       <c r="AJ933" s="4" t="n"/>
+      <c r="AK933" s="4" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n"/>
@@ -36280,6 +37222,7 @@
       <c r="AH934" s="2" t="n"/>
       <c r="AI934" s="2" t="n"/>
       <c r="AJ934" s="2" t="n"/>
+      <c r="AK934" s="2" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="4" t="n"/>
@@ -36318,6 +37261,7 @@
       <c r="AH935" s="4" t="n"/>
       <c r="AI935" s="4" t="n"/>
       <c r="AJ935" s="4" t="n"/>
+      <c r="AK935" s="4" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n"/>
@@ -36356,6 +37300,7 @@
       <c r="AH936" s="2" t="n"/>
       <c r="AI936" s="2" t="n"/>
       <c r="AJ936" s="2" t="n"/>
+      <c r="AK936" s="2" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="4" t="n"/>
@@ -36394,6 +37339,7 @@
       <c r="AH937" s="4" t="n"/>
       <c r="AI937" s="4" t="n"/>
       <c r="AJ937" s="4" t="n"/>
+      <c r="AK937" s="4" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n"/>
@@ -36432,6 +37378,7 @@
       <c r="AH938" s="2" t="n"/>
       <c r="AI938" s="2" t="n"/>
       <c r="AJ938" s="2" t="n"/>
+      <c r="AK938" s="2" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="4" t="n"/>
@@ -36470,6 +37417,7 @@
       <c r="AH939" s="4" t="n"/>
       <c r="AI939" s="4" t="n"/>
       <c r="AJ939" s="4" t="n"/>
+      <c r="AK939" s="4" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n"/>
@@ -36508,6 +37456,7 @@
       <c r="AH940" s="2" t="n"/>
       <c r="AI940" s="2" t="n"/>
       <c r="AJ940" s="2" t="n"/>
+      <c r="AK940" s="2" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="4" t="n"/>
@@ -36546,6 +37495,7 @@
       <c r="AH941" s="4" t="n"/>
       <c r="AI941" s="4" t="n"/>
       <c r="AJ941" s="4" t="n"/>
+      <c r="AK941" s="4" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n"/>
@@ -36584,6 +37534,7 @@
       <c r="AH942" s="2" t="n"/>
       <c r="AI942" s="2" t="n"/>
       <c r="AJ942" s="2" t="n"/>
+      <c r="AK942" s="2" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="4" t="n"/>
@@ -36622,6 +37573,7 @@
       <c r="AH943" s="4" t="n"/>
       <c r="AI943" s="4" t="n"/>
       <c r="AJ943" s="4" t="n"/>
+      <c r="AK943" s="4" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n"/>
@@ -36660,6 +37612,7 @@
       <c r="AH944" s="2" t="n"/>
       <c r="AI944" s="2" t="n"/>
       <c r="AJ944" s="2" t="n"/>
+      <c r="AK944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="4" t="n"/>
@@ -36698,6 +37651,7 @@
       <c r="AH945" s="4" t="n"/>
       <c r="AI945" s="4" t="n"/>
       <c r="AJ945" s="4" t="n"/>
+      <c r="AK945" s="4" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n"/>
@@ -36736,6 +37690,7 @@
       <c r="AH946" s="2" t="n"/>
       <c r="AI946" s="2" t="n"/>
       <c r="AJ946" s="2" t="n"/>
+      <c r="AK946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="4" t="n"/>
@@ -36774,6 +37729,7 @@
       <c r="AH947" s="4" t="n"/>
       <c r="AI947" s="4" t="n"/>
       <c r="AJ947" s="4" t="n"/>
+      <c r="AK947" s="4" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n"/>
@@ -36812,6 +37768,7 @@
       <c r="AH948" s="2" t="n"/>
       <c r="AI948" s="2" t="n"/>
       <c r="AJ948" s="2" t="n"/>
+      <c r="AK948" s="2" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="4" t="n"/>
@@ -36850,6 +37807,7 @@
       <c r="AH949" s="4" t="n"/>
       <c r="AI949" s="4" t="n"/>
       <c r="AJ949" s="4" t="n"/>
+      <c r="AK949" s="4" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n"/>
@@ -36888,6 +37846,7 @@
       <c r="AH950" s="2" t="n"/>
       <c r="AI950" s="2" t="n"/>
       <c r="AJ950" s="2" t="n"/>
+      <c r="AK950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="4" t="n"/>
@@ -36926,6 +37885,7 @@
       <c r="AH951" s="4" t="n"/>
       <c r="AI951" s="4" t="n"/>
       <c r="AJ951" s="4" t="n"/>
+      <c r="AK951" s="4" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n"/>
@@ -36964,6 +37924,7 @@
       <c r="AH952" s="2" t="n"/>
       <c r="AI952" s="2" t="n"/>
       <c r="AJ952" s="2" t="n"/>
+      <c r="AK952" s="2" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="4" t="n"/>
@@ -37002,6 +37963,7 @@
       <c r="AH953" s="4" t="n"/>
       <c r="AI953" s="4" t="n"/>
       <c r="AJ953" s="4" t="n"/>
+      <c r="AK953" s="4" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n"/>
@@ -37040,6 +38002,7 @@
       <c r="AH954" s="2" t="n"/>
       <c r="AI954" s="2" t="n"/>
       <c r="AJ954" s="2" t="n"/>
+      <c r="AK954" s="2" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="4" t="n"/>
@@ -37078,6 +38041,7 @@
       <c r="AH955" s="4" t="n"/>
       <c r="AI955" s="4" t="n"/>
       <c r="AJ955" s="4" t="n"/>
+      <c r="AK955" s="4" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n"/>
@@ -37116,6 +38080,7 @@
       <c r="AH956" s="2" t="n"/>
       <c r="AI956" s="2" t="n"/>
       <c r="AJ956" s="2" t="n"/>
+      <c r="AK956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="4" t="n"/>
@@ -37154,6 +38119,7 @@
       <c r="AH957" s="4" t="n"/>
       <c r="AI957" s="4" t="n"/>
       <c r="AJ957" s="4" t="n"/>
+      <c r="AK957" s="4" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n"/>
@@ -37192,6 +38158,7 @@
       <c r="AH958" s="2" t="n"/>
       <c r="AI958" s="2" t="n"/>
       <c r="AJ958" s="2" t="n"/>
+      <c r="AK958" s="2" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="4" t="n"/>
@@ -37230,6 +38197,7 @@
       <c r="AH959" s="4" t="n"/>
       <c r="AI959" s="4" t="n"/>
       <c r="AJ959" s="4" t="n"/>
+      <c r="AK959" s="4" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n"/>
@@ -37268,6 +38236,7 @@
       <c r="AH960" s="2" t="n"/>
       <c r="AI960" s="2" t="n"/>
       <c r="AJ960" s="2" t="n"/>
+      <c r="AK960" s="2" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="4" t="n"/>
@@ -37306,6 +38275,7 @@
       <c r="AH961" s="4" t="n"/>
       <c r="AI961" s="4" t="n"/>
       <c r="AJ961" s="4" t="n"/>
+      <c r="AK961" s="4" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n"/>
@@ -37344,6 +38314,7 @@
       <c r="AH962" s="2" t="n"/>
       <c r="AI962" s="2" t="n"/>
       <c r="AJ962" s="2" t="n"/>
+      <c r="AK962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="4" t="n"/>
@@ -37382,6 +38353,7 @@
       <c r="AH963" s="4" t="n"/>
       <c r="AI963" s="4" t="n"/>
       <c r="AJ963" s="4" t="n"/>
+      <c r="AK963" s="4" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n"/>
@@ -37420,6 +38392,7 @@
       <c r="AH964" s="2" t="n"/>
       <c r="AI964" s="2" t="n"/>
       <c r="AJ964" s="2" t="n"/>
+      <c r="AK964" s="2" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="4" t="n"/>
@@ -37458,6 +38431,7 @@
       <c r="AH965" s="4" t="n"/>
       <c r="AI965" s="4" t="n"/>
       <c r="AJ965" s="4" t="n"/>
+      <c r="AK965" s="4" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n"/>
@@ -37496,6 +38470,7 @@
       <c r="AH966" s="2" t="n"/>
       <c r="AI966" s="2" t="n"/>
       <c r="AJ966" s="2" t="n"/>
+      <c r="AK966" s="2" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="4" t="n"/>
@@ -37534,6 +38509,7 @@
       <c r="AH967" s="4" t="n"/>
       <c r="AI967" s="4" t="n"/>
       <c r="AJ967" s="4" t="n"/>
+      <c r="AK967" s="4" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n"/>
@@ -37572,6 +38548,7 @@
       <c r="AH968" s="2" t="n"/>
       <c r="AI968" s="2" t="n"/>
       <c r="AJ968" s="2" t="n"/>
+      <c r="AK968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="4" t="n"/>
@@ -37610,6 +38587,7 @@
       <c r="AH969" s="4" t="n"/>
       <c r="AI969" s="4" t="n"/>
       <c r="AJ969" s="4" t="n"/>
+      <c r="AK969" s="4" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n"/>
@@ -37648,6 +38626,7 @@
       <c r="AH970" s="2" t="n"/>
       <c r="AI970" s="2" t="n"/>
       <c r="AJ970" s="2" t="n"/>
+      <c r="AK970" s="2" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="4" t="n"/>
@@ -37686,6 +38665,7 @@
       <c r="AH971" s="4" t="n"/>
       <c r="AI971" s="4" t="n"/>
       <c r="AJ971" s="4" t="n"/>
+      <c r="AK971" s="4" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n"/>
@@ -37724,6 +38704,7 @@
       <c r="AH972" s="2" t="n"/>
       <c r="AI972" s="2" t="n"/>
       <c r="AJ972" s="2" t="n"/>
+      <c r="AK972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="4" t="n"/>
@@ -37762,6 +38743,7 @@
       <c r="AH973" s="4" t="n"/>
       <c r="AI973" s="4" t="n"/>
       <c r="AJ973" s="4" t="n"/>
+      <c r="AK973" s="4" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n"/>
@@ -37800,6 +38782,7 @@
       <c r="AH974" s="2" t="n"/>
       <c r="AI974" s="2" t="n"/>
       <c r="AJ974" s="2" t="n"/>
+      <c r="AK974" s="2" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="4" t="n"/>
@@ -37838,6 +38821,7 @@
       <c r="AH975" s="4" t="n"/>
       <c r="AI975" s="4" t="n"/>
       <c r="AJ975" s="4" t="n"/>
+      <c r="AK975" s="4" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n"/>
@@ -37876,6 +38860,7 @@
       <c r="AH976" s="2" t="n"/>
       <c r="AI976" s="2" t="n"/>
       <c r="AJ976" s="2" t="n"/>
+      <c r="AK976" s="2" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="4" t="n"/>
@@ -37914,6 +38899,7 @@
       <c r="AH977" s="4" t="n"/>
       <c r="AI977" s="4" t="n"/>
       <c r="AJ977" s="4" t="n"/>
+      <c r="AK977" s="4" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n"/>
@@ -37952,6 +38938,7 @@
       <c r="AH978" s="2" t="n"/>
       <c r="AI978" s="2" t="n"/>
       <c r="AJ978" s="2" t="n"/>
+      <c r="AK978" s="2" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="4" t="n"/>
@@ -37990,6 +38977,7 @@
       <c r="AH979" s="4" t="n"/>
       <c r="AI979" s="4" t="n"/>
       <c r="AJ979" s="4" t="n"/>
+      <c r="AK979" s="4" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n"/>
@@ -38028,6 +39016,7 @@
       <c r="AH980" s="2" t="n"/>
       <c r="AI980" s="2" t="n"/>
       <c r="AJ980" s="2" t="n"/>
+      <c r="AK980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="4" t="n"/>
@@ -38066,6 +39055,7 @@
       <c r="AH981" s="4" t="n"/>
       <c r="AI981" s="4" t="n"/>
       <c r="AJ981" s="4" t="n"/>
+      <c r="AK981" s="4" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n"/>
@@ -38104,6 +39094,7 @@
       <c r="AH982" s="2" t="n"/>
       <c r="AI982" s="2" t="n"/>
       <c r="AJ982" s="2" t="n"/>
+      <c r="AK982" s="2" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="4" t="n"/>
@@ -38142,6 +39133,7 @@
       <c r="AH983" s="4" t="n"/>
       <c r="AI983" s="4" t="n"/>
       <c r="AJ983" s="4" t="n"/>
+      <c r="AK983" s="4" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n"/>
@@ -38180,6 +39172,7 @@
       <c r="AH984" s="2" t="n"/>
       <c r="AI984" s="2" t="n"/>
       <c r="AJ984" s="2" t="n"/>
+      <c r="AK984" s="2" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="4" t="n"/>
@@ -38218,6 +39211,7 @@
       <c r="AH985" s="4" t="n"/>
       <c r="AI985" s="4" t="n"/>
       <c r="AJ985" s="4" t="n"/>
+      <c r="AK985" s="4" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n"/>
@@ -38256,6 +39250,7 @@
       <c r="AH986" s="2" t="n"/>
       <c r="AI986" s="2" t="n"/>
       <c r="AJ986" s="2" t="n"/>
+      <c r="AK986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="4" t="n"/>
@@ -38294,6 +39289,7 @@
       <c r="AH987" s="4" t="n"/>
       <c r="AI987" s="4" t="n"/>
       <c r="AJ987" s="4" t="n"/>
+      <c r="AK987" s="4" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n"/>
@@ -38332,6 +39328,7 @@
       <c r="AH988" s="2" t="n"/>
       <c r="AI988" s="2" t="n"/>
       <c r="AJ988" s="2" t="n"/>
+      <c r="AK988" s="2" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="4" t="n"/>
@@ -38370,6 +39367,7 @@
       <c r="AH989" s="4" t="n"/>
       <c r="AI989" s="4" t="n"/>
       <c r="AJ989" s="4" t="n"/>
+      <c r="AK989" s="4" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n"/>
@@ -38408,6 +39406,7 @@
       <c r="AH990" s="2" t="n"/>
       <c r="AI990" s="2" t="n"/>
       <c r="AJ990" s="2" t="n"/>
+      <c r="AK990" s="2" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="4" t="n"/>
@@ -38446,6 +39445,7 @@
       <c r="AH991" s="4" t="n"/>
       <c r="AI991" s="4" t="n"/>
       <c r="AJ991" s="4" t="n"/>
+      <c r="AK991" s="4" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n"/>
@@ -38484,6 +39484,7 @@
       <c r="AH992" s="2" t="n"/>
       <c r="AI992" s="2" t="n"/>
       <c r="AJ992" s="2" t="n"/>
+      <c r="AK992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="4" t="n"/>
@@ -38522,6 +39523,7 @@
       <c r="AH993" s="4" t="n"/>
       <c r="AI993" s="4" t="n"/>
       <c r="AJ993" s="4" t="n"/>
+      <c r="AK993" s="4" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n"/>
@@ -38560,6 +39562,7 @@
       <c r="AH994" s="2" t="n"/>
       <c r="AI994" s="2" t="n"/>
       <c r="AJ994" s="2" t="n"/>
+      <c r="AK994" s="2" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="4" t="n"/>
@@ -38598,6 +39601,7 @@
       <c r="AH995" s="4" t="n"/>
       <c r="AI995" s="4" t="n"/>
       <c r="AJ995" s="4" t="n"/>
+      <c r="AK995" s="4" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n"/>
@@ -38636,6 +39640,7 @@
       <c r="AH996" s="2" t="n"/>
       <c r="AI996" s="2" t="n"/>
       <c r="AJ996" s="2" t="n"/>
+      <c r="AK996" s="2" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="4" t="n"/>
@@ -38674,6 +39679,7 @@
       <c r="AH997" s="4" t="n"/>
       <c r="AI997" s="4" t="n"/>
       <c r="AJ997" s="4" t="n"/>
+      <c r="AK997" s="4" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n"/>
@@ -38712,6 +39718,7 @@
       <c r="AH998" s="2" t="n"/>
       <c r="AI998" s="2" t="n"/>
       <c r="AJ998" s="2" t="n"/>
+      <c r="AK998" s="2" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="4" t="n"/>
@@ -38750,6 +39757,7 @@
       <c r="AH999" s="4" t="n"/>
       <c r="AI999" s="4" t="n"/>
       <c r="AJ999" s="4" t="n"/>
+      <c r="AK999" s="4" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n"/>
@@ -38788,6 +39796,7 @@
       <c r="AH1000" s="2" t="n"/>
       <c r="AI1000" s="2" t="n"/>
       <c r="AJ1000" s="2" t="n"/>
+      <c r="AK1000" s="2" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="4" t="n"/>
@@ -38826,10 +39835,11 @@
       <c r="AH1001" s="4" t="n"/>
       <c r="AI1001" s="4" t="n"/>
       <c r="AJ1001" s="4" t="n"/>
+      <c r="AK1001" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ1"/>
-  <dataValidations count="14">
+  <autoFilter ref="A1:AK1"/>
+  <dataValidations count="13">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
@@ -38862,15 +39872,12 @@
     <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>'_Lookups'!$C$2:$C$83</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>"2x2,4x4,8x8"</formula1>
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
+      <formula1>"5G only,3G5G,4G5G,3G4G5G"</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="PCI không hợp lệ" error="NR PCI phải trong khoảng 0 – 1007" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>1007</formula2>
-    </dataValidation>
-    <dataValidation sqref="AJ2:AJ1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="X2:X1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cell max power không hợp lệ" error="Cell max power thường trong khoảng -30 đến 60 dBm" type="decimal" operator="between">
       <formula1>-30</formula1>
@@ -38887,7 +39894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -39172,107 +40179,95 @@
       </c>
       <c r="C26" s="9" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa để trống</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>→ Tự động điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường). Ví dụ: HNIHKM44DI4DA → HNIHKM</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Tinh / Phuong xa đã có giá trị</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>→ Giữ nguyên giá trị đã nhập, KHÔNG tự động điền</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Không tìm thấy mã 6 ký tự</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>→ Tinh / Phuong xa để trống (không phải lỗi – các cột này KHÔNG bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MÔ TẢ CÁC CỘT</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Tên cột</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Mô tả / Hướng dẫn</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Mien</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Miền: MB / MT / MN</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Tinh</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Tỉnh / Thành phố – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Phuong xa</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Phường / Xã – chọn từ danh sách</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Site Name</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Tên site – bắt buộc, phải khớp với site đã có</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Site Name Old</t>
+          <t>Tinh</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Tên site cũ – điền khi site vừa đổi tên</t>
+          <t>Tỉnh / Thành phố – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -39282,116 +40277,116 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Cell Name</t>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Phuong xa</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>Tên cell – bắt buộc, duy nhất trong site</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
+          <t>Phường / Xã – chọn từ danh sách. KHÔNG bắt buộc – để trống thì hệ thống tự điền theo 6 ký tự đầu của Cell Name (khớp cột ky_tu_1_6 trong danh mục Tỉnh/Xã/Phường); đã nhập thì giữ nguyên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Site Name</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Tên site – bắt buộc, phải khớp với site đã có</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Cell Name Old</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Tên cell cũ – điền khi cell vừa đổi tên</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>Site Name Old</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Tên site cũ – điền khi site vừa đổi tên</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Cell Name</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Tên cell – bắt buộc, duy nhất trong site (vd: HNIHKM44DI4DA)</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Cell Name Old</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Tên cell cũ – điền khi cell vừa đổi tên</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
           <t>Cell VIP</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Mức độ VIP: VIP hoặc VVIP</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>MORAN</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>MORAN: VNPT HOST hoặc MBF HOST</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Latitude – phải trong 8.33–23.39</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Longitude – phải trong 102.14–109.47</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Vung phu song</t>
+          <t>MORAN</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Vùng phủ sóng: Indoor hoặc Outdoor</t>
+          <t>MORAN: VNPT HOST hoặc MBF HOST</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -39403,12 +40398,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Lat</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Hãng thiết bị – bắt buộc, chọn từ danh sách</t>
+          <t>Latitude – phải trong 8.33–23.39</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -39420,12 +40415,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Do cao anten</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
+          <t>Longitude – phải trong 102.14–109.47</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -39435,31 +40430,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Azimuth</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Vung phu song</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>✔ Bắt buộc</t>
+          <t>Vùng phủ sóng: Indoor hoặc Outdoor</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>M-tilt</t>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
+          <t>Hãng thiết bị – bắt buộc, chọn từ danh sách</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -39471,80 +40466,80 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
+          <t>Do cao anten</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>Độ cao anten – bắt buộc (số hoặc chuỗi, vd: 28 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Azimuth</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Góc phương vị – bắt buộc (số hoặc chuỗi, vd: 120 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>M-tilt</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Mechanical tilt – bắt buộc (số hoặc chuỗi, vd: 2 hoặc IBC)</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>✔ Bắt buộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
           <t>E-Tilt</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Electrical tilt – bắt buộc (số hoặc chuỗi, vd: 4 hoặc IBC)</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>✔ Bắt buộc</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Total Tilt</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Loai Anten</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Loại anten – chọn từ danh sách antenna</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Baseband</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Tên thiết bị baseband</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Tùy chọn</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>Total Tilt</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>Tên thiết bị RF</t>
+          <t>Tổng tilt (số hoặc chuỗi, tự tính hoặc để trống)</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -39556,12 +40551,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Cell ID</t>
+          <t>Loai Anten</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Cell ID (chuỗi hoặc số)</t>
+          <t>Loại anten – chọn từ danh sách antenna</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -39573,12 +40568,12 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>MIMO</t>
+          <t>Chung anten</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>Cấu hình MIMO: 2x2 / 4x4 / 8x8</t>
+          <t>Chung anten – chọn từ danh sách: 5G only, 3G5G, 4G5G, 3G4G5G</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -39590,12 +40585,12 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Cell max power (dBm)</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Công suất tối đa cell (dBm)</t>
+          <t>Tên thiết bị RF</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -39607,12 +40602,12 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>BBUname</t>
+          <t>Cell ID</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Tên BBU</t>
+          <t>Cell ID (chuỗi hoặc số)</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -39624,12 +40619,12 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Cell status (at dump time)</t>
+          <t>MIMO</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Trạng thái cell tại thời điểm dump</t>
+          <t>Cấu hình MIMO – nhập tự do (vd: 2x2, 4x4, 8x8, 32T32R)</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -39641,12 +40636,12 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>gNodeB ID</t>
+          <t>Cell max power (dBm)</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>gNodeB ID</t>
+          <t>Công suất tối đa cell (dBm)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -39658,12 +40653,12 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>BBUname</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Tracking Area Code</t>
+          <t>Tên BBU</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -39675,12 +40670,12 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>PCI</t>
+          <t>Cell status (at dump time)</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>Physical Cell Identity 0–1007 (NR)</t>
+          <t>Trạng thái cell tại thời điểm dump</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -39692,12 +40687,12 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Root Sequence ID</t>
+          <t>gNodeB ID</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>Root Sequence Index</t>
+          <t>gNodeB ID</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -39709,12 +40704,12 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>SSB-ARFCN</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>SSB Absolute Radio Frequency Channel Number</t>
+          <t>Tracking Area Code</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -39726,12 +40721,12 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Center-ARFCN</t>
+          <t>PCI</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Center Frequency ARFCN</t>
+          <t>Physical Cell Identity 0–1007 (NR)</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
@@ -39743,12 +40738,12 @@
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>GSCN</t>
+          <t>Root Sequence ID</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Global Synchronization Channel Number</t>
+          <t>Root Sequence Index</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -39760,12 +40755,12 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Bandwidth (MHz)</t>
+          <t>SSB-ARFCN</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Bandwidth (MHz) – ví dụ: 50, 100, 200</t>
+          <t>SSB Absolute Radio Frequency Channel Number</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
@@ -39777,12 +40772,12 @@
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>NCI</t>
+          <t>Center-ARFCN</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>NR Cell Identity</t>
+          <t>Center Frequency ARFCN</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -39794,15 +40789,83 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
+          <t>GSCN</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>Global Synchronization Channel Number</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Bandwidth (MHz)</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Bandwidth (MHz) – ví dụ: 50, 100, 200</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>NCI</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>NR Cell Identity</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
           <t>MU-MIMO</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>Multi-User MIMO: Yes hoặc No</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>Multi-User MIMO – nhập tự do (vd: Yes, No, 16 layers)</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Tùy chọn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>OSS</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>Hệ thống OSS nguồn dữ liệu – nhập tự do</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>Tùy chọn</t>
         </is>
@@ -39810,9 +40873,9 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>

--- a/backend/templates/template_cell_5g.xlsx
+++ b/backend/templates/template_cell_5g.xlsx
@@ -850,11 +850,7 @@
       </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>8x8</t>
-        </is>
-      </c>
+      <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
